--- a/To-Do/MainALR.xlsx
+++ b/To-Do/MainALR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="145">
   <si>
     <t>MainALR</t>
   </si>
@@ -200,6 +200,21 @@
   </si>
   <si>
     <t>A node that'll take an existing object in the game, and then utilize the fade ui to seemlessly switch from a scene in which you're only watching, to a playable section with limited movement for the player to do certain actions</t>
+  </si>
+  <si>
+    <t>Github Site</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Internal Data Saving</t>
+  </si>
+  <si>
+    <t>Node Name: Internal Save/Pull</t>
+  </si>
+  <si>
+    <t>Save node that'll save or pull certain data from an unwipeable save file inside of the game to be used for remembering certain choices across saves and changing the title screens after reaching certain points regardless of if the player restarts their game / save or not</t>
   </si>
   <si>
     <t>MAIN ALR</t>
@@ -701,7 +716,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -733,8 +748,14 @@
     <xf borderId="10" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf borderId="3" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="10" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="3" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="11" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -1954,13 +1975,19 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
+      <c r="E21" s="27" t="s">
+        <v>62</v>
+      </c>
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
-      <c r="H21" s="18"/>
+      <c r="H21" s="27" t="s">
+        <v>63</v>
+      </c>
       <c r="I21" s="8"/>
       <c r="J21" s="9"/>
-      <c r="K21" s="18"/>
+      <c r="K21" s="27" t="s">
+        <v>62</v>
+      </c>
       <c r="L21" s="8"/>
       <c r="M21" s="9"/>
       <c r="N21" s="2"/>
@@ -1970,7 +1997,7 @@
       <c r="R21" s="21"/>
       <c r="S21" s="22"/>
       <c r="T21" s="23"/>
-      <c r="U21" s="27"/>
+      <c r="U21" s="28"/>
       <c r="V21" s="22"/>
       <c r="W21" s="23"/>
       <c r="X21" s="20"/>
@@ -1991,13 +2018,19 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="D22" s="15"/>
-      <c r="E22" s="16"/>
+      <c r="E22" s="29" t="s">
+        <v>64</v>
+      </c>
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
-      <c r="H22" s="16"/>
+      <c r="H22" s="29" t="s">
+        <v>65</v>
+      </c>
       <c r="I22" s="8"/>
       <c r="J22" s="9"/>
-      <c r="K22" s="16"/>
+      <c r="K22" s="29" t="s">
+        <v>66</v>
+      </c>
       <c r="L22" s="8"/>
       <c r="M22" s="9"/>
       <c r="N22" s="2"/>
@@ -2226,9 +2259,9 @@
       <c r="O28" s="16"/>
       <c r="P28" s="8"/>
       <c r="Q28" s="9"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="32"/>
       <c r="U28" s="18"/>
       <c r="V28" s="8"/>
       <c r="W28" s="9"/>
@@ -3203,10 +3236,10 @@
       <c r="E55" s="25"/>
       <c r="F55" s="22"/>
       <c r="G55" s="23"/>
-      <c r="H55" s="31"/>
+      <c r="H55" s="33"/>
       <c r="I55" s="22"/>
       <c r="J55" s="23"/>
-      <c r="K55" s="31"/>
+      <c r="K55" s="33"/>
       <c r="L55" s="22"/>
       <c r="M55" s="23"/>
       <c r="O55" s="16"/>
@@ -3275,10 +3308,10 @@
       <c r="E57" s="25"/>
       <c r="F57" s="22"/>
       <c r="G57" s="23"/>
-      <c r="H57" s="31"/>
+      <c r="H57" s="33"/>
       <c r="I57" s="22"/>
       <c r="J57" s="23"/>
-      <c r="K57" s="31"/>
+      <c r="K57" s="33"/>
       <c r="L57" s="22"/>
       <c r="M57" s="23"/>
       <c r="O57" s="16"/>
@@ -3347,10 +3380,10 @@
       <c r="E59" s="25"/>
       <c r="F59" s="22"/>
       <c r="G59" s="23"/>
-      <c r="H59" s="31"/>
+      <c r="H59" s="33"/>
       <c r="I59" s="22"/>
       <c r="J59" s="23"/>
-      <c r="K59" s="31"/>
+      <c r="K59" s="33"/>
       <c r="L59" s="22"/>
       <c r="M59" s="23"/>
       <c r="O59" s="16"/>
@@ -3419,10 +3452,10 @@
       <c r="E61" s="25"/>
       <c r="F61" s="22"/>
       <c r="G61" s="23"/>
-      <c r="H61" s="31"/>
+      <c r="H61" s="33"/>
       <c r="I61" s="22"/>
       <c r="J61" s="23"/>
-      <c r="K61" s="31"/>
+      <c r="K61" s="33"/>
       <c r="L61" s="22"/>
       <c r="M61" s="23"/>
       <c r="O61" s="16"/>
@@ -3491,10 +3524,10 @@
       <c r="E63" s="25"/>
       <c r="F63" s="22"/>
       <c r="G63" s="23"/>
-      <c r="H63" s="31"/>
+      <c r="H63" s="33"/>
       <c r="I63" s="22"/>
       <c r="J63" s="23"/>
-      <c r="K63" s="31"/>
+      <c r="K63" s="33"/>
       <c r="L63" s="22"/>
       <c r="M63" s="23"/>
       <c r="O63" s="16"/>
@@ -3563,10 +3596,10 @@
       <c r="E65" s="25"/>
       <c r="F65" s="22"/>
       <c r="G65" s="23"/>
-      <c r="H65" s="31"/>
+      <c r="H65" s="33"/>
       <c r="I65" s="22"/>
       <c r="J65" s="23"/>
-      <c r="K65" s="31"/>
+      <c r="K65" s="33"/>
       <c r="L65" s="22"/>
       <c r="M65" s="23"/>
       <c r="O65" s="16"/>
@@ -3635,10 +3668,10 @@
       <c r="E67" s="25"/>
       <c r="F67" s="22"/>
       <c r="G67" s="23"/>
-      <c r="H67" s="31"/>
+      <c r="H67" s="33"/>
       <c r="I67" s="22"/>
       <c r="J67" s="23"/>
-      <c r="K67" s="31"/>
+      <c r="K67" s="33"/>
       <c r="L67" s="22"/>
       <c r="M67" s="23"/>
       <c r="O67" s="16"/>
@@ -3707,10 +3740,10 @@
       <c r="E69" s="25"/>
       <c r="F69" s="22"/>
       <c r="G69" s="23"/>
-      <c r="H69" s="31"/>
+      <c r="H69" s="33"/>
       <c r="I69" s="22"/>
       <c r="J69" s="23"/>
-      <c r="K69" s="31"/>
+      <c r="K69" s="33"/>
       <c r="L69" s="22"/>
       <c r="M69" s="23"/>
       <c r="O69" s="16"/>
@@ -3782,7 +3815,7 @@
       <c r="H71" s="26"/>
       <c r="I71" s="22"/>
       <c r="J71" s="23"/>
-      <c r="K71" s="31"/>
+      <c r="K71" s="33"/>
       <c r="L71" s="22"/>
       <c r="M71" s="23"/>
       <c r="O71" s="16"/>
@@ -3815,7 +3848,7 @@
       <c r="E72" s="21"/>
       <c r="F72" s="22"/>
       <c r="G72" s="23"/>
-      <c r="H72" s="27"/>
+      <c r="H72" s="28"/>
       <c r="I72" s="22"/>
       <c r="J72" s="23"/>
       <c r="K72" s="24"/>
@@ -3851,10 +3884,10 @@
       <c r="E73" s="25"/>
       <c r="F73" s="22"/>
       <c r="G73" s="23"/>
-      <c r="H73" s="31"/>
+      <c r="H73" s="33"/>
       <c r="I73" s="22"/>
       <c r="J73" s="23"/>
-      <c r="K73" s="31"/>
+      <c r="K73" s="33"/>
       <c r="L73" s="22"/>
       <c r="M73" s="23"/>
       <c r="O73" s="16"/>
@@ -3923,10 +3956,10 @@
       <c r="E75" s="25"/>
       <c r="F75" s="22"/>
       <c r="G75" s="23"/>
-      <c r="H75" s="31"/>
+      <c r="H75" s="33"/>
       <c r="I75" s="22"/>
       <c r="J75" s="23"/>
-      <c r="K75" s="31"/>
+      <c r="K75" s="33"/>
       <c r="L75" s="22"/>
       <c r="M75" s="23"/>
       <c r="O75" s="16"/>
@@ -3995,10 +4028,10 @@
       <c r="E77" s="25"/>
       <c r="F77" s="22"/>
       <c r="G77" s="23"/>
-      <c r="H77" s="31"/>
+      <c r="H77" s="33"/>
       <c r="I77" s="22"/>
       <c r="J77" s="23"/>
-      <c r="K77" s="31"/>
+      <c r="K77" s="33"/>
       <c r="L77" s="22"/>
       <c r="M77" s="23"/>
       <c r="O77" s="16"/>
@@ -4067,10 +4100,10 @@
       <c r="E79" s="25"/>
       <c r="F79" s="22"/>
       <c r="G79" s="23"/>
-      <c r="H79" s="31"/>
+      <c r="H79" s="33"/>
       <c r="I79" s="22"/>
       <c r="J79" s="23"/>
-      <c r="K79" s="31"/>
+      <c r="K79" s="33"/>
       <c r="L79" s="22"/>
       <c r="M79" s="23"/>
       <c r="O79" s="16"/>
@@ -4139,10 +4172,10 @@
       <c r="E81" s="25"/>
       <c r="F81" s="22"/>
       <c r="G81" s="23"/>
-      <c r="H81" s="31"/>
+      <c r="H81" s="33"/>
       <c r="I81" s="22"/>
       <c r="J81" s="23"/>
-      <c r="K81" s="31"/>
+      <c r="K81" s="33"/>
       <c r="L81" s="22"/>
       <c r="M81" s="23"/>
       <c r="O81" s="16"/>
@@ -4211,10 +4244,10 @@
       <c r="E83" s="25"/>
       <c r="F83" s="22"/>
       <c r="G83" s="23"/>
-      <c r="H83" s="31"/>
+      <c r="H83" s="33"/>
       <c r="I83" s="22"/>
       <c r="J83" s="23"/>
-      <c r="K83" s="31"/>
+      <c r="K83" s="33"/>
       <c r="L83" s="22"/>
       <c r="M83" s="23"/>
       <c r="O83" s="16"/>
@@ -4283,10 +4316,10 @@
       <c r="E85" s="25"/>
       <c r="F85" s="22"/>
       <c r="G85" s="23"/>
-      <c r="H85" s="31"/>
+      <c r="H85" s="33"/>
       <c r="I85" s="22"/>
       <c r="J85" s="23"/>
-      <c r="K85" s="31"/>
+      <c r="K85" s="33"/>
       <c r="L85" s="22"/>
       <c r="M85" s="23"/>
     </row>
@@ -4307,10 +4340,10 @@
       <c r="E87" s="25"/>
       <c r="F87" s="22"/>
       <c r="G87" s="23"/>
-      <c r="H87" s="31"/>
+      <c r="H87" s="33"/>
       <c r="I87" s="22"/>
       <c r="J87" s="23"/>
-      <c r="K87" s="31"/>
+      <c r="K87" s="33"/>
       <c r="L87" s="22"/>
       <c r="M87" s="23"/>
     </row>
@@ -4331,10 +4364,10 @@
       <c r="E89" s="25"/>
       <c r="F89" s="22"/>
       <c r="G89" s="23"/>
-      <c r="H89" s="31"/>
+      <c r="H89" s="33"/>
       <c r="I89" s="22"/>
       <c r="J89" s="23"/>
-      <c r="K89" s="31"/>
+      <c r="K89" s="33"/>
       <c r="L89" s="22"/>
       <c r="M89" s="23"/>
     </row>
@@ -4355,10 +4388,10 @@
       <c r="E91" s="25"/>
       <c r="F91" s="22"/>
       <c r="G91" s="23"/>
-      <c r="H91" s="31"/>
+      <c r="H91" s="33"/>
       <c r="I91" s="22"/>
       <c r="J91" s="23"/>
-      <c r="K91" s="31"/>
+      <c r="K91" s="33"/>
       <c r="L91" s="22"/>
       <c r="M91" s="23"/>
     </row>
@@ -4379,10 +4412,10 @@
       <c r="E93" s="25"/>
       <c r="F93" s="22"/>
       <c r="G93" s="23"/>
-      <c r="H93" s="31"/>
+      <c r="H93" s="33"/>
       <c r="I93" s="22"/>
       <c r="J93" s="23"/>
-      <c r="K93" s="31"/>
+      <c r="K93" s="33"/>
       <c r="L93" s="22"/>
       <c r="M93" s="23"/>
     </row>
@@ -4403,10 +4436,10 @@
       <c r="E95" s="25"/>
       <c r="F95" s="22"/>
       <c r="G95" s="23"/>
-      <c r="H95" s="31"/>
+      <c r="H95" s="33"/>
       <c r="I95" s="22"/>
       <c r="J95" s="23"/>
-      <c r="K95" s="31"/>
+      <c r="K95" s="33"/>
       <c r="L95" s="22"/>
       <c r="M95" s="23"/>
     </row>
@@ -4427,10 +4460,10 @@
       <c r="E97" s="25"/>
       <c r="F97" s="22"/>
       <c r="G97" s="23"/>
-      <c r="H97" s="31"/>
+      <c r="H97" s="33"/>
       <c r="I97" s="22"/>
       <c r="J97" s="23"/>
-      <c r="K97" s="31"/>
+      <c r="K97" s="33"/>
       <c r="L97" s="22"/>
       <c r="M97" s="23"/>
     </row>
@@ -4447,14 +4480,14 @@
       <c r="M98" s="23"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="D99" s="32"/>
-      <c r="E99" s="31"/>
+      <c r="D99" s="34"/>
+      <c r="E99" s="33"/>
       <c r="F99" s="22"/>
       <c r="G99" s="23"/>
-      <c r="H99" s="31"/>
+      <c r="H99" s="33"/>
       <c r="I99" s="22"/>
       <c r="J99" s="23"/>
-      <c r="K99" s="31"/>
+      <c r="K99" s="33"/>
       <c r="L99" s="22"/>
       <c r="M99" s="23"/>
     </row>
@@ -4471,14 +4504,14 @@
       <c r="M100" s="23"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="D101" s="32"/>
-      <c r="E101" s="31"/>
+      <c r="D101" s="34"/>
+      <c r="E101" s="33"/>
       <c r="F101" s="22"/>
       <c r="G101" s="23"/>
-      <c r="H101" s="31"/>
+      <c r="H101" s="33"/>
       <c r="I101" s="22"/>
       <c r="J101" s="23"/>
-      <c r="K101" s="31"/>
+      <c r="K101" s="33"/>
       <c r="L101" s="22"/>
       <c r="M101" s="23"/>
     </row>
@@ -4495,14 +4528,14 @@
       <c r="M102" s="23"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="D103" s="32"/>
-      <c r="E103" s="31"/>
+      <c r="D103" s="34"/>
+      <c r="E103" s="33"/>
       <c r="F103" s="22"/>
       <c r="G103" s="23"/>
-      <c r="H103" s="31"/>
+      <c r="H103" s="33"/>
       <c r="I103" s="22"/>
       <c r="J103" s="23"/>
-      <c r="K103" s="31"/>
+      <c r="K103" s="33"/>
       <c r="L103" s="22"/>
       <c r="M103" s="23"/>
     </row>
@@ -4519,14 +4552,14 @@
       <c r="M104" s="23"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="D105" s="32"/>
-      <c r="E105" s="31"/>
+      <c r="D105" s="34"/>
+      <c r="E105" s="33"/>
       <c r="F105" s="22"/>
       <c r="G105" s="23"/>
-      <c r="H105" s="31"/>
+      <c r="H105" s="33"/>
       <c r="I105" s="22"/>
       <c r="J105" s="23"/>
-      <c r="K105" s="31"/>
+      <c r="K105" s="33"/>
       <c r="L105" s="22"/>
       <c r="M105" s="23"/>
     </row>
@@ -4543,14 +4576,14 @@
       <c r="M106" s="23"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="D107" s="32"/>
-      <c r="E107" s="31"/>
+      <c r="D107" s="34"/>
+      <c r="E107" s="33"/>
       <c r="F107" s="22"/>
       <c r="G107" s="23"/>
-      <c r="H107" s="31"/>
+      <c r="H107" s="33"/>
       <c r="I107" s="22"/>
       <c r="J107" s="23"/>
-      <c r="K107" s="31"/>
+      <c r="K107" s="33"/>
       <c r="L107" s="22"/>
       <c r="M107" s="23"/>
     </row>
@@ -4567,14 +4600,14 @@
       <c r="M108" s="23"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="D109" s="32"/>
-      <c r="E109" s="31"/>
+      <c r="D109" s="34"/>
+      <c r="E109" s="33"/>
       <c r="F109" s="22"/>
       <c r="G109" s="23"/>
-      <c r="H109" s="31"/>
+      <c r="H109" s="33"/>
       <c r="I109" s="22"/>
       <c r="J109" s="23"/>
-      <c r="K109" s="31"/>
+      <c r="K109" s="33"/>
       <c r="L109" s="22"/>
       <c r="M109" s="23"/>
     </row>
@@ -4591,14 +4624,14 @@
       <c r="M110" s="23"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="D111" s="32"/>
-      <c r="E111" s="31"/>
+      <c r="D111" s="34"/>
+      <c r="E111" s="33"/>
       <c r="F111" s="22"/>
       <c r="G111" s="23"/>
-      <c r="H111" s="31"/>
+      <c r="H111" s="33"/>
       <c r="I111" s="22"/>
       <c r="J111" s="23"/>
-      <c r="K111" s="31"/>
+      <c r="K111" s="33"/>
       <c r="L111" s="22"/>
       <c r="M111" s="23"/>
     </row>
@@ -6495,10 +6528,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -6506,7 +6539,7 @@
     <row r="2" ht="15.75" customHeight="1"/>
     <row r="3" ht="15.75" customHeight="1">
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E3" s="4"/>
     </row>
@@ -6516,11 +6549,11 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="R4" s="33" t="s">
+      <c r="R4" s="35" t="s">
         <v>4</v>
       </c>
       <c r="S4" s="2"/>
-      <c r="AF4" s="34" t="s">
+      <c r="AF4" s="36" t="s">
         <v>5</v>
       </c>
       <c r="AG4" s="2"/>
@@ -6531,11 +6564,11 @@
         <v>6</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="37" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="9"/>
@@ -6550,16 +6583,16 @@
       <c r="L5" s="8"/>
       <c r="M5" s="9"/>
       <c r="N5" s="13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="2"/>
-      <c r="R5" s="35" t="s">
+      <c r="R5" s="37" t="s">
         <v>7</v>
       </c>
       <c r="S5" s="13" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="T5" s="8"/>
       <c r="U5" s="9"/>
@@ -6574,15 +6607,15 @@
       <c r="Z5" s="8"/>
       <c r="AA5" s="9"/>
       <c r="AB5" s="13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AC5" s="8"/>
       <c r="AD5" s="9"/>
-      <c r="AF5" s="35" t="s">
+      <c r="AF5" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>65</v>
+      <c r="AG5" s="38" t="s">
+        <v>70</v>
       </c>
       <c r="AH5" s="22"/>
       <c r="AI5" s="23"/>
@@ -6597,7 +6630,7 @@
       <c r="AN5" s="8"/>
       <c r="AO5" s="9"/>
       <c r="AP5" s="13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AQ5" s="8"/>
       <c r="AR5" s="9"/>
@@ -6607,21 +6640,21 @@
         <v>11</v>
       </c>
       <c r="B6" s="9"/>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="39" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
       <c r="H6" s="16" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="9"/>
       <c r="K6" s="16" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="9"/>
@@ -6629,7 +6662,7 @@
       <c r="O6" s="8"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="37"/>
+      <c r="R6" s="39"/>
       <c r="S6" s="16"/>
       <c r="T6" s="8"/>
       <c r="U6" s="9"/>
@@ -6642,7 +6675,7 @@
       <c r="AB6" s="16"/>
       <c r="AC6" s="8"/>
       <c r="AD6" s="9"/>
-      <c r="AF6" s="37"/>
+      <c r="AF6" s="39"/>
       <c r="AG6" s="16"/>
       <c r="AH6" s="8"/>
       <c r="AI6" s="9"/>
@@ -6661,21 +6694,21 @@
         <v>16</v>
       </c>
       <c r="B7" s="9"/>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="40" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="9"/>
       <c r="H7" s="18" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="9"/>
       <c r="K7" s="18" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="9"/>
@@ -6683,7 +6716,7 @@
       <c r="O7" s="8"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="37"/>
+      <c r="R7" s="39"/>
       <c r="S7" s="18"/>
       <c r="T7" s="8"/>
       <c r="U7" s="9"/>
@@ -6696,7 +6729,7 @@
       <c r="AB7" s="18"/>
       <c r="AC7" s="8"/>
       <c r="AD7" s="9"/>
-      <c r="AF7" s="37"/>
+      <c r="AF7" s="39"/>
       <c r="AG7" s="18"/>
       <c r="AH7" s="8"/>
       <c r="AI7" s="9"/>
@@ -6715,19 +6748,19 @@
         <v>20</v>
       </c>
       <c r="B8" s="9"/>
-      <c r="D8" s="37"/>
+      <c r="D8" s="39"/>
       <c r="E8" s="16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
       <c r="H8" s="18" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="9"/>
       <c r="K8" s="16" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="9"/>
@@ -6735,7 +6768,7 @@
       <c r="O8" s="8"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="2"/>
-      <c r="R8" s="37"/>
+      <c r="R8" s="39"/>
       <c r="S8" s="16"/>
       <c r="T8" s="8"/>
       <c r="U8" s="9"/>
@@ -6748,7 +6781,7 @@
       <c r="AB8" s="16"/>
       <c r="AC8" s="8"/>
       <c r="AD8" s="9"/>
-      <c r="AF8" s="37"/>
+      <c r="AF8" s="39"/>
       <c r="AG8" s="16"/>
       <c r="AH8" s="8"/>
       <c r="AI8" s="9"/>
@@ -6763,19 +6796,19 @@
       <c r="AR8" s="9"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="D9" s="37"/>
+      <c r="D9" s="39"/>
       <c r="E9" s="18" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
       <c r="H9" s="18" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="9"/>
       <c r="K9" s="18" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="9"/>
@@ -6783,7 +6816,7 @@
       <c r="O9" s="8"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="2"/>
-      <c r="R9" s="37"/>
+      <c r="R9" s="39"/>
       <c r="S9" s="18"/>
       <c r="T9" s="8"/>
       <c r="U9" s="9"/>
@@ -6796,7 +6829,7 @@
       <c r="AB9" s="18"/>
       <c r="AC9" s="8"/>
       <c r="AD9" s="9"/>
-      <c r="AF9" s="37"/>
+      <c r="AF9" s="39"/>
       <c r="AG9" s="18"/>
       <c r="AH9" s="8"/>
       <c r="AI9" s="9"/>
@@ -6811,19 +6844,19 @@
       <c r="AR9" s="9"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="D10" s="37"/>
+      <c r="D10" s="39"/>
       <c r="E10" s="16" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
       <c r="H10" s="18" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="9"/>
       <c r="K10" s="16" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="9"/>
@@ -6831,7 +6864,7 @@
       <c r="O10" s="8"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="37"/>
+      <c r="R10" s="39"/>
       <c r="S10" s="16"/>
       <c r="T10" s="8"/>
       <c r="U10" s="9"/>
@@ -6844,7 +6877,7 @@
       <c r="AB10" s="16"/>
       <c r="AC10" s="8"/>
       <c r="AD10" s="9"/>
-      <c r="AF10" s="37"/>
+      <c r="AF10" s="39"/>
       <c r="AG10" s="16"/>
       <c r="AH10" s="8"/>
       <c r="AI10" s="9"/>
@@ -6860,22 +6893,22 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="D11" s="37"/>
+      <c r="D11" s="39"/>
       <c r="E11" s="18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="9"/>
       <c r="H11" s="18" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="9"/>
       <c r="K11" s="18" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="9"/>
@@ -6883,7 +6916,7 @@
       <c r="O11" s="8"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="2"/>
-      <c r="R11" s="37"/>
+      <c r="R11" s="39"/>
       <c r="S11" s="18"/>
       <c r="T11" s="8"/>
       <c r="U11" s="9"/>
@@ -6896,7 +6929,7 @@
       <c r="AB11" s="18"/>
       <c r="AC11" s="8"/>
       <c r="AD11" s="9"/>
-      <c r="AF11" s="37"/>
+      <c r="AF11" s="39"/>
       <c r="AG11" s="18"/>
       <c r="AH11" s="8"/>
       <c r="AI11" s="9"/>
@@ -6911,19 +6944,19 @@
       <c r="AR11" s="9"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="D12" s="37"/>
+      <c r="D12" s="39"/>
       <c r="E12" s="16" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="9"/>
       <c r="H12" s="18" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="9"/>
       <c r="K12" s="16" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L12" s="8"/>
       <c r="M12" s="9"/>
@@ -6931,7 +6964,7 @@
       <c r="O12" s="8"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="2"/>
-      <c r="R12" s="37"/>
+      <c r="R12" s="39"/>
       <c r="S12" s="16"/>
       <c r="T12" s="8"/>
       <c r="U12" s="9"/>
@@ -6944,7 +6977,7 @@
       <c r="AB12" s="16"/>
       <c r="AC12" s="8"/>
       <c r="AD12" s="9"/>
-      <c r="AF12" s="37"/>
+      <c r="AF12" s="39"/>
       <c r="AG12" s="16"/>
       <c r="AH12" s="8"/>
       <c r="AI12" s="9"/>
@@ -6959,21 +6992,21 @@
       <c r="AR12" s="9"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="39" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="9"/>
       <c r="H13" s="18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="9"/>
       <c r="K13" s="18" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="L13" s="8"/>
       <c r="M13" s="9"/>
@@ -6981,7 +7014,7 @@
       <c r="O13" s="8"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="2"/>
-      <c r="R13" s="37"/>
+      <c r="R13" s="39"/>
       <c r="S13" s="18"/>
       <c r="T13" s="8"/>
       <c r="U13" s="9"/>
@@ -6994,7 +7027,7 @@
       <c r="AB13" s="18"/>
       <c r="AC13" s="8"/>
       <c r="AD13" s="9"/>
-      <c r="AF13" s="37"/>
+      <c r="AF13" s="39"/>
       <c r="AG13" s="18"/>
       <c r="AH13" s="8"/>
       <c r="AI13" s="9"/>
@@ -7009,19 +7042,19 @@
       <c r="AR13" s="9"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="D14" s="37"/>
+      <c r="D14" s="39"/>
       <c r="E14" s="16" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
       <c r="H14" s="16" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="9"/>
       <c r="K14" s="16" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L14" s="8"/>
       <c r="M14" s="9"/>
@@ -7029,7 +7062,7 @@
       <c r="O14" s="8"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="2"/>
-      <c r="R14" s="37"/>
+      <c r="R14" s="39"/>
       <c r="S14" s="16"/>
       <c r="T14" s="8"/>
       <c r="U14" s="9"/>
@@ -7042,7 +7075,7 @@
       <c r="AB14" s="16"/>
       <c r="AC14" s="8"/>
       <c r="AD14" s="9"/>
-      <c r="AF14" s="37"/>
+      <c r="AF14" s="39"/>
       <c r="AG14" s="16"/>
       <c r="AH14" s="8"/>
       <c r="AI14" s="9"/>
@@ -7058,24 +7091,24 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="40" t="s">
         <v>58</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
       <c r="H15" s="18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="9"/>
       <c r="K15" s="18" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L15" s="8"/>
       <c r="M15" s="9"/>
@@ -7083,7 +7116,7 @@
       <c r="O15" s="8"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="37"/>
+      <c r="R15" s="39"/>
       <c r="S15" s="18"/>
       <c r="T15" s="8"/>
       <c r="U15" s="9"/>
@@ -7096,7 +7129,7 @@
       <c r="AB15" s="18"/>
       <c r="AC15" s="8"/>
       <c r="AD15" s="9"/>
-      <c r="AF15" s="37"/>
+      <c r="AF15" s="39"/>
       <c r="AG15" s="18"/>
       <c r="AH15" s="8"/>
       <c r="AI15" s="9"/>
@@ -7111,7 +7144,7 @@
       <c r="AR15" s="9"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="D16" s="37"/>
+      <c r="D16" s="39"/>
       <c r="E16" s="16"/>
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
@@ -7125,7 +7158,7 @@
       <c r="O16" s="8"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="37"/>
+      <c r="R16" s="39"/>
       <c r="S16" s="16"/>
       <c r="T16" s="8"/>
       <c r="U16" s="9"/>
@@ -7138,7 +7171,7 @@
       <c r="AB16" s="16"/>
       <c r="AC16" s="8"/>
       <c r="AD16" s="9"/>
-      <c r="AF16" s="37"/>
+      <c r="AF16" s="39"/>
       <c r="AG16" s="16"/>
       <c r="AH16" s="8"/>
       <c r="AI16" s="9"/>
@@ -7153,21 +7186,21 @@
       <c r="AR16" s="9"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="D17" s="37"/>
+      <c r="D17" s="39"/>
       <c r="E17" s="25"/>
       <c r="F17" s="22"/>
       <c r="G17" s="23"/>
-      <c r="H17" s="31"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="22"/>
       <c r="J17" s="23"/>
-      <c r="K17" s="31"/>
+      <c r="K17" s="33"/>
       <c r="L17" s="22"/>
       <c r="M17" s="23"/>
       <c r="N17" s="18"/>
       <c r="O17" s="8"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="37"/>
+      <c r="R17" s="39"/>
       <c r="S17" s="18"/>
       <c r="T17" s="8"/>
       <c r="U17" s="9"/>
@@ -7180,7 +7213,7 @@
       <c r="AB17" s="18"/>
       <c r="AC17" s="8"/>
       <c r="AD17" s="9"/>
-      <c r="AF17" s="37"/>
+      <c r="AF17" s="39"/>
       <c r="AG17" s="18"/>
       <c r="AH17" s="8"/>
       <c r="AI17" s="9"/>
@@ -7195,7 +7228,7 @@
       <c r="AR17" s="9"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="D18" s="37"/>
+      <c r="D18" s="39"/>
       <c r="E18" s="21"/>
       <c r="F18" s="22"/>
       <c r="G18" s="23"/>
@@ -7209,7 +7242,7 @@
       <c r="O18" s="8"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="2"/>
-      <c r="R18" s="37"/>
+      <c r="R18" s="39"/>
       <c r="S18" s="16"/>
       <c r="T18" s="8"/>
       <c r="U18" s="9"/>
@@ -7222,7 +7255,7 @@
       <c r="AB18" s="16"/>
       <c r="AC18" s="8"/>
       <c r="AD18" s="9"/>
-      <c r="AF18" s="37"/>
+      <c r="AF18" s="39"/>
       <c r="AG18" s="16"/>
       <c r="AH18" s="8"/>
       <c r="AI18" s="9"/>
@@ -7237,21 +7270,21 @@
       <c r="AR18" s="9"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="D19" s="37"/>
+      <c r="D19" s="39"/>
       <c r="E19" s="25"/>
       <c r="F19" s="22"/>
       <c r="G19" s="23"/>
-      <c r="H19" s="31"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="22"/>
       <c r="J19" s="23"/>
-      <c r="K19" s="31"/>
+      <c r="K19" s="33"/>
       <c r="L19" s="22"/>
       <c r="M19" s="23"/>
       <c r="N19" s="18"/>
       <c r="O19" s="8"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="2"/>
-      <c r="R19" s="37"/>
+      <c r="R19" s="39"/>
       <c r="S19" s="18"/>
       <c r="T19" s="8"/>
       <c r="U19" s="9"/>
@@ -7264,7 +7297,7 @@
       <c r="AB19" s="18"/>
       <c r="AC19" s="8"/>
       <c r="AD19" s="9"/>
-      <c r="AF19" s="37"/>
+      <c r="AF19" s="39"/>
       <c r="AG19" s="18"/>
       <c r="AH19" s="8"/>
       <c r="AI19" s="9"/>
@@ -7279,7 +7312,7 @@
       <c r="AR19" s="9"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="D20" s="37"/>
+      <c r="D20" s="39"/>
       <c r="E20" s="16"/>
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
@@ -7293,7 +7326,7 @@
       <c r="O20" s="8"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
-      <c r="R20" s="37"/>
+      <c r="R20" s="39"/>
       <c r="S20" s="16"/>
       <c r="T20" s="8"/>
       <c r="U20" s="9"/>
@@ -7306,7 +7339,7 @@
       <c r="AB20" s="16"/>
       <c r="AC20" s="8"/>
       <c r="AD20" s="9"/>
-      <c r="AF20" s="37"/>
+      <c r="AF20" s="39"/>
       <c r="AG20" s="16"/>
       <c r="AH20" s="8"/>
       <c r="AI20" s="9"/>
@@ -7321,7 +7354,7 @@
       <c r="AR20" s="9"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="D21" s="37"/>
+      <c r="D21" s="39"/>
       <c r="E21" s="18"/>
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
@@ -7335,7 +7368,7 @@
       <c r="O21" s="8"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="2"/>
-      <c r="R21" s="37"/>
+      <c r="R21" s="39"/>
       <c r="S21" s="18"/>
       <c r="T21" s="8"/>
       <c r="U21" s="9"/>
@@ -7348,7 +7381,7 @@
       <c r="AB21" s="18"/>
       <c r="AC21" s="8"/>
       <c r="AD21" s="9"/>
-      <c r="AF21" s="37"/>
+      <c r="AF21" s="39"/>
       <c r="AG21" s="18"/>
       <c r="AH21" s="8"/>
       <c r="AI21" s="9"/>
@@ -7363,7 +7396,7 @@
       <c r="AR21" s="9"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="D22" s="37"/>
+      <c r="D22" s="39"/>
       <c r="E22" s="16"/>
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
@@ -7377,7 +7410,7 @@
       <c r="O22" s="8"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="2"/>
-      <c r="R22" s="37"/>
+      <c r="R22" s="39"/>
       <c r="S22" s="16"/>
       <c r="T22" s="8"/>
       <c r="U22" s="9"/>
@@ -7390,7 +7423,7 @@
       <c r="AB22" s="16"/>
       <c r="AC22" s="8"/>
       <c r="AD22" s="9"/>
-      <c r="AF22" s="37"/>
+      <c r="AF22" s="39"/>
       <c r="AG22" s="16"/>
       <c r="AH22" s="8"/>
       <c r="AI22" s="9"/>
@@ -7405,7 +7438,7 @@
       <c r="AR22" s="9"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="D23" s="37"/>
+      <c r="D23" s="39"/>
       <c r="E23" s="18"/>
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
@@ -7419,7 +7452,7 @@
       <c r="O23" s="8"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="2"/>
-      <c r="R23" s="37"/>
+      <c r="R23" s="39"/>
       <c r="S23" s="18"/>
       <c r="T23" s="8"/>
       <c r="U23" s="9"/>
@@ -7432,7 +7465,7 @@
       <c r="AB23" s="18"/>
       <c r="AC23" s="8"/>
       <c r="AD23" s="9"/>
-      <c r="AF23" s="37"/>
+      <c r="AF23" s="39"/>
       <c r="AG23" s="18"/>
       <c r="AH23" s="8"/>
       <c r="AI23" s="9"/>
@@ -7447,7 +7480,7 @@
       <c r="AR23" s="9"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="D24" s="37"/>
+      <c r="D24" s="39"/>
       <c r="E24" s="16"/>
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
@@ -7461,7 +7494,7 @@
       <c r="O24" s="8"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="2"/>
-      <c r="R24" s="37"/>
+      <c r="R24" s="39"/>
       <c r="S24" s="16"/>
       <c r="T24" s="8"/>
       <c r="U24" s="9"/>
@@ -7474,7 +7507,7 @@
       <c r="AB24" s="16"/>
       <c r="AC24" s="8"/>
       <c r="AD24" s="9"/>
-      <c r="AF24" s="37"/>
+      <c r="AF24" s="39"/>
       <c r="AG24" s="16"/>
       <c r="AH24" s="8"/>
       <c r="AI24" s="9"/>
@@ -7489,7 +7522,7 @@
       <c r="AR24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="D25" s="37"/>
+      <c r="D25" s="39"/>
       <c r="E25" s="18"/>
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
@@ -7503,7 +7536,7 @@
       <c r="O25" s="8"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="2"/>
-      <c r="R25" s="37"/>
+      <c r="R25" s="39"/>
       <c r="S25" s="18"/>
       <c r="T25" s="8"/>
       <c r="U25" s="9"/>
@@ -7516,7 +7549,7 @@
       <c r="AB25" s="18"/>
       <c r="AC25" s="8"/>
       <c r="AD25" s="9"/>
-      <c r="AF25" s="37"/>
+      <c r="AF25" s="39"/>
       <c r="AG25" s="18"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="9"/>
@@ -7531,7 +7564,7 @@
       <c r="AR25" s="9"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="D26" s="37"/>
+      <c r="D26" s="39"/>
       <c r="E26" s="16"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
@@ -7545,7 +7578,7 @@
       <c r="O26" s="8"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="2"/>
-      <c r="R26" s="37"/>
+      <c r="R26" s="39"/>
       <c r="S26" s="16"/>
       <c r="T26" s="8"/>
       <c r="U26" s="9"/>
@@ -7558,7 +7591,7 @@
       <c r="AB26" s="16"/>
       <c r="AC26" s="8"/>
       <c r="AD26" s="9"/>
-      <c r="AF26" s="37"/>
+      <c r="AF26" s="39"/>
       <c r="AG26" s="16"/>
       <c r="AH26" s="8"/>
       <c r="AI26" s="9"/>
@@ -7573,7 +7606,7 @@
       <c r="AR26" s="9"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="D27" s="37"/>
+      <c r="D27" s="39"/>
       <c r="E27" s="18"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
@@ -7587,7 +7620,7 @@
       <c r="O27" s="8"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="2"/>
-      <c r="R27" s="37"/>
+      <c r="R27" s="39"/>
       <c r="S27" s="18"/>
       <c r="T27" s="8"/>
       <c r="U27" s="9"/>
@@ -7600,7 +7633,7 @@
       <c r="AB27" s="18"/>
       <c r="AC27" s="8"/>
       <c r="AD27" s="9"/>
-      <c r="AF27" s="37"/>
+      <c r="AF27" s="39"/>
       <c r="AG27" s="18"/>
       <c r="AH27" s="8"/>
       <c r="AI27" s="9"/>
@@ -7615,7 +7648,7 @@
       <c r="AR27" s="9"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="D28" s="37"/>
+      <c r="D28" s="39"/>
       <c r="E28" s="16"/>
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
@@ -7629,7 +7662,7 @@
       <c r="O28" s="8"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="2"/>
-      <c r="R28" s="37"/>
+      <c r="R28" s="39"/>
       <c r="S28" s="16"/>
       <c r="T28" s="8"/>
       <c r="U28" s="9"/>
@@ -7642,7 +7675,7 @@
       <c r="AB28" s="16"/>
       <c r="AC28" s="8"/>
       <c r="AD28" s="9"/>
-      <c r="AF28" s="37"/>
+      <c r="AF28" s="39"/>
       <c r="AG28" s="16"/>
       <c r="AH28" s="8"/>
       <c r="AI28" s="9"/>
@@ -7657,7 +7690,7 @@
       <c r="AR28" s="9"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="D29" s="37"/>
+      <c r="D29" s="39"/>
       <c r="E29" s="18"/>
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
@@ -7671,7 +7704,7 @@
       <c r="O29" s="8"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="2"/>
-      <c r="R29" s="37"/>
+      <c r="R29" s="39"/>
       <c r="S29" s="18"/>
       <c r="T29" s="8"/>
       <c r="U29" s="9"/>
@@ -7684,7 +7717,7 @@
       <c r="AB29" s="18"/>
       <c r="AC29" s="8"/>
       <c r="AD29" s="9"/>
-      <c r="AF29" s="37"/>
+      <c r="AF29" s="39"/>
       <c r="AG29" s="18"/>
       <c r="AH29" s="8"/>
       <c r="AI29" s="9"/>
@@ -7699,7 +7732,7 @@
       <c r="AR29" s="9"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="D30" s="37"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="16"/>
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
@@ -7713,7 +7746,7 @@
       <c r="O30" s="8"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="2"/>
-      <c r="R30" s="37"/>
+      <c r="R30" s="39"/>
       <c r="S30" s="16"/>
       <c r="T30" s="8"/>
       <c r="U30" s="9"/>
@@ -7726,7 +7759,7 @@
       <c r="AB30" s="16"/>
       <c r="AC30" s="8"/>
       <c r="AD30" s="9"/>
-      <c r="AF30" s="37"/>
+      <c r="AF30" s="39"/>
       <c r="AG30" s="16"/>
       <c r="AH30" s="8"/>
       <c r="AI30" s="9"/>
@@ -7741,7 +7774,7 @@
       <c r="AR30" s="9"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="D31" s="37"/>
+      <c r="D31" s="39"/>
       <c r="E31" s="18"/>
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
@@ -7755,7 +7788,7 @@
       <c r="O31" s="8"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="2"/>
-      <c r="R31" s="37"/>
+      <c r="R31" s="39"/>
       <c r="S31" s="18"/>
       <c r="T31" s="8"/>
       <c r="U31" s="9"/>
@@ -7768,7 +7801,7 @@
       <c r="AB31" s="18"/>
       <c r="AC31" s="8"/>
       <c r="AD31" s="9"/>
-      <c r="AF31" s="37"/>
+      <c r="AF31" s="39"/>
       <c r="AG31" s="18"/>
       <c r="AH31" s="8"/>
       <c r="AI31" s="9"/>
@@ -7783,7 +7816,7 @@
       <c r="AR31" s="9"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="D32" s="37"/>
+      <c r="D32" s="39"/>
       <c r="E32" s="16"/>
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
@@ -7797,7 +7830,7 @@
       <c r="O32" s="8"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="2"/>
-      <c r="R32" s="37"/>
+      <c r="R32" s="39"/>
       <c r="S32" s="16"/>
       <c r="T32" s="8"/>
       <c r="U32" s="9"/>
@@ -7810,7 +7843,7 @@
       <c r="AB32" s="16"/>
       <c r="AC32" s="8"/>
       <c r="AD32" s="9"/>
-      <c r="AF32" s="37"/>
+      <c r="AF32" s="39"/>
       <c r="AG32" s="16"/>
       <c r="AH32" s="8"/>
       <c r="AI32" s="9"/>
@@ -7825,7 +7858,7 @@
       <c r="AR32" s="9"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="D33" s="37"/>
+      <c r="D33" s="39"/>
       <c r="E33" s="18"/>
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
@@ -7839,7 +7872,7 @@
       <c r="O33" s="8"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="2"/>
-      <c r="R33" s="37"/>
+      <c r="R33" s="39"/>
       <c r="S33" s="18"/>
       <c r="T33" s="8"/>
       <c r="U33" s="9"/>
@@ -7852,7 +7885,7 @@
       <c r="AB33" s="18"/>
       <c r="AC33" s="8"/>
       <c r="AD33" s="9"/>
-      <c r="AF33" s="37"/>
+      <c r="AF33" s="39"/>
       <c r="AG33" s="18"/>
       <c r="AH33" s="8"/>
       <c r="AI33" s="9"/>
@@ -7867,7 +7900,7 @@
       <c r="AR33" s="9"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="D34" s="37"/>
+      <c r="D34" s="39"/>
       <c r="E34" s="16"/>
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
@@ -7881,7 +7914,7 @@
       <c r="O34" s="8"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="2"/>
-      <c r="R34" s="37"/>
+      <c r="R34" s="39"/>
       <c r="S34" s="16"/>
       <c r="T34" s="8"/>
       <c r="U34" s="9"/>
@@ -7894,7 +7927,7 @@
       <c r="AB34" s="16"/>
       <c r="AC34" s="8"/>
       <c r="AD34" s="9"/>
-      <c r="AF34" s="37"/>
+      <c r="AF34" s="39"/>
       <c r="AG34" s="16"/>
       <c r="AH34" s="8"/>
       <c r="AI34" s="9"/>
@@ -7909,7 +7942,7 @@
       <c r="AR34" s="9"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="D35" s="37"/>
+      <c r="D35" s="39"/>
       <c r="E35" s="18"/>
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
@@ -7923,7 +7956,7 @@
       <c r="O35" s="8"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="2"/>
-      <c r="R35" s="37"/>
+      <c r="R35" s="39"/>
       <c r="S35" s="18"/>
       <c r="T35" s="8"/>
       <c r="U35" s="9"/>
@@ -7936,7 +7969,7 @@
       <c r="AB35" s="18"/>
       <c r="AC35" s="8"/>
       <c r="AD35" s="9"/>
-      <c r="AF35" s="37"/>
+      <c r="AF35" s="39"/>
       <c r="AG35" s="18"/>
       <c r="AH35" s="8"/>
       <c r="AI35" s="9"/>
@@ -7951,7 +7984,7 @@
       <c r="AR35" s="9"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="D36" s="37"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="16"/>
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
@@ -7965,7 +7998,7 @@
       <c r="O36" s="8"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="2"/>
-      <c r="R36" s="37"/>
+      <c r="R36" s="39"/>
       <c r="S36" s="16"/>
       <c r="T36" s="8"/>
       <c r="U36" s="9"/>
@@ -7978,7 +8011,7 @@
       <c r="AB36" s="16"/>
       <c r="AC36" s="8"/>
       <c r="AD36" s="9"/>
-      <c r="AF36" s="37"/>
+      <c r="AF36" s="39"/>
       <c r="AG36" s="16"/>
       <c r="AH36" s="8"/>
       <c r="AI36" s="9"/>
@@ -7993,7 +8026,7 @@
       <c r="AR36" s="9"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="D37" s="37"/>
+      <c r="D37" s="39"/>
       <c r="E37" s="18"/>
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
@@ -8007,7 +8040,7 @@
       <c r="O37" s="8"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="2"/>
-      <c r="R37" s="37"/>
+      <c r="R37" s="39"/>
       <c r="S37" s="18"/>
       <c r="T37" s="8"/>
       <c r="U37" s="9"/>
@@ -8020,7 +8053,7 @@
       <c r="AB37" s="18"/>
       <c r="AC37" s="8"/>
       <c r="AD37" s="9"/>
-      <c r="AF37" s="37"/>
+      <c r="AF37" s="39"/>
       <c r="AG37" s="18"/>
       <c r="AH37" s="8"/>
       <c r="AI37" s="9"/>
@@ -8035,7 +8068,7 @@
       <c r="AR37" s="9"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="D38" s="37"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="16"/>
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
@@ -8049,7 +8082,7 @@
       <c r="O38" s="8"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="2"/>
-      <c r="R38" s="37"/>
+      <c r="R38" s="39"/>
       <c r="S38" s="16"/>
       <c r="T38" s="8"/>
       <c r="U38" s="9"/>
@@ -8062,7 +8095,7 @@
       <c r="AB38" s="16"/>
       <c r="AC38" s="8"/>
       <c r="AD38" s="9"/>
-      <c r="AF38" s="37"/>
+      <c r="AF38" s="39"/>
       <c r="AG38" s="16"/>
       <c r="AH38" s="8"/>
       <c r="AI38" s="9"/>
@@ -8077,7 +8110,7 @@
       <c r="AR38" s="9"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="D39" s="37"/>
+      <c r="D39" s="39"/>
       <c r="E39" s="18"/>
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
@@ -8091,7 +8124,7 @@
       <c r="O39" s="8"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="2"/>
-      <c r="R39" s="37"/>
+      <c r="R39" s="39"/>
       <c r="S39" s="18"/>
       <c r="T39" s="8"/>
       <c r="U39" s="9"/>
@@ -8104,7 +8137,7 @@
       <c r="AB39" s="18"/>
       <c r="AC39" s="8"/>
       <c r="AD39" s="9"/>
-      <c r="AF39" s="37"/>
+      <c r="AF39" s="39"/>
       <c r="AG39" s="18"/>
       <c r="AH39" s="8"/>
       <c r="AI39" s="9"/>
@@ -8119,7 +8152,7 @@
       <c r="AR39" s="9"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="D40" s="37"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="16"/>
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
@@ -8133,7 +8166,7 @@
       <c r="O40" s="8"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="2"/>
-      <c r="R40" s="37"/>
+      <c r="R40" s="39"/>
       <c r="S40" s="16"/>
       <c r="T40" s="8"/>
       <c r="U40" s="9"/>
@@ -8146,7 +8179,7 @@
       <c r="AB40" s="16"/>
       <c r="AC40" s="8"/>
       <c r="AD40" s="9"/>
-      <c r="AF40" s="37"/>
+      <c r="AF40" s="39"/>
       <c r="AG40" s="16"/>
       <c r="AH40" s="8"/>
       <c r="AI40" s="9"/>
@@ -8161,7 +8194,7 @@
       <c r="AR40" s="9"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="D41" s="37"/>
+      <c r="D41" s="39"/>
       <c r="E41" s="18"/>
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
@@ -8175,7 +8208,7 @@
       <c r="O41" s="8"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="2"/>
-      <c r="R41" s="37"/>
+      <c r="R41" s="39"/>
       <c r="S41" s="18"/>
       <c r="T41" s="8"/>
       <c r="U41" s="9"/>
@@ -8188,7 +8221,7 @@
       <c r="AB41" s="18"/>
       <c r="AC41" s="8"/>
       <c r="AD41" s="9"/>
-      <c r="AF41" s="37"/>
+      <c r="AF41" s="39"/>
       <c r="AG41" s="18"/>
       <c r="AH41" s="8"/>
       <c r="AI41" s="9"/>
@@ -8203,7 +8236,7 @@
       <c r="AR41" s="9"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="D42" s="37"/>
+      <c r="D42" s="39"/>
       <c r="E42" s="16"/>
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
@@ -8216,7 +8249,7 @@
       <c r="N42" s="16"/>
       <c r="O42" s="8"/>
       <c r="P42" s="9"/>
-      <c r="R42" s="37"/>
+      <c r="R42" s="39"/>
       <c r="S42" s="16"/>
       <c r="T42" s="8"/>
       <c r="U42" s="9"/>
@@ -8229,7 +8262,7 @@
       <c r="AB42" s="16"/>
       <c r="AC42" s="8"/>
       <c r="AD42" s="9"/>
-      <c r="AF42" s="37"/>
+      <c r="AF42" s="39"/>
       <c r="AG42" s="16"/>
       <c r="AH42" s="8"/>
       <c r="AI42" s="9"/>
@@ -8244,7 +8277,7 @@
       <c r="AR42" s="9"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="D43" s="37"/>
+      <c r="D43" s="39"/>
       <c r="E43" s="18"/>
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
@@ -8257,7 +8290,7 @@
       <c r="N43" s="18"/>
       <c r="O43" s="8"/>
       <c r="P43" s="9"/>
-      <c r="R43" s="37"/>
+      <c r="R43" s="39"/>
       <c r="S43" s="18"/>
       <c r="T43" s="8"/>
       <c r="U43" s="9"/>
@@ -8270,7 +8303,7 @@
       <c r="AB43" s="18"/>
       <c r="AC43" s="8"/>
       <c r="AD43" s="9"/>
-      <c r="AF43" s="37"/>
+      <c r="AF43" s="39"/>
       <c r="AG43" s="18"/>
       <c r="AH43" s="8"/>
       <c r="AI43" s="9"/>
@@ -8285,7 +8318,7 @@
       <c r="AR43" s="9"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="D44" s="37"/>
+      <c r="D44" s="39"/>
       <c r="E44" s="16"/>
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
@@ -8298,7 +8331,7 @@
       <c r="N44" s="16"/>
       <c r="O44" s="8"/>
       <c r="P44" s="9"/>
-      <c r="R44" s="37"/>
+      <c r="R44" s="39"/>
       <c r="S44" s="16"/>
       <c r="T44" s="8"/>
       <c r="U44" s="9"/>
@@ -8311,7 +8344,7 @@
       <c r="AB44" s="16"/>
       <c r="AC44" s="8"/>
       <c r="AD44" s="9"/>
-      <c r="AF44" s="37"/>
+      <c r="AF44" s="39"/>
       <c r="AG44" s="16"/>
       <c r="AH44" s="8"/>
       <c r="AI44" s="9"/>
@@ -8326,7 +8359,7 @@
       <c r="AR44" s="9"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="D45" s="37"/>
+      <c r="D45" s="39"/>
       <c r="E45" s="18"/>
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
@@ -8339,7 +8372,7 @@
       <c r="N45" s="18"/>
       <c r="O45" s="8"/>
       <c r="P45" s="9"/>
-      <c r="R45" s="37"/>
+      <c r="R45" s="39"/>
       <c r="S45" s="18"/>
       <c r="T45" s="8"/>
       <c r="U45" s="9"/>
@@ -8352,7 +8385,7 @@
       <c r="AB45" s="18"/>
       <c r="AC45" s="8"/>
       <c r="AD45" s="9"/>
-      <c r="AF45" s="37"/>
+      <c r="AF45" s="39"/>
       <c r="AG45" s="18"/>
       <c r="AH45" s="8"/>
       <c r="AI45" s="9"/>
@@ -8367,7 +8400,7 @@
       <c r="AR45" s="9"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="D46" s="37"/>
+      <c r="D46" s="39"/>
       <c r="E46" s="16"/>
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
@@ -8380,7 +8413,7 @@
       <c r="N46" s="16"/>
       <c r="O46" s="8"/>
       <c r="P46" s="9"/>
-      <c r="R46" s="37"/>
+      <c r="R46" s="39"/>
       <c r="S46" s="16"/>
       <c r="T46" s="8"/>
       <c r="U46" s="9"/>
@@ -8393,7 +8426,7 @@
       <c r="AB46" s="16"/>
       <c r="AC46" s="8"/>
       <c r="AD46" s="9"/>
-      <c r="AF46" s="37"/>
+      <c r="AF46" s="39"/>
       <c r="AG46" s="16"/>
       <c r="AH46" s="8"/>
       <c r="AI46" s="9"/>
@@ -8408,7 +8441,7 @@
       <c r="AR46" s="9"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="D47" s="37"/>
+      <c r="D47" s="39"/>
       <c r="E47" s="18"/>
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
@@ -8421,7 +8454,7 @@
       <c r="N47" s="18"/>
       <c r="O47" s="8"/>
       <c r="P47" s="9"/>
-      <c r="R47" s="37"/>
+      <c r="R47" s="39"/>
       <c r="S47" s="18"/>
       <c r="T47" s="8"/>
       <c r="U47" s="9"/>
@@ -8434,7 +8467,7 @@
       <c r="AB47" s="18"/>
       <c r="AC47" s="8"/>
       <c r="AD47" s="9"/>
-      <c r="AF47" s="37"/>
+      <c r="AF47" s="39"/>
       <c r="AG47" s="18"/>
       <c r="AH47" s="8"/>
       <c r="AI47" s="9"/>
@@ -8449,7 +8482,7 @@
       <c r="AR47" s="9"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="D48" s="37"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="21"/>
       <c r="F48" s="22"/>
       <c r="G48" s="23"/>
@@ -8462,7 +8495,7 @@
       <c r="N48" s="16"/>
       <c r="O48" s="8"/>
       <c r="P48" s="9"/>
-      <c r="R48" s="37"/>
+      <c r="R48" s="39"/>
       <c r="S48" s="16"/>
       <c r="T48" s="8"/>
       <c r="U48" s="9"/>
@@ -8475,7 +8508,7 @@
       <c r="AB48" s="16"/>
       <c r="AC48" s="8"/>
       <c r="AD48" s="9"/>
-      <c r="AF48" s="37"/>
+      <c r="AF48" s="39"/>
       <c r="AG48" s="16"/>
       <c r="AH48" s="8"/>
       <c r="AI48" s="9"/>
@@ -8490,7 +8523,7 @@
       <c r="AR48" s="9"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="D49" s="37"/>
+      <c r="D49" s="39"/>
       <c r="E49" s="25"/>
       <c r="F49" s="22"/>
       <c r="G49" s="23"/>
@@ -8503,7 +8536,7 @@
       <c r="N49" s="18"/>
       <c r="O49" s="8"/>
       <c r="P49" s="9"/>
-      <c r="R49" s="37"/>
+      <c r="R49" s="39"/>
       <c r="S49" s="18"/>
       <c r="T49" s="8"/>
       <c r="U49" s="9"/>
@@ -8516,7 +8549,7 @@
       <c r="AB49" s="18"/>
       <c r="AC49" s="8"/>
       <c r="AD49" s="9"/>
-      <c r="AF49" s="37"/>
+      <c r="AF49" s="39"/>
       <c r="AG49" s="18"/>
       <c r="AH49" s="8"/>
       <c r="AI49" s="9"/>
@@ -8531,7 +8564,7 @@
       <c r="AR49" s="9"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="D50" s="37"/>
+      <c r="D50" s="39"/>
       <c r="E50" s="21"/>
       <c r="F50" s="22"/>
       <c r="G50" s="23"/>
@@ -8544,7 +8577,7 @@
       <c r="N50" s="16"/>
       <c r="O50" s="8"/>
       <c r="P50" s="9"/>
-      <c r="R50" s="37"/>
+      <c r="R50" s="39"/>
       <c r="S50" s="16"/>
       <c r="T50" s="8"/>
       <c r="U50" s="9"/>
@@ -8557,7 +8590,7 @@
       <c r="AB50" s="16"/>
       <c r="AC50" s="8"/>
       <c r="AD50" s="9"/>
-      <c r="AF50" s="37"/>
+      <c r="AF50" s="39"/>
       <c r="AG50" s="16"/>
       <c r="AH50" s="8"/>
       <c r="AI50" s="9"/>
@@ -8572,7 +8605,7 @@
       <c r="AR50" s="9"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="D51" s="37"/>
+      <c r="D51" s="39"/>
       <c r="E51" s="18"/>
       <c r="F51" s="8"/>
       <c r="G51" s="9"/>
@@ -8585,7 +8618,7 @@
       <c r="N51" s="18"/>
       <c r="O51" s="8"/>
       <c r="P51" s="9"/>
-      <c r="R51" s="37"/>
+      <c r="R51" s="39"/>
       <c r="S51" s="18"/>
       <c r="T51" s="8"/>
       <c r="U51" s="9"/>
@@ -8598,7 +8631,7 @@
       <c r="AB51" s="18"/>
       <c r="AC51" s="8"/>
       <c r="AD51" s="9"/>
-      <c r="AF51" s="37"/>
+      <c r="AF51" s="39"/>
       <c r="AG51" s="18"/>
       <c r="AH51" s="8"/>
       <c r="AI51" s="9"/>
@@ -8613,7 +8646,7 @@
       <c r="AR51" s="9"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="D52" s="37"/>
+      <c r="D52" s="39"/>
       <c r="E52" s="16"/>
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
@@ -8626,7 +8659,7 @@
       <c r="N52" s="16"/>
       <c r="O52" s="8"/>
       <c r="P52" s="9"/>
-      <c r="R52" s="37"/>
+      <c r="R52" s="39"/>
       <c r="S52" s="16"/>
       <c r="T52" s="8"/>
       <c r="U52" s="9"/>
@@ -8639,7 +8672,7 @@
       <c r="AB52" s="16"/>
       <c r="AC52" s="8"/>
       <c r="AD52" s="9"/>
-      <c r="AF52" s="37"/>
+      <c r="AF52" s="39"/>
       <c r="AG52" s="16"/>
       <c r="AH52" s="8"/>
       <c r="AI52" s="9"/>
@@ -8654,7 +8687,7 @@
       <c r="AR52" s="9"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="D53" s="37"/>
+      <c r="D53" s="39"/>
       <c r="E53" s="18"/>
       <c r="F53" s="8"/>
       <c r="G53" s="9"/>
@@ -8667,7 +8700,7 @@
       <c r="N53" s="18"/>
       <c r="O53" s="8"/>
       <c r="P53" s="9"/>
-      <c r="R53" s="37"/>
+      <c r="R53" s="39"/>
       <c r="S53" s="18"/>
       <c r="T53" s="8"/>
       <c r="U53" s="9"/>
@@ -8680,7 +8713,7 @@
       <c r="AB53" s="18"/>
       <c r="AC53" s="8"/>
       <c r="AD53" s="9"/>
-      <c r="AF53" s="37"/>
+      <c r="AF53" s="39"/>
       <c r="AG53" s="18"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="9"/>
@@ -8695,7 +8728,7 @@
       <c r="AR53" s="9"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="D54" s="37"/>
+      <c r="D54" s="39"/>
       <c r="E54" s="16"/>
       <c r="F54" s="8"/>
       <c r="G54" s="9"/>
@@ -8708,7 +8741,7 @@
       <c r="N54" s="16"/>
       <c r="O54" s="8"/>
       <c r="P54" s="9"/>
-      <c r="R54" s="37"/>
+      <c r="R54" s="39"/>
       <c r="S54" s="16"/>
       <c r="T54" s="8"/>
       <c r="U54" s="9"/>
@@ -8721,7 +8754,7 @@
       <c r="AB54" s="16"/>
       <c r="AC54" s="8"/>
       <c r="AD54" s="9"/>
-      <c r="AF54" s="37"/>
+      <c r="AF54" s="39"/>
       <c r="AG54" s="16"/>
       <c r="AH54" s="8"/>
       <c r="AI54" s="9"/>
@@ -8736,7 +8769,7 @@
       <c r="AR54" s="9"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="D55" s="37"/>
+      <c r="D55" s="39"/>
       <c r="E55" s="18"/>
       <c r="F55" s="8"/>
       <c r="G55" s="9"/>
@@ -8749,7 +8782,7 @@
       <c r="N55" s="18"/>
       <c r="O55" s="8"/>
       <c r="P55" s="9"/>
-      <c r="R55" s="37"/>
+      <c r="R55" s="39"/>
       <c r="S55" s="18"/>
       <c r="T55" s="8"/>
       <c r="U55" s="9"/>
@@ -8762,7 +8795,7 @@
       <c r="AB55" s="18"/>
       <c r="AC55" s="8"/>
       <c r="AD55" s="9"/>
-      <c r="AF55" s="37"/>
+      <c r="AF55" s="39"/>
       <c r="AG55" s="18"/>
       <c r="AH55" s="8"/>
       <c r="AI55" s="9"/>
@@ -8777,7 +8810,7 @@
       <c r="AR55" s="9"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="D56" s="37"/>
+      <c r="D56" s="39"/>
       <c r="E56" s="16"/>
       <c r="F56" s="8"/>
       <c r="G56" s="9"/>
@@ -8790,7 +8823,7 @@
       <c r="N56" s="16"/>
       <c r="O56" s="8"/>
       <c r="P56" s="9"/>
-      <c r="R56" s="37"/>
+      <c r="R56" s="39"/>
       <c r="S56" s="16"/>
       <c r="T56" s="8"/>
       <c r="U56" s="9"/>
@@ -8803,7 +8836,7 @@
       <c r="AB56" s="16"/>
       <c r="AC56" s="8"/>
       <c r="AD56" s="9"/>
-      <c r="AF56" s="37"/>
+      <c r="AF56" s="39"/>
       <c r="AG56" s="16"/>
       <c r="AH56" s="8"/>
       <c r="AI56" s="9"/>
@@ -8818,7 +8851,7 @@
       <c r="AR56" s="9"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="D57" s="37"/>
+      <c r="D57" s="39"/>
       <c r="E57" s="18"/>
       <c r="F57" s="8"/>
       <c r="G57" s="9"/>
@@ -8831,7 +8864,7 @@
       <c r="N57" s="18"/>
       <c r="O57" s="8"/>
       <c r="P57" s="9"/>
-      <c r="R57" s="37"/>
+      <c r="R57" s="39"/>
       <c r="S57" s="18"/>
       <c r="T57" s="8"/>
       <c r="U57" s="9"/>
@@ -8844,7 +8877,7 @@
       <c r="AB57" s="18"/>
       <c r="AC57" s="8"/>
       <c r="AD57" s="9"/>
-      <c r="AF57" s="37"/>
+      <c r="AF57" s="39"/>
       <c r="AG57" s="18"/>
       <c r="AH57" s="8"/>
       <c r="AI57" s="9"/>
@@ -8859,7 +8892,7 @@
       <c r="AR57" s="9"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="D58" s="37"/>
+      <c r="D58" s="39"/>
       <c r="E58" s="21"/>
       <c r="F58" s="22"/>
       <c r="G58" s="23"/>
@@ -8872,7 +8905,7 @@
       <c r="N58" s="16"/>
       <c r="O58" s="8"/>
       <c r="P58" s="9"/>
-      <c r="R58" s="37"/>
+      <c r="R58" s="39"/>
       <c r="S58" s="16"/>
       <c r="T58" s="8"/>
       <c r="U58" s="9"/>
@@ -8885,7 +8918,7 @@
       <c r="AB58" s="16"/>
       <c r="AC58" s="8"/>
       <c r="AD58" s="9"/>
-      <c r="AF58" s="37"/>
+      <c r="AF58" s="39"/>
       <c r="AG58" s="16"/>
       <c r="AH58" s="8"/>
       <c r="AI58" s="9"/>
@@ -8900,20 +8933,20 @@
       <c r="AR58" s="9"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="D59" s="37"/>
+      <c r="D59" s="39"/>
       <c r="E59" s="25"/>
       <c r="F59" s="22"/>
       <c r="G59" s="23"/>
-      <c r="H59" s="31"/>
+      <c r="H59" s="33"/>
       <c r="I59" s="22"/>
       <c r="J59" s="23"/>
-      <c r="K59" s="31"/>
+      <c r="K59" s="33"/>
       <c r="L59" s="22"/>
       <c r="M59" s="23"/>
       <c r="N59" s="18"/>
       <c r="O59" s="8"/>
       <c r="P59" s="9"/>
-      <c r="R59" s="37"/>
+      <c r="R59" s="39"/>
       <c r="S59" s="18"/>
       <c r="T59" s="8"/>
       <c r="U59" s="9"/>
@@ -8926,7 +8959,7 @@
       <c r="AB59" s="18"/>
       <c r="AC59" s="8"/>
       <c r="AD59" s="9"/>
-      <c r="AF59" s="37"/>
+      <c r="AF59" s="39"/>
       <c r="AG59" s="18"/>
       <c r="AH59" s="8"/>
       <c r="AI59" s="9"/>
@@ -8941,7 +8974,7 @@
       <c r="AR59" s="9"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="D60" s="37"/>
+      <c r="D60" s="39"/>
       <c r="E60" s="21"/>
       <c r="F60" s="22"/>
       <c r="G60" s="23"/>
@@ -8954,7 +8987,7 @@
       <c r="N60" s="16"/>
       <c r="O60" s="8"/>
       <c r="P60" s="9"/>
-      <c r="R60" s="37"/>
+      <c r="R60" s="39"/>
       <c r="S60" s="16"/>
       <c r="T60" s="8"/>
       <c r="U60" s="9"/>
@@ -8967,7 +9000,7 @@
       <c r="AB60" s="16"/>
       <c r="AC60" s="8"/>
       <c r="AD60" s="9"/>
-      <c r="AF60" s="37"/>
+      <c r="AF60" s="39"/>
       <c r="AG60" s="16"/>
       <c r="AH60" s="8"/>
       <c r="AI60" s="9"/>
@@ -8982,20 +9015,20 @@
       <c r="AR60" s="9"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="D61" s="37"/>
+      <c r="D61" s="39"/>
       <c r="E61" s="25"/>
       <c r="F61" s="22"/>
       <c r="G61" s="23"/>
-      <c r="H61" s="31"/>
+      <c r="H61" s="33"/>
       <c r="I61" s="22"/>
       <c r="J61" s="23"/>
-      <c r="K61" s="31"/>
+      <c r="K61" s="33"/>
       <c r="L61" s="22"/>
       <c r="M61" s="23"/>
       <c r="N61" s="18"/>
       <c r="O61" s="8"/>
       <c r="P61" s="9"/>
-      <c r="R61" s="37"/>
+      <c r="R61" s="39"/>
       <c r="S61" s="18"/>
       <c r="T61" s="8"/>
       <c r="U61" s="9"/>
@@ -9008,7 +9041,7 @@
       <c r="AB61" s="18"/>
       <c r="AC61" s="8"/>
       <c r="AD61" s="9"/>
-      <c r="AF61" s="37"/>
+      <c r="AF61" s="39"/>
       <c r="AG61" s="18"/>
       <c r="AH61" s="8"/>
       <c r="AI61" s="9"/>
@@ -9023,7 +9056,7 @@
       <c r="AR61" s="9"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="D62" s="37"/>
+      <c r="D62" s="39"/>
       <c r="E62" s="21"/>
       <c r="F62" s="22"/>
       <c r="G62" s="23"/>
@@ -9036,7 +9069,7 @@
       <c r="N62" s="16"/>
       <c r="O62" s="8"/>
       <c r="P62" s="9"/>
-      <c r="R62" s="37"/>
+      <c r="R62" s="39"/>
       <c r="S62" s="16"/>
       <c r="T62" s="8"/>
       <c r="U62" s="9"/>
@@ -9049,7 +9082,7 @@
       <c r="AB62" s="16"/>
       <c r="AC62" s="8"/>
       <c r="AD62" s="9"/>
-      <c r="AF62" s="37"/>
+      <c r="AF62" s="39"/>
       <c r="AG62" s="16"/>
       <c r="AH62" s="8"/>
       <c r="AI62" s="9"/>
@@ -9064,20 +9097,20 @@
       <c r="AR62" s="9"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="D63" s="37"/>
+      <c r="D63" s="39"/>
       <c r="E63" s="25"/>
       <c r="F63" s="22"/>
       <c r="G63" s="23"/>
-      <c r="H63" s="31"/>
+      <c r="H63" s="33"/>
       <c r="I63" s="22"/>
       <c r="J63" s="23"/>
-      <c r="K63" s="31"/>
+      <c r="K63" s="33"/>
       <c r="L63" s="22"/>
       <c r="M63" s="23"/>
       <c r="N63" s="18"/>
       <c r="O63" s="8"/>
       <c r="P63" s="9"/>
-      <c r="R63" s="37"/>
+      <c r="R63" s="39"/>
       <c r="S63" s="18"/>
       <c r="T63" s="8"/>
       <c r="U63" s="9"/>
@@ -9090,7 +9123,7 @@
       <c r="AB63" s="18"/>
       <c r="AC63" s="8"/>
       <c r="AD63" s="9"/>
-      <c r="AF63" s="37"/>
+      <c r="AF63" s="39"/>
       <c r="AG63" s="18"/>
       <c r="AH63" s="8"/>
       <c r="AI63" s="9"/>
@@ -9105,7 +9138,7 @@
       <c r="AR63" s="9"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="D64" s="37"/>
+      <c r="D64" s="39"/>
       <c r="E64" s="16"/>
       <c r="F64" s="8"/>
       <c r="G64" s="9"/>
@@ -9118,7 +9151,7 @@
       <c r="N64" s="16"/>
       <c r="O64" s="8"/>
       <c r="P64" s="9"/>
-      <c r="R64" s="37"/>
+      <c r="R64" s="39"/>
       <c r="S64" s="16"/>
       <c r="T64" s="8"/>
       <c r="U64" s="9"/>
@@ -9131,7 +9164,7 @@
       <c r="AB64" s="16"/>
       <c r="AC64" s="8"/>
       <c r="AD64" s="9"/>
-      <c r="AF64" s="37"/>
+      <c r="AF64" s="39"/>
       <c r="AG64" s="16"/>
       <c r="AH64" s="8"/>
       <c r="AI64" s="9"/>
@@ -9146,7 +9179,7 @@
       <c r="AR64" s="9"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="D65" s="37"/>
+      <c r="D65" s="39"/>
       <c r="E65" s="18"/>
       <c r="F65" s="8"/>
       <c r="G65" s="9"/>
@@ -9159,7 +9192,7 @@
       <c r="N65" s="18"/>
       <c r="O65" s="8"/>
       <c r="P65" s="9"/>
-      <c r="R65" s="37"/>
+      <c r="R65" s="39"/>
       <c r="S65" s="18"/>
       <c r="T65" s="8"/>
       <c r="U65" s="9"/>
@@ -9172,7 +9205,7 @@
       <c r="AB65" s="18"/>
       <c r="AC65" s="8"/>
       <c r="AD65" s="9"/>
-      <c r="AF65" s="37"/>
+      <c r="AF65" s="39"/>
       <c r="AG65" s="18"/>
       <c r="AH65" s="8"/>
       <c r="AI65" s="9"/>
@@ -9187,7 +9220,7 @@
       <c r="AR65" s="9"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="D66" s="37"/>
+      <c r="D66" s="39"/>
       <c r="E66" s="16"/>
       <c r="F66" s="8"/>
       <c r="G66" s="9"/>
@@ -9200,7 +9233,7 @@
       <c r="N66" s="16"/>
       <c r="O66" s="8"/>
       <c r="P66" s="9"/>
-      <c r="R66" s="37"/>
+      <c r="R66" s="39"/>
       <c r="S66" s="16"/>
       <c r="T66" s="8"/>
       <c r="U66" s="9"/>
@@ -9213,7 +9246,7 @@
       <c r="AB66" s="16"/>
       <c r="AC66" s="8"/>
       <c r="AD66" s="9"/>
-      <c r="AF66" s="37"/>
+      <c r="AF66" s="39"/>
       <c r="AG66" s="16"/>
       <c r="AH66" s="8"/>
       <c r="AI66" s="9"/>
@@ -9228,7 +9261,7 @@
       <c r="AR66" s="9"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="D67" s="37"/>
+      <c r="D67" s="39"/>
       <c r="E67" s="18"/>
       <c r="F67" s="8"/>
       <c r="G67" s="9"/>
@@ -9241,7 +9274,7 @@
       <c r="N67" s="18"/>
       <c r="O67" s="8"/>
       <c r="P67" s="9"/>
-      <c r="R67" s="37"/>
+      <c r="R67" s="39"/>
       <c r="S67" s="18"/>
       <c r="T67" s="8"/>
       <c r="U67" s="9"/>
@@ -9254,7 +9287,7 @@
       <c r="AB67" s="18"/>
       <c r="AC67" s="8"/>
       <c r="AD67" s="9"/>
-      <c r="AF67" s="37"/>
+      <c r="AF67" s="39"/>
       <c r="AG67" s="18"/>
       <c r="AH67" s="8"/>
       <c r="AI67" s="9"/>
@@ -9269,7 +9302,7 @@
       <c r="AR67" s="9"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="D68" s="37"/>
+      <c r="D68" s="39"/>
       <c r="E68" s="16"/>
       <c r="F68" s="8"/>
       <c r="G68" s="9"/>
@@ -9282,7 +9315,7 @@
       <c r="N68" s="16"/>
       <c r="O68" s="8"/>
       <c r="P68" s="9"/>
-      <c r="R68" s="37"/>
+      <c r="R68" s="39"/>
       <c r="S68" s="16"/>
       <c r="T68" s="8"/>
       <c r="U68" s="9"/>
@@ -9295,7 +9328,7 @@
       <c r="AB68" s="16"/>
       <c r="AC68" s="8"/>
       <c r="AD68" s="9"/>
-      <c r="AF68" s="37"/>
+      <c r="AF68" s="39"/>
       <c r="AG68" s="16"/>
       <c r="AH68" s="8"/>
       <c r="AI68" s="9"/>
@@ -9310,7 +9343,7 @@
       <c r="AR68" s="9"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="D69" s="37"/>
+      <c r="D69" s="39"/>
       <c r="E69" s="18"/>
       <c r="F69" s="8"/>
       <c r="G69" s="9"/>
@@ -9323,7 +9356,7 @@
       <c r="N69" s="18"/>
       <c r="O69" s="8"/>
       <c r="P69" s="9"/>
-      <c r="R69" s="37"/>
+      <c r="R69" s="39"/>
       <c r="S69" s="18"/>
       <c r="T69" s="8"/>
       <c r="U69" s="9"/>
@@ -9336,7 +9369,7 @@
       <c r="AB69" s="18"/>
       <c r="AC69" s="8"/>
       <c r="AD69" s="9"/>
-      <c r="AF69" s="37"/>
+      <c r="AF69" s="39"/>
       <c r="AG69" s="18"/>
       <c r="AH69" s="8"/>
       <c r="AI69" s="9"/>
@@ -9351,7 +9384,7 @@
       <c r="AR69" s="9"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="D70" s="37"/>
+      <c r="D70" s="39"/>
       <c r="E70" s="16"/>
       <c r="F70" s="8"/>
       <c r="G70" s="9"/>
@@ -9364,7 +9397,7 @@
       <c r="N70" s="16"/>
       <c r="O70" s="8"/>
       <c r="P70" s="9"/>
-      <c r="R70" s="37"/>
+      <c r="R70" s="39"/>
       <c r="S70" s="16"/>
       <c r="T70" s="8"/>
       <c r="U70" s="9"/>
@@ -9377,7 +9410,7 @@
       <c r="AB70" s="16"/>
       <c r="AC70" s="8"/>
       <c r="AD70" s="9"/>
-      <c r="AF70" s="37"/>
+      <c r="AF70" s="39"/>
       <c r="AG70" s="16"/>
       <c r="AH70" s="8"/>
       <c r="AI70" s="9"/>
@@ -9392,20 +9425,20 @@
       <c r="AR70" s="9"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="D71" s="37"/>
+      <c r="D71" s="39"/>
       <c r="E71" s="25"/>
       <c r="F71" s="22"/>
       <c r="G71" s="23"/>
-      <c r="H71" s="31"/>
+      <c r="H71" s="33"/>
       <c r="I71" s="22"/>
       <c r="J71" s="23"/>
-      <c r="K71" s="31"/>
+      <c r="K71" s="33"/>
       <c r="L71" s="22"/>
       <c r="M71" s="23"/>
       <c r="N71" s="18"/>
       <c r="O71" s="8"/>
       <c r="P71" s="9"/>
-      <c r="R71" s="37"/>
+      <c r="R71" s="39"/>
       <c r="S71" s="18"/>
       <c r="T71" s="8"/>
       <c r="U71" s="9"/>
@@ -9418,7 +9451,7 @@
       <c r="AB71" s="18"/>
       <c r="AC71" s="8"/>
       <c r="AD71" s="9"/>
-      <c r="AF71" s="37"/>
+      <c r="AF71" s="39"/>
       <c r="AG71" s="18"/>
       <c r="AH71" s="8"/>
       <c r="AI71" s="9"/>
@@ -9433,7 +9466,7 @@
       <c r="AR71" s="9"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="D72" s="37"/>
+      <c r="D72" s="39"/>
       <c r="E72" s="21"/>
       <c r="F72" s="22"/>
       <c r="G72" s="23"/>
@@ -9446,7 +9479,7 @@
       <c r="N72" s="16"/>
       <c r="O72" s="8"/>
       <c r="P72" s="9"/>
-      <c r="R72" s="37"/>
+      <c r="R72" s="39"/>
       <c r="S72" s="16"/>
       <c r="T72" s="8"/>
       <c r="U72" s="9"/>
@@ -9459,7 +9492,7 @@
       <c r="AB72" s="16"/>
       <c r="AC72" s="8"/>
       <c r="AD72" s="9"/>
-      <c r="AF72" s="37"/>
+      <c r="AF72" s="39"/>
       <c r="AG72" s="16"/>
       <c r="AH72" s="8"/>
       <c r="AI72" s="9"/>
@@ -9474,20 +9507,20 @@
       <c r="AR72" s="9"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="D73" s="37"/>
+      <c r="D73" s="39"/>
       <c r="E73" s="25"/>
       <c r="F73" s="22"/>
       <c r="G73" s="23"/>
-      <c r="H73" s="31"/>
+      <c r="H73" s="33"/>
       <c r="I73" s="22"/>
       <c r="J73" s="23"/>
-      <c r="K73" s="31"/>
+      <c r="K73" s="33"/>
       <c r="L73" s="22"/>
       <c r="M73" s="23"/>
       <c r="N73" s="18"/>
       <c r="O73" s="8"/>
       <c r="P73" s="9"/>
-      <c r="R73" s="37"/>
+      <c r="R73" s="39"/>
       <c r="S73" s="18"/>
       <c r="T73" s="8"/>
       <c r="U73" s="9"/>
@@ -9500,7 +9533,7 @@
       <c r="AB73" s="18"/>
       <c r="AC73" s="8"/>
       <c r="AD73" s="9"/>
-      <c r="AF73" s="37"/>
+      <c r="AF73" s="39"/>
       <c r="AG73" s="18"/>
       <c r="AH73" s="8"/>
       <c r="AI73" s="9"/>
@@ -9515,7 +9548,7 @@
       <c r="AR73" s="9"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="D74" s="37"/>
+      <c r="D74" s="39"/>
       <c r="E74" s="21"/>
       <c r="F74" s="22"/>
       <c r="G74" s="23"/>
@@ -9528,7 +9561,7 @@
       <c r="N74" s="16"/>
       <c r="O74" s="8"/>
       <c r="P74" s="9"/>
-      <c r="R74" s="37"/>
+      <c r="R74" s="39"/>
       <c r="S74" s="16"/>
       <c r="T74" s="8"/>
       <c r="U74" s="9"/>
@@ -9541,7 +9574,7 @@
       <c r="AB74" s="16"/>
       <c r="AC74" s="8"/>
       <c r="AD74" s="9"/>
-      <c r="AF74" s="37"/>
+      <c r="AF74" s="39"/>
       <c r="AG74" s="16"/>
       <c r="AH74" s="8"/>
       <c r="AI74" s="9"/>
@@ -9556,20 +9589,20 @@
       <c r="AR74" s="9"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="D75" s="37"/>
+      <c r="D75" s="39"/>
       <c r="E75" s="25"/>
       <c r="F75" s="22"/>
       <c r="G75" s="23"/>
-      <c r="H75" s="31"/>
+      <c r="H75" s="33"/>
       <c r="I75" s="22"/>
       <c r="J75" s="23"/>
-      <c r="K75" s="31"/>
+      <c r="K75" s="33"/>
       <c r="L75" s="22"/>
       <c r="M75" s="23"/>
       <c r="N75" s="18"/>
       <c r="O75" s="8"/>
       <c r="P75" s="9"/>
-      <c r="R75" s="37"/>
+      <c r="R75" s="39"/>
       <c r="S75" s="18"/>
       <c r="T75" s="8"/>
       <c r="U75" s="9"/>
@@ -9582,7 +9615,7 @@
       <c r="AB75" s="18"/>
       <c r="AC75" s="8"/>
       <c r="AD75" s="9"/>
-      <c r="AF75" s="37"/>
+      <c r="AF75" s="39"/>
       <c r="AG75" s="18"/>
       <c r="AH75" s="8"/>
       <c r="AI75" s="9"/>
@@ -9597,7 +9630,7 @@
       <c r="AR75" s="9"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="D76" s="37"/>
+      <c r="D76" s="39"/>
       <c r="E76" s="21"/>
       <c r="F76" s="22"/>
       <c r="G76" s="23"/>
@@ -9610,7 +9643,7 @@
       <c r="N76" s="16"/>
       <c r="O76" s="8"/>
       <c r="P76" s="9"/>
-      <c r="R76" s="37"/>
+      <c r="R76" s="39"/>
       <c r="S76" s="16"/>
       <c r="T76" s="8"/>
       <c r="U76" s="9"/>
@@ -9623,7 +9656,7 @@
       <c r="AB76" s="16"/>
       <c r="AC76" s="8"/>
       <c r="AD76" s="9"/>
-      <c r="AF76" s="37"/>
+      <c r="AF76" s="39"/>
       <c r="AG76" s="16"/>
       <c r="AH76" s="8"/>
       <c r="AI76" s="9"/>
@@ -9638,7 +9671,7 @@
       <c r="AR76" s="9"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="D77" s="37"/>
+      <c r="D77" s="39"/>
       <c r="E77" s="25"/>
       <c r="F77" s="22"/>
       <c r="G77" s="23"/>
@@ -9651,7 +9684,7 @@
       <c r="N77" s="18"/>
       <c r="O77" s="8"/>
       <c r="P77" s="9"/>
-      <c r="R77" s="37"/>
+      <c r="R77" s="39"/>
       <c r="S77" s="18"/>
       <c r="T77" s="8"/>
       <c r="U77" s="9"/>
@@ -9664,7 +9697,7 @@
       <c r="AB77" s="18"/>
       <c r="AC77" s="8"/>
       <c r="AD77" s="9"/>
-      <c r="AF77" s="37"/>
+      <c r="AF77" s="39"/>
       <c r="AG77" s="18"/>
       <c r="AH77" s="8"/>
       <c r="AI77" s="9"/>
@@ -9679,7 +9712,7 @@
       <c r="AR77" s="9"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="D78" s="37"/>
+      <c r="D78" s="39"/>
       <c r="E78" s="21"/>
       <c r="F78" s="22"/>
       <c r="G78" s="23"/>
@@ -9692,7 +9725,7 @@
       <c r="N78" s="16"/>
       <c r="O78" s="8"/>
       <c r="P78" s="9"/>
-      <c r="R78" s="37"/>
+      <c r="R78" s="39"/>
       <c r="S78" s="16"/>
       <c r="T78" s="8"/>
       <c r="U78" s="9"/>
@@ -9705,7 +9738,7 @@
       <c r="AB78" s="16"/>
       <c r="AC78" s="8"/>
       <c r="AD78" s="9"/>
-      <c r="AF78" s="37"/>
+      <c r="AF78" s="39"/>
       <c r="AG78" s="16"/>
       <c r="AH78" s="8"/>
       <c r="AI78" s="9"/>
@@ -9720,7 +9753,7 @@
       <c r="AR78" s="9"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="D79" s="37"/>
+      <c r="D79" s="39"/>
       <c r="E79" s="25"/>
       <c r="F79" s="22"/>
       <c r="G79" s="23"/>
@@ -9733,7 +9766,7 @@
       <c r="N79" s="18"/>
       <c r="O79" s="8"/>
       <c r="P79" s="9"/>
-      <c r="R79" s="37"/>
+      <c r="R79" s="39"/>
       <c r="S79" s="18"/>
       <c r="T79" s="8"/>
       <c r="U79" s="9"/>
@@ -9746,7 +9779,7 @@
       <c r="AB79" s="18"/>
       <c r="AC79" s="8"/>
       <c r="AD79" s="9"/>
-      <c r="AF79" s="37"/>
+      <c r="AF79" s="39"/>
       <c r="AG79" s="18"/>
       <c r="AH79" s="8"/>
       <c r="AI79" s="9"/>
@@ -9761,7 +9794,7 @@
       <c r="AR79" s="9"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="D80" s="37"/>
+      <c r="D80" s="39"/>
       <c r="E80" s="16"/>
       <c r="F80" s="8"/>
       <c r="G80" s="9"/>
@@ -9774,7 +9807,7 @@
       <c r="N80" s="16"/>
       <c r="O80" s="8"/>
       <c r="P80" s="9"/>
-      <c r="R80" s="37"/>
+      <c r="R80" s="39"/>
       <c r="S80" s="16"/>
       <c r="T80" s="8"/>
       <c r="U80" s="9"/>
@@ -9787,7 +9820,7 @@
       <c r="AB80" s="16"/>
       <c r="AC80" s="8"/>
       <c r="AD80" s="9"/>
-      <c r="AF80" s="37"/>
+      <c r="AF80" s="39"/>
       <c r="AG80" s="16"/>
       <c r="AH80" s="8"/>
       <c r="AI80" s="9"/>
@@ -9802,7 +9835,7 @@
       <c r="AR80" s="9"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="D81" s="37"/>
+      <c r="D81" s="39"/>
       <c r="E81" s="18"/>
       <c r="F81" s="8"/>
       <c r="G81" s="9"/>
@@ -9815,7 +9848,7 @@
       <c r="N81" s="18"/>
       <c r="O81" s="8"/>
       <c r="P81" s="9"/>
-      <c r="R81" s="37"/>
+      <c r="R81" s="39"/>
       <c r="S81" s="18"/>
       <c r="T81" s="8"/>
       <c r="U81" s="9"/>
@@ -9828,7 +9861,7 @@
       <c r="AB81" s="18"/>
       <c r="AC81" s="8"/>
       <c r="AD81" s="9"/>
-      <c r="AF81" s="37"/>
+      <c r="AF81" s="39"/>
       <c r="AG81" s="18"/>
       <c r="AH81" s="8"/>
       <c r="AI81" s="9"/>
@@ -11727,10 +11760,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -11738,7 +11771,7 @@
     <row r="2" ht="15.75" customHeight="1"/>
     <row r="3" ht="15.75" customHeight="1">
       <c r="D3" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E3" s="4"/>
     </row>
@@ -11748,11 +11781,11 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="R4" s="33" t="s">
+      <c r="R4" s="35" t="s">
         <v>4</v>
       </c>
       <c r="S4" s="2"/>
-      <c r="AF4" s="34" t="s">
+      <c r="AF4" s="36" t="s">
         <v>5</v>
       </c>
       <c r="AG4" s="2"/>
@@ -11763,11 +11796,11 @@
         <v>6</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="37" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="9"/>
@@ -11782,16 +11815,16 @@
       <c r="L5" s="8"/>
       <c r="M5" s="9"/>
       <c r="N5" s="13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="2"/>
-      <c r="R5" s="35" t="s">
+      <c r="R5" s="37" t="s">
         <v>7</v>
       </c>
       <c r="S5" s="13" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="T5" s="8"/>
       <c r="U5" s="9"/>
@@ -11806,15 +11839,15 @@
       <c r="Z5" s="8"/>
       <c r="AA5" s="9"/>
       <c r="AB5" s="13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AC5" s="8"/>
       <c r="AD5" s="9"/>
-      <c r="AF5" s="35" t="s">
+      <c r="AF5" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>94</v>
+      <c r="AG5" s="38" t="s">
+        <v>99</v>
       </c>
       <c r="AH5" s="22"/>
       <c r="AI5" s="23"/>
@@ -11829,41 +11862,41 @@
       <c r="AN5" s="8"/>
       <c r="AO5" s="9"/>
       <c r="AP5" s="13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AQ5" s="8"/>
       <c r="AR5" s="9"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="14" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B6" s="9"/>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="39" t="s">
-        <v>96</v>
+      <c r="E6" s="41" t="s">
+        <v>101</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
       <c r="H6" s="16" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="9"/>
       <c r="K6" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="9"/>
       <c r="N6" s="16" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="37"/>
+      <c r="R6" s="39"/>
       <c r="S6" s="16"/>
       <c r="T6" s="8"/>
       <c r="U6" s="9"/>
@@ -11876,7 +11909,7 @@
       <c r="AB6" s="16"/>
       <c r="AC6" s="8"/>
       <c r="AD6" s="9"/>
-      <c r="AF6" s="37"/>
+      <c r="AF6" s="39"/>
       <c r="AG6" s="16"/>
       <c r="AH6" s="8"/>
       <c r="AI6" s="9"/>
@@ -11892,32 +11925,32 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B7" s="9"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="40" t="s">
-        <v>101</v>
+      <c r="D7" s="39"/>
+      <c r="E7" s="42" t="s">
+        <v>106</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="9"/>
       <c r="H7" s="18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="9"/>
       <c r="K7" s="18" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="9"/>
       <c r="N7" s="18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="37"/>
+      <c r="R7" s="39"/>
       <c r="S7" s="18"/>
       <c r="T7" s="8"/>
       <c r="U7" s="9"/>
@@ -11930,7 +11963,7 @@
       <c r="AB7" s="18"/>
       <c r="AC7" s="8"/>
       <c r="AD7" s="9"/>
-      <c r="AF7" s="37"/>
+      <c r="AF7" s="39"/>
       <c r="AG7" s="18"/>
       <c r="AH7" s="8"/>
       <c r="AI7" s="9"/>
@@ -11946,14 +11979,14 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B8" s="9"/>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="39" t="s">
-        <v>105</v>
+      <c r="E8" s="41" t="s">
+        <v>110</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
@@ -11963,17 +11996,17 @@
       <c r="I8" s="8"/>
       <c r="J8" s="9"/>
       <c r="K8" s="16" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="9"/>
       <c r="N8" s="16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="2"/>
-      <c r="R8" s="37"/>
+      <c r="R8" s="39"/>
       <c r="S8" s="16"/>
       <c r="T8" s="8"/>
       <c r="U8" s="9"/>
@@ -11986,7 +12019,7 @@
       <c r="AB8" s="16"/>
       <c r="AC8" s="8"/>
       <c r="AD8" s="9"/>
-      <c r="AF8" s="37"/>
+      <c r="AF8" s="39"/>
       <c r="AG8" s="16"/>
       <c r="AH8" s="8"/>
       <c r="AI8" s="9"/>
@@ -12001,29 +12034,29 @@
       <c r="AR8" s="9"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="D9" s="37"/>
+      <c r="D9" s="39"/>
       <c r="E9" s="18" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
       <c r="H9" s="18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="9"/>
       <c r="K9" s="18" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="9"/>
-      <c r="N9" s="41" t="s">
-        <v>111</v>
+      <c r="N9" s="43" t="s">
+        <v>116</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="2"/>
-      <c r="R9" s="37"/>
+      <c r="R9" s="39"/>
       <c r="S9" s="18"/>
       <c r="T9" s="8"/>
       <c r="U9" s="9"/>
@@ -12036,7 +12069,7 @@
       <c r="AB9" s="18"/>
       <c r="AC9" s="8"/>
       <c r="AD9" s="9"/>
-      <c r="AF9" s="37"/>
+      <c r="AF9" s="39"/>
       <c r="AG9" s="18"/>
       <c r="AH9" s="8"/>
       <c r="AI9" s="9"/>
@@ -12051,29 +12084,29 @@
       <c r="AR9" s="9"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="D10" s="37"/>
+      <c r="D10" s="39"/>
       <c r="E10" s="16" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
       <c r="H10" s="16" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="9"/>
       <c r="K10" s="16" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="9"/>
       <c r="N10" s="16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="37"/>
+      <c r="R10" s="39"/>
       <c r="S10" s="16"/>
       <c r="T10" s="8"/>
       <c r="U10" s="9"/>
@@ -12086,7 +12119,7 @@
       <c r="AB10" s="16"/>
       <c r="AC10" s="8"/>
       <c r="AD10" s="9"/>
-      <c r="AF10" s="37"/>
+      <c r="AF10" s="39"/>
       <c r="AG10" s="16"/>
       <c r="AH10" s="8"/>
       <c r="AI10" s="9"/>
@@ -12102,22 +12135,22 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="D11" s="37"/>
+      <c r="D11" s="39"/>
       <c r="E11" s="18" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="9"/>
       <c r="H11" s="18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="9"/>
       <c r="K11" s="18" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="9"/>
@@ -12125,7 +12158,7 @@
       <c r="O11" s="8"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="2"/>
-      <c r="R11" s="37"/>
+      <c r="R11" s="39"/>
       <c r="S11" s="18"/>
       <c r="T11" s="8"/>
       <c r="U11" s="9"/>
@@ -12138,7 +12171,7 @@
       <c r="AB11" s="18"/>
       <c r="AC11" s="8"/>
       <c r="AD11" s="9"/>
-      <c r="AF11" s="37"/>
+      <c r="AF11" s="39"/>
       <c r="AG11" s="18"/>
       <c r="AH11" s="8"/>
       <c r="AI11" s="9"/>
@@ -12153,29 +12186,29 @@
       <c r="AR11" s="9"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="D12" s="37"/>
+      <c r="D12" s="39"/>
       <c r="E12" s="16" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="9"/>
       <c r="H12" s="16" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="9"/>
       <c r="K12" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L12" s="8"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="42" t="s">
-        <v>122</v>
+      <c r="N12" s="44" t="s">
+        <v>127</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="2"/>
-      <c r="R12" s="37"/>
+      <c r="R12" s="39"/>
       <c r="S12" s="16"/>
       <c r="T12" s="8"/>
       <c r="U12" s="9"/>
@@ -12188,7 +12221,7 @@
       <c r="AB12" s="16"/>
       <c r="AC12" s="8"/>
       <c r="AD12" s="9"/>
-      <c r="AF12" s="37"/>
+      <c r="AF12" s="39"/>
       <c r="AG12" s="16"/>
       <c r="AH12" s="8"/>
       <c r="AI12" s="9"/>
@@ -12203,29 +12236,29 @@
       <c r="AR12" s="9"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="D13" s="37"/>
+      <c r="D13" s="39"/>
       <c r="E13" s="18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="9"/>
       <c r="H13" s="18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="9"/>
       <c r="K13" s="18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="L13" s="8"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="41" t="s">
-        <v>126</v>
+      <c r="N13" s="43" t="s">
+        <v>131</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="2"/>
-      <c r="R13" s="37"/>
+      <c r="R13" s="39"/>
       <c r="S13" s="18"/>
       <c r="T13" s="8"/>
       <c r="U13" s="9"/>
@@ -12238,7 +12271,7 @@
       <c r="AB13" s="18"/>
       <c r="AC13" s="8"/>
       <c r="AD13" s="9"/>
-      <c r="AF13" s="37"/>
+      <c r="AF13" s="39"/>
       <c r="AG13" s="18"/>
       <c r="AH13" s="8"/>
       <c r="AI13" s="9"/>
@@ -12253,29 +12286,29 @@
       <c r="AR13" s="9"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="D14" s="37"/>
+      <c r="D14" s="39"/>
       <c r="E14" s="16" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
       <c r="H14" s="16" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="9"/>
       <c r="K14" s="16" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="L14" s="8"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="43" t="s">
-        <v>129</v>
+      <c r="N14" s="45" t="s">
+        <v>134</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="2"/>
-      <c r="R14" s="37"/>
+      <c r="R14" s="39"/>
       <c r="S14" s="16"/>
       <c r="T14" s="8"/>
       <c r="U14" s="9"/>
@@ -12288,7 +12321,7 @@
       <c r="AB14" s="16"/>
       <c r="AC14" s="8"/>
       <c r="AD14" s="9"/>
-      <c r="AF14" s="37"/>
+      <c r="AF14" s="39"/>
       <c r="AG14" s="16"/>
       <c r="AH14" s="8"/>
       <c r="AI14" s="9"/>
@@ -12304,14 +12337,14 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="39" t="s">
         <v>58</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
@@ -12321,7 +12354,7 @@
       <c r="I15" s="8"/>
       <c r="J15" s="9"/>
       <c r="K15" s="18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L15" s="8"/>
       <c r="M15" s="9"/>
@@ -12329,7 +12362,7 @@
       <c r="O15" s="8"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="37"/>
+      <c r="R15" s="39"/>
       <c r="S15" s="18"/>
       <c r="T15" s="8"/>
       <c r="U15" s="9"/>
@@ -12342,7 +12375,7 @@
       <c r="AB15" s="18"/>
       <c r="AC15" s="8"/>
       <c r="AD15" s="9"/>
-      <c r="AF15" s="37"/>
+      <c r="AF15" s="39"/>
       <c r="AG15" s="18"/>
       <c r="AH15" s="8"/>
       <c r="AI15" s="9"/>
@@ -12357,7 +12390,7 @@
       <c r="AR15" s="9"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="D16" s="37"/>
+      <c r="D16" s="39"/>
       <c r="E16" s="16"/>
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
@@ -12371,7 +12404,7 @@
       <c r="O16" s="8"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="37"/>
+      <c r="R16" s="39"/>
       <c r="S16" s="16"/>
       <c r="T16" s="8"/>
       <c r="U16" s="9"/>
@@ -12384,7 +12417,7 @@
       <c r="AB16" s="16"/>
       <c r="AC16" s="8"/>
       <c r="AD16" s="9"/>
-      <c r="AF16" s="37"/>
+      <c r="AF16" s="39"/>
       <c r="AG16" s="16"/>
       <c r="AH16" s="8"/>
       <c r="AI16" s="9"/>
@@ -12399,21 +12432,21 @@
       <c r="AR16" s="9"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="D17" s="37"/>
+      <c r="D17" s="39"/>
       <c r="E17" s="25"/>
       <c r="F17" s="22"/>
       <c r="G17" s="23"/>
-      <c r="H17" s="31"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="22"/>
       <c r="J17" s="23"/>
-      <c r="K17" s="31"/>
+      <c r="K17" s="33"/>
       <c r="L17" s="22"/>
       <c r="M17" s="23"/>
       <c r="N17" s="18"/>
       <c r="O17" s="8"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="37"/>
+      <c r="R17" s="39"/>
       <c r="S17" s="18"/>
       <c r="T17" s="8"/>
       <c r="U17" s="9"/>
@@ -12426,7 +12459,7 @@
       <c r="AB17" s="18"/>
       <c r="AC17" s="8"/>
       <c r="AD17" s="9"/>
-      <c r="AF17" s="37"/>
+      <c r="AF17" s="39"/>
       <c r="AG17" s="18"/>
       <c r="AH17" s="8"/>
       <c r="AI17" s="9"/>
@@ -12441,7 +12474,7 @@
       <c r="AR17" s="9"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="D18" s="37"/>
+      <c r="D18" s="39"/>
       <c r="E18" s="21"/>
       <c r="F18" s="22"/>
       <c r="G18" s="23"/>
@@ -12455,7 +12488,7 @@
       <c r="O18" s="8"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="2"/>
-      <c r="R18" s="37"/>
+      <c r="R18" s="39"/>
       <c r="S18" s="16"/>
       <c r="T18" s="8"/>
       <c r="U18" s="9"/>
@@ -12468,7 +12501,7 @@
       <c r="AB18" s="16"/>
       <c r="AC18" s="8"/>
       <c r="AD18" s="9"/>
-      <c r="AF18" s="37"/>
+      <c r="AF18" s="39"/>
       <c r="AG18" s="16"/>
       <c r="AH18" s="8"/>
       <c r="AI18" s="9"/>
@@ -12483,21 +12516,21 @@
       <c r="AR18" s="9"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="D19" s="37"/>
+      <c r="D19" s="39"/>
       <c r="E19" s="25"/>
       <c r="F19" s="22"/>
       <c r="G19" s="23"/>
-      <c r="H19" s="31"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="22"/>
       <c r="J19" s="23"/>
-      <c r="K19" s="31"/>
+      <c r="K19" s="33"/>
       <c r="L19" s="22"/>
       <c r="M19" s="23"/>
       <c r="N19" s="18"/>
       <c r="O19" s="8"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="2"/>
-      <c r="R19" s="37"/>
+      <c r="R19" s="39"/>
       <c r="S19" s="18"/>
       <c r="T19" s="8"/>
       <c r="U19" s="9"/>
@@ -12510,7 +12543,7 @@
       <c r="AB19" s="18"/>
       <c r="AC19" s="8"/>
       <c r="AD19" s="9"/>
-      <c r="AF19" s="37"/>
+      <c r="AF19" s="39"/>
       <c r="AG19" s="18"/>
       <c r="AH19" s="8"/>
       <c r="AI19" s="9"/>
@@ -12525,7 +12558,7 @@
       <c r="AR19" s="9"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="D20" s="37"/>
+      <c r="D20" s="39"/>
       <c r="E20" s="16"/>
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
@@ -12539,7 +12572,7 @@
       <c r="O20" s="8"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
-      <c r="R20" s="37"/>
+      <c r="R20" s="39"/>
       <c r="S20" s="16"/>
       <c r="T20" s="8"/>
       <c r="U20" s="9"/>
@@ -12552,7 +12585,7 @@
       <c r="AB20" s="16"/>
       <c r="AC20" s="8"/>
       <c r="AD20" s="9"/>
-      <c r="AF20" s="37"/>
+      <c r="AF20" s="39"/>
       <c r="AG20" s="16"/>
       <c r="AH20" s="8"/>
       <c r="AI20" s="9"/>
@@ -12567,7 +12600,7 @@
       <c r="AR20" s="9"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="D21" s="37"/>
+      <c r="D21" s="39"/>
       <c r="E21" s="18"/>
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
@@ -12581,7 +12614,7 @@
       <c r="O21" s="8"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="2"/>
-      <c r="R21" s="37"/>
+      <c r="R21" s="39"/>
       <c r="S21" s="18"/>
       <c r="T21" s="8"/>
       <c r="U21" s="9"/>
@@ -12594,7 +12627,7 @@
       <c r="AB21" s="18"/>
       <c r="AC21" s="8"/>
       <c r="AD21" s="9"/>
-      <c r="AF21" s="37"/>
+      <c r="AF21" s="39"/>
       <c r="AG21" s="18"/>
       <c r="AH21" s="8"/>
       <c r="AI21" s="9"/>
@@ -12609,7 +12642,7 @@
       <c r="AR21" s="9"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="D22" s="37"/>
+      <c r="D22" s="39"/>
       <c r="E22" s="16"/>
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
@@ -12623,7 +12656,7 @@
       <c r="O22" s="8"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="2"/>
-      <c r="R22" s="37"/>
+      <c r="R22" s="39"/>
       <c r="S22" s="16"/>
       <c r="T22" s="8"/>
       <c r="U22" s="9"/>
@@ -12636,7 +12669,7 @@
       <c r="AB22" s="16"/>
       <c r="AC22" s="8"/>
       <c r="AD22" s="9"/>
-      <c r="AF22" s="37"/>
+      <c r="AF22" s="39"/>
       <c r="AG22" s="16"/>
       <c r="AH22" s="8"/>
       <c r="AI22" s="9"/>
@@ -12651,7 +12684,7 @@
       <c r="AR22" s="9"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="D23" s="37"/>
+      <c r="D23" s="39"/>
       <c r="E23" s="18"/>
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
@@ -12665,7 +12698,7 @@
       <c r="O23" s="8"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="2"/>
-      <c r="R23" s="37"/>
+      <c r="R23" s="39"/>
       <c r="S23" s="18"/>
       <c r="T23" s="8"/>
       <c r="U23" s="9"/>
@@ -12678,7 +12711,7 @@
       <c r="AB23" s="18"/>
       <c r="AC23" s="8"/>
       <c r="AD23" s="9"/>
-      <c r="AF23" s="37"/>
+      <c r="AF23" s="39"/>
       <c r="AG23" s="18"/>
       <c r="AH23" s="8"/>
       <c r="AI23" s="9"/>
@@ -12693,7 +12726,7 @@
       <c r="AR23" s="9"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="D24" s="37"/>
+      <c r="D24" s="39"/>
       <c r="E24" s="16"/>
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
@@ -12707,7 +12740,7 @@
       <c r="O24" s="8"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="2"/>
-      <c r="R24" s="37"/>
+      <c r="R24" s="39"/>
       <c r="S24" s="16"/>
       <c r="T24" s="8"/>
       <c r="U24" s="9"/>
@@ -12720,7 +12753,7 @@
       <c r="AB24" s="16"/>
       <c r="AC24" s="8"/>
       <c r="AD24" s="9"/>
-      <c r="AF24" s="37"/>
+      <c r="AF24" s="39"/>
       <c r="AG24" s="16"/>
       <c r="AH24" s="8"/>
       <c r="AI24" s="9"/>
@@ -12735,7 +12768,7 @@
       <c r="AR24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="D25" s="37"/>
+      <c r="D25" s="39"/>
       <c r="E25" s="18"/>
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
@@ -12749,7 +12782,7 @@
       <c r="O25" s="8"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="2"/>
-      <c r="R25" s="37"/>
+      <c r="R25" s="39"/>
       <c r="S25" s="18"/>
       <c r="T25" s="8"/>
       <c r="U25" s="9"/>
@@ -12762,7 +12795,7 @@
       <c r="AB25" s="18"/>
       <c r="AC25" s="8"/>
       <c r="AD25" s="9"/>
-      <c r="AF25" s="37"/>
+      <c r="AF25" s="39"/>
       <c r="AG25" s="18"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="9"/>
@@ -12777,7 +12810,7 @@
       <c r="AR25" s="9"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="D26" s="37"/>
+      <c r="D26" s="39"/>
       <c r="E26" s="16"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
@@ -12791,7 +12824,7 @@
       <c r="O26" s="8"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="2"/>
-      <c r="R26" s="37"/>
+      <c r="R26" s="39"/>
       <c r="S26" s="16"/>
       <c r="T26" s="8"/>
       <c r="U26" s="9"/>
@@ -12804,7 +12837,7 @@
       <c r="AB26" s="16"/>
       <c r="AC26" s="8"/>
       <c r="AD26" s="9"/>
-      <c r="AF26" s="37"/>
+      <c r="AF26" s="39"/>
       <c r="AG26" s="16"/>
       <c r="AH26" s="8"/>
       <c r="AI26" s="9"/>
@@ -12819,7 +12852,7 @@
       <c r="AR26" s="9"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="D27" s="37"/>
+      <c r="D27" s="39"/>
       <c r="E27" s="18"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
@@ -12833,7 +12866,7 @@
       <c r="O27" s="8"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="2"/>
-      <c r="R27" s="37"/>
+      <c r="R27" s="39"/>
       <c r="S27" s="18"/>
       <c r="T27" s="8"/>
       <c r="U27" s="9"/>
@@ -12846,7 +12879,7 @@
       <c r="AB27" s="18"/>
       <c r="AC27" s="8"/>
       <c r="AD27" s="9"/>
-      <c r="AF27" s="37"/>
+      <c r="AF27" s="39"/>
       <c r="AG27" s="18"/>
       <c r="AH27" s="8"/>
       <c r="AI27" s="9"/>
@@ -12861,7 +12894,7 @@
       <c r="AR27" s="9"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="D28" s="37"/>
+      <c r="D28" s="39"/>
       <c r="E28" s="16"/>
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
@@ -12875,7 +12908,7 @@
       <c r="O28" s="8"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="2"/>
-      <c r="R28" s="37"/>
+      <c r="R28" s="39"/>
       <c r="S28" s="16"/>
       <c r="T28" s="8"/>
       <c r="U28" s="9"/>
@@ -12888,7 +12921,7 @@
       <c r="AB28" s="16"/>
       <c r="AC28" s="8"/>
       <c r="AD28" s="9"/>
-      <c r="AF28" s="37"/>
+      <c r="AF28" s="39"/>
       <c r="AG28" s="16"/>
       <c r="AH28" s="8"/>
       <c r="AI28" s="9"/>
@@ -12903,7 +12936,7 @@
       <c r="AR28" s="9"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="D29" s="37"/>
+      <c r="D29" s="39"/>
       <c r="E29" s="18"/>
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
@@ -12917,7 +12950,7 @@
       <c r="O29" s="8"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="2"/>
-      <c r="R29" s="37"/>
+      <c r="R29" s="39"/>
       <c r="S29" s="18"/>
       <c r="T29" s="8"/>
       <c r="U29" s="9"/>
@@ -12930,7 +12963,7 @@
       <c r="AB29" s="18"/>
       <c r="AC29" s="8"/>
       <c r="AD29" s="9"/>
-      <c r="AF29" s="37"/>
+      <c r="AF29" s="39"/>
       <c r="AG29" s="18"/>
       <c r="AH29" s="8"/>
       <c r="AI29" s="9"/>
@@ -12945,7 +12978,7 @@
       <c r="AR29" s="9"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="D30" s="37"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="16"/>
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
@@ -12959,7 +12992,7 @@
       <c r="O30" s="8"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="2"/>
-      <c r="R30" s="37"/>
+      <c r="R30" s="39"/>
       <c r="S30" s="16"/>
       <c r="T30" s="8"/>
       <c r="U30" s="9"/>
@@ -12972,7 +13005,7 @@
       <c r="AB30" s="16"/>
       <c r="AC30" s="8"/>
       <c r="AD30" s="9"/>
-      <c r="AF30" s="37"/>
+      <c r="AF30" s="39"/>
       <c r="AG30" s="16"/>
       <c r="AH30" s="8"/>
       <c r="AI30" s="9"/>
@@ -12987,7 +13020,7 @@
       <c r="AR30" s="9"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="D31" s="37"/>
+      <c r="D31" s="39"/>
       <c r="E31" s="18"/>
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
@@ -13001,7 +13034,7 @@
       <c r="O31" s="8"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="2"/>
-      <c r="R31" s="37"/>
+      <c r="R31" s="39"/>
       <c r="S31" s="18"/>
       <c r="T31" s="8"/>
       <c r="U31" s="9"/>
@@ -13014,7 +13047,7 @@
       <c r="AB31" s="18"/>
       <c r="AC31" s="8"/>
       <c r="AD31" s="9"/>
-      <c r="AF31" s="37"/>
+      <c r="AF31" s="39"/>
       <c r="AG31" s="18"/>
       <c r="AH31" s="8"/>
       <c r="AI31" s="9"/>
@@ -13029,7 +13062,7 @@
       <c r="AR31" s="9"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="D32" s="37"/>
+      <c r="D32" s="39"/>
       <c r="E32" s="16"/>
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
@@ -13043,7 +13076,7 @@
       <c r="O32" s="8"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="2"/>
-      <c r="R32" s="37"/>
+      <c r="R32" s="39"/>
       <c r="S32" s="16"/>
       <c r="T32" s="8"/>
       <c r="U32" s="9"/>
@@ -13056,7 +13089,7 @@
       <c r="AB32" s="16"/>
       <c r="AC32" s="8"/>
       <c r="AD32" s="9"/>
-      <c r="AF32" s="37"/>
+      <c r="AF32" s="39"/>
       <c r="AG32" s="16"/>
       <c r="AH32" s="8"/>
       <c r="AI32" s="9"/>
@@ -13071,7 +13104,7 @@
       <c r="AR32" s="9"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="D33" s="37"/>
+      <c r="D33" s="39"/>
       <c r="E33" s="18"/>
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
@@ -13085,7 +13118,7 @@
       <c r="O33" s="8"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="2"/>
-      <c r="R33" s="37"/>
+      <c r="R33" s="39"/>
       <c r="S33" s="18"/>
       <c r="T33" s="8"/>
       <c r="U33" s="9"/>
@@ -13098,7 +13131,7 @@
       <c r="AB33" s="18"/>
       <c r="AC33" s="8"/>
       <c r="AD33" s="9"/>
-      <c r="AF33" s="37"/>
+      <c r="AF33" s="39"/>
       <c r="AG33" s="18"/>
       <c r="AH33" s="8"/>
       <c r="AI33" s="9"/>
@@ -13113,7 +13146,7 @@
       <c r="AR33" s="9"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="D34" s="37"/>
+      <c r="D34" s="39"/>
       <c r="E34" s="16"/>
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
@@ -13127,7 +13160,7 @@
       <c r="O34" s="8"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="2"/>
-      <c r="R34" s="37"/>
+      <c r="R34" s="39"/>
       <c r="S34" s="16"/>
       <c r="T34" s="8"/>
       <c r="U34" s="9"/>
@@ -13140,7 +13173,7 @@
       <c r="AB34" s="16"/>
       <c r="AC34" s="8"/>
       <c r="AD34" s="9"/>
-      <c r="AF34" s="37"/>
+      <c r="AF34" s="39"/>
       <c r="AG34" s="16"/>
       <c r="AH34" s="8"/>
       <c r="AI34" s="9"/>
@@ -13155,7 +13188,7 @@
       <c r="AR34" s="9"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="D35" s="37"/>
+      <c r="D35" s="39"/>
       <c r="E35" s="18"/>
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
@@ -13169,7 +13202,7 @@
       <c r="O35" s="8"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="2"/>
-      <c r="R35" s="37"/>
+      <c r="R35" s="39"/>
       <c r="S35" s="18"/>
       <c r="T35" s="8"/>
       <c r="U35" s="9"/>
@@ -13182,7 +13215,7 @@
       <c r="AB35" s="18"/>
       <c r="AC35" s="8"/>
       <c r="AD35" s="9"/>
-      <c r="AF35" s="37"/>
+      <c r="AF35" s="39"/>
       <c r="AG35" s="18"/>
       <c r="AH35" s="8"/>
       <c r="AI35" s="9"/>
@@ -13197,7 +13230,7 @@
       <c r="AR35" s="9"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="D36" s="37"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="16"/>
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
@@ -13211,7 +13244,7 @@
       <c r="O36" s="8"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="2"/>
-      <c r="R36" s="37"/>
+      <c r="R36" s="39"/>
       <c r="S36" s="16"/>
       <c r="T36" s="8"/>
       <c r="U36" s="9"/>
@@ -13224,7 +13257,7 @@
       <c r="AB36" s="16"/>
       <c r="AC36" s="8"/>
       <c r="AD36" s="9"/>
-      <c r="AF36" s="37"/>
+      <c r="AF36" s="39"/>
       <c r="AG36" s="16"/>
       <c r="AH36" s="8"/>
       <c r="AI36" s="9"/>
@@ -13239,7 +13272,7 @@
       <c r="AR36" s="9"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="D37" s="37"/>
+      <c r="D37" s="39"/>
       <c r="E37" s="18"/>
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
@@ -13253,7 +13286,7 @@
       <c r="O37" s="8"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="2"/>
-      <c r="R37" s="37"/>
+      <c r="R37" s="39"/>
       <c r="S37" s="18"/>
       <c r="T37" s="8"/>
       <c r="U37" s="9"/>
@@ -13266,7 +13299,7 @@
       <c r="AB37" s="18"/>
       <c r="AC37" s="8"/>
       <c r="AD37" s="9"/>
-      <c r="AF37" s="37"/>
+      <c r="AF37" s="39"/>
       <c r="AG37" s="18"/>
       <c r="AH37" s="8"/>
       <c r="AI37" s="9"/>
@@ -13281,7 +13314,7 @@
       <c r="AR37" s="9"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="D38" s="37"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="16"/>
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
@@ -13295,7 +13328,7 @@
       <c r="O38" s="8"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="2"/>
-      <c r="R38" s="37"/>
+      <c r="R38" s="39"/>
       <c r="S38" s="16"/>
       <c r="T38" s="8"/>
       <c r="U38" s="9"/>
@@ -13308,7 +13341,7 @@
       <c r="AB38" s="16"/>
       <c r="AC38" s="8"/>
       <c r="AD38" s="9"/>
-      <c r="AF38" s="37"/>
+      <c r="AF38" s="39"/>
       <c r="AG38" s="16"/>
       <c r="AH38" s="8"/>
       <c r="AI38" s="9"/>
@@ -13323,7 +13356,7 @@
       <c r="AR38" s="9"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="D39" s="37"/>
+      <c r="D39" s="39"/>
       <c r="E39" s="18"/>
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
@@ -13337,7 +13370,7 @@
       <c r="O39" s="8"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="2"/>
-      <c r="R39" s="37"/>
+      <c r="R39" s="39"/>
       <c r="S39" s="18"/>
       <c r="T39" s="8"/>
       <c r="U39" s="9"/>
@@ -13350,7 +13383,7 @@
       <c r="AB39" s="18"/>
       <c r="AC39" s="8"/>
       <c r="AD39" s="9"/>
-      <c r="AF39" s="37"/>
+      <c r="AF39" s="39"/>
       <c r="AG39" s="18"/>
       <c r="AH39" s="8"/>
       <c r="AI39" s="9"/>
@@ -13365,7 +13398,7 @@
       <c r="AR39" s="9"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="D40" s="37"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="16"/>
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
@@ -13379,7 +13412,7 @@
       <c r="O40" s="8"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="2"/>
-      <c r="R40" s="37"/>
+      <c r="R40" s="39"/>
       <c r="S40" s="16"/>
       <c r="T40" s="8"/>
       <c r="U40" s="9"/>
@@ -13392,7 +13425,7 @@
       <c r="AB40" s="16"/>
       <c r="AC40" s="8"/>
       <c r="AD40" s="9"/>
-      <c r="AF40" s="37"/>
+      <c r="AF40" s="39"/>
       <c r="AG40" s="16"/>
       <c r="AH40" s="8"/>
       <c r="AI40" s="9"/>
@@ -13407,7 +13440,7 @@
       <c r="AR40" s="9"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="D41" s="37"/>
+      <c r="D41" s="39"/>
       <c r="E41" s="18"/>
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
@@ -13421,7 +13454,7 @@
       <c r="O41" s="8"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="2"/>
-      <c r="R41" s="37"/>
+      <c r="R41" s="39"/>
       <c r="S41" s="18"/>
       <c r="T41" s="8"/>
       <c r="U41" s="9"/>
@@ -13434,7 +13467,7 @@
       <c r="AB41" s="18"/>
       <c r="AC41" s="8"/>
       <c r="AD41" s="9"/>
-      <c r="AF41" s="37"/>
+      <c r="AF41" s="39"/>
       <c r="AG41" s="18"/>
       <c r="AH41" s="8"/>
       <c r="AI41" s="9"/>
@@ -13449,7 +13482,7 @@
       <c r="AR41" s="9"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="D42" s="37"/>
+      <c r="D42" s="39"/>
       <c r="E42" s="16"/>
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
@@ -13462,7 +13495,7 @@
       <c r="N42" s="16"/>
       <c r="O42" s="8"/>
       <c r="P42" s="9"/>
-      <c r="R42" s="37"/>
+      <c r="R42" s="39"/>
       <c r="S42" s="16"/>
       <c r="T42" s="8"/>
       <c r="U42" s="9"/>
@@ -13475,7 +13508,7 @@
       <c r="AB42" s="16"/>
       <c r="AC42" s="8"/>
       <c r="AD42" s="9"/>
-      <c r="AF42" s="37"/>
+      <c r="AF42" s="39"/>
       <c r="AG42" s="16"/>
       <c r="AH42" s="8"/>
       <c r="AI42" s="9"/>
@@ -13490,7 +13523,7 @@
       <c r="AR42" s="9"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="D43" s="37"/>
+      <c r="D43" s="39"/>
       <c r="E43" s="18"/>
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
@@ -13503,7 +13536,7 @@
       <c r="N43" s="18"/>
       <c r="O43" s="8"/>
       <c r="P43" s="9"/>
-      <c r="R43" s="37"/>
+      <c r="R43" s="39"/>
       <c r="S43" s="18"/>
       <c r="T43" s="8"/>
       <c r="U43" s="9"/>
@@ -13516,7 +13549,7 @@
       <c r="AB43" s="18"/>
       <c r="AC43" s="8"/>
       <c r="AD43" s="9"/>
-      <c r="AF43" s="37"/>
+      <c r="AF43" s="39"/>
       <c r="AG43" s="18"/>
       <c r="AH43" s="8"/>
       <c r="AI43" s="9"/>
@@ -13531,7 +13564,7 @@
       <c r="AR43" s="9"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="D44" s="37"/>
+      <c r="D44" s="39"/>
       <c r="E44" s="16"/>
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
@@ -13544,7 +13577,7 @@
       <c r="N44" s="16"/>
       <c r="O44" s="8"/>
       <c r="P44" s="9"/>
-      <c r="R44" s="37"/>
+      <c r="R44" s="39"/>
       <c r="S44" s="16"/>
       <c r="T44" s="8"/>
       <c r="U44" s="9"/>
@@ -13557,7 +13590,7 @@
       <c r="AB44" s="16"/>
       <c r="AC44" s="8"/>
       <c r="AD44" s="9"/>
-      <c r="AF44" s="37"/>
+      <c r="AF44" s="39"/>
       <c r="AG44" s="16"/>
       <c r="AH44" s="8"/>
       <c r="AI44" s="9"/>
@@ -13572,7 +13605,7 @@
       <c r="AR44" s="9"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="D45" s="37"/>
+      <c r="D45" s="39"/>
       <c r="E45" s="18"/>
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
@@ -13585,7 +13618,7 @@
       <c r="N45" s="18"/>
       <c r="O45" s="8"/>
       <c r="P45" s="9"/>
-      <c r="R45" s="37"/>
+      <c r="R45" s="39"/>
       <c r="S45" s="18"/>
       <c r="T45" s="8"/>
       <c r="U45" s="9"/>
@@ -13598,7 +13631,7 @@
       <c r="AB45" s="18"/>
       <c r="AC45" s="8"/>
       <c r="AD45" s="9"/>
-      <c r="AF45" s="37"/>
+      <c r="AF45" s="39"/>
       <c r="AG45" s="18"/>
       <c r="AH45" s="8"/>
       <c r="AI45" s="9"/>
@@ -13613,7 +13646,7 @@
       <c r="AR45" s="9"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="D46" s="37"/>
+      <c r="D46" s="39"/>
       <c r="E46" s="16"/>
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
@@ -13626,7 +13659,7 @@
       <c r="N46" s="16"/>
       <c r="O46" s="8"/>
       <c r="P46" s="9"/>
-      <c r="R46" s="37"/>
+      <c r="R46" s="39"/>
       <c r="S46" s="16"/>
       <c r="T46" s="8"/>
       <c r="U46" s="9"/>
@@ -13639,7 +13672,7 @@
       <c r="AB46" s="16"/>
       <c r="AC46" s="8"/>
       <c r="AD46" s="9"/>
-      <c r="AF46" s="37"/>
+      <c r="AF46" s="39"/>
       <c r="AG46" s="16"/>
       <c r="AH46" s="8"/>
       <c r="AI46" s="9"/>
@@ -13654,7 +13687,7 @@
       <c r="AR46" s="9"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="D47" s="37"/>
+      <c r="D47" s="39"/>
       <c r="E47" s="18"/>
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
@@ -13667,7 +13700,7 @@
       <c r="N47" s="18"/>
       <c r="O47" s="8"/>
       <c r="P47" s="9"/>
-      <c r="R47" s="37"/>
+      <c r="R47" s="39"/>
       <c r="S47" s="18"/>
       <c r="T47" s="8"/>
       <c r="U47" s="9"/>
@@ -13680,7 +13713,7 @@
       <c r="AB47" s="18"/>
       <c r="AC47" s="8"/>
       <c r="AD47" s="9"/>
-      <c r="AF47" s="37"/>
+      <c r="AF47" s="39"/>
       <c r="AG47" s="18"/>
       <c r="AH47" s="8"/>
       <c r="AI47" s="9"/>
@@ -13695,7 +13728,7 @@
       <c r="AR47" s="9"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="D48" s="37"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="21"/>
       <c r="F48" s="22"/>
       <c r="G48" s="23"/>
@@ -13708,7 +13741,7 @@
       <c r="N48" s="16"/>
       <c r="O48" s="8"/>
       <c r="P48" s="9"/>
-      <c r="R48" s="37"/>
+      <c r="R48" s="39"/>
       <c r="S48" s="16"/>
       <c r="T48" s="8"/>
       <c r="U48" s="9"/>
@@ -13721,7 +13754,7 @@
       <c r="AB48" s="16"/>
       <c r="AC48" s="8"/>
       <c r="AD48" s="9"/>
-      <c r="AF48" s="37"/>
+      <c r="AF48" s="39"/>
       <c r="AG48" s="16"/>
       <c r="AH48" s="8"/>
       <c r="AI48" s="9"/>
@@ -13736,7 +13769,7 @@
       <c r="AR48" s="9"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="D49" s="37"/>
+      <c r="D49" s="39"/>
       <c r="E49" s="25"/>
       <c r="F49" s="22"/>
       <c r="G49" s="23"/>
@@ -13749,7 +13782,7 @@
       <c r="N49" s="18"/>
       <c r="O49" s="8"/>
       <c r="P49" s="9"/>
-      <c r="R49" s="37"/>
+      <c r="R49" s="39"/>
       <c r="S49" s="18"/>
       <c r="T49" s="8"/>
       <c r="U49" s="9"/>
@@ -13762,7 +13795,7 @@
       <c r="AB49" s="18"/>
       <c r="AC49" s="8"/>
       <c r="AD49" s="9"/>
-      <c r="AF49" s="37"/>
+      <c r="AF49" s="39"/>
       <c r="AG49" s="18"/>
       <c r="AH49" s="8"/>
       <c r="AI49" s="9"/>
@@ -13777,7 +13810,7 @@
       <c r="AR49" s="9"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="D50" s="37"/>
+      <c r="D50" s="39"/>
       <c r="E50" s="21"/>
       <c r="F50" s="22"/>
       <c r="G50" s="23"/>
@@ -13790,7 +13823,7 @@
       <c r="N50" s="16"/>
       <c r="O50" s="8"/>
       <c r="P50" s="9"/>
-      <c r="R50" s="37"/>
+      <c r="R50" s="39"/>
       <c r="S50" s="16"/>
       <c r="T50" s="8"/>
       <c r="U50" s="9"/>
@@ -13803,7 +13836,7 @@
       <c r="AB50" s="16"/>
       <c r="AC50" s="8"/>
       <c r="AD50" s="9"/>
-      <c r="AF50" s="37"/>
+      <c r="AF50" s="39"/>
       <c r="AG50" s="16"/>
       <c r="AH50" s="8"/>
       <c r="AI50" s="9"/>
@@ -13818,7 +13851,7 @@
       <c r="AR50" s="9"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="D51" s="37"/>
+      <c r="D51" s="39"/>
       <c r="E51" s="18"/>
       <c r="F51" s="8"/>
       <c r="G51" s="9"/>
@@ -13831,7 +13864,7 @@
       <c r="N51" s="18"/>
       <c r="O51" s="8"/>
       <c r="P51" s="9"/>
-      <c r="R51" s="37"/>
+      <c r="R51" s="39"/>
       <c r="S51" s="18"/>
       <c r="T51" s="8"/>
       <c r="U51" s="9"/>
@@ -13844,7 +13877,7 @@
       <c r="AB51" s="18"/>
       <c r="AC51" s="8"/>
       <c r="AD51" s="9"/>
-      <c r="AF51" s="37"/>
+      <c r="AF51" s="39"/>
       <c r="AG51" s="18"/>
       <c r="AH51" s="8"/>
       <c r="AI51" s="9"/>
@@ -13859,7 +13892,7 @@
       <c r="AR51" s="9"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="D52" s="37"/>
+      <c r="D52" s="39"/>
       <c r="E52" s="16"/>
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
@@ -13872,7 +13905,7 @@
       <c r="N52" s="16"/>
       <c r="O52" s="8"/>
       <c r="P52" s="9"/>
-      <c r="R52" s="37"/>
+      <c r="R52" s="39"/>
       <c r="S52" s="16"/>
       <c r="T52" s="8"/>
       <c r="U52" s="9"/>
@@ -13885,7 +13918,7 @@
       <c r="AB52" s="16"/>
       <c r="AC52" s="8"/>
       <c r="AD52" s="9"/>
-      <c r="AF52" s="37"/>
+      <c r="AF52" s="39"/>
       <c r="AG52" s="16"/>
       <c r="AH52" s="8"/>
       <c r="AI52" s="9"/>
@@ -13900,7 +13933,7 @@
       <c r="AR52" s="9"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="D53" s="37"/>
+      <c r="D53" s="39"/>
       <c r="E53" s="18"/>
       <c r="F53" s="8"/>
       <c r="G53" s="9"/>
@@ -13913,7 +13946,7 @@
       <c r="N53" s="18"/>
       <c r="O53" s="8"/>
       <c r="P53" s="9"/>
-      <c r="R53" s="37"/>
+      <c r="R53" s="39"/>
       <c r="S53" s="18"/>
       <c r="T53" s="8"/>
       <c r="U53" s="9"/>
@@ -13926,7 +13959,7 @@
       <c r="AB53" s="18"/>
       <c r="AC53" s="8"/>
       <c r="AD53" s="9"/>
-      <c r="AF53" s="37"/>
+      <c r="AF53" s="39"/>
       <c r="AG53" s="18"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="9"/>
@@ -13941,7 +13974,7 @@
       <c r="AR53" s="9"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="D54" s="37"/>
+      <c r="D54" s="39"/>
       <c r="E54" s="16"/>
       <c r="F54" s="8"/>
       <c r="G54" s="9"/>
@@ -13954,7 +13987,7 @@
       <c r="N54" s="16"/>
       <c r="O54" s="8"/>
       <c r="P54" s="9"/>
-      <c r="R54" s="37"/>
+      <c r="R54" s="39"/>
       <c r="S54" s="16"/>
       <c r="T54" s="8"/>
       <c r="U54" s="9"/>
@@ -13967,7 +14000,7 @@
       <c r="AB54" s="16"/>
       <c r="AC54" s="8"/>
       <c r="AD54" s="9"/>
-      <c r="AF54" s="37"/>
+      <c r="AF54" s="39"/>
       <c r="AG54" s="16"/>
       <c r="AH54" s="8"/>
       <c r="AI54" s="9"/>
@@ -13982,7 +14015,7 @@
       <c r="AR54" s="9"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="D55" s="37"/>
+      <c r="D55" s="39"/>
       <c r="E55" s="18"/>
       <c r="F55" s="8"/>
       <c r="G55" s="9"/>
@@ -13995,7 +14028,7 @@
       <c r="N55" s="18"/>
       <c r="O55" s="8"/>
       <c r="P55" s="9"/>
-      <c r="R55" s="37"/>
+      <c r="R55" s="39"/>
       <c r="S55" s="18"/>
       <c r="T55" s="8"/>
       <c r="U55" s="9"/>
@@ -14008,7 +14041,7 @@
       <c r="AB55" s="18"/>
       <c r="AC55" s="8"/>
       <c r="AD55" s="9"/>
-      <c r="AF55" s="37"/>
+      <c r="AF55" s="39"/>
       <c r="AG55" s="18"/>
       <c r="AH55" s="8"/>
       <c r="AI55" s="9"/>
@@ -14023,7 +14056,7 @@
       <c r="AR55" s="9"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="D56" s="37"/>
+      <c r="D56" s="39"/>
       <c r="E56" s="16"/>
       <c r="F56" s="8"/>
       <c r="G56" s="9"/>
@@ -14036,7 +14069,7 @@
       <c r="N56" s="16"/>
       <c r="O56" s="8"/>
       <c r="P56" s="9"/>
-      <c r="R56" s="37"/>
+      <c r="R56" s="39"/>
       <c r="S56" s="16"/>
       <c r="T56" s="8"/>
       <c r="U56" s="9"/>
@@ -14049,7 +14082,7 @@
       <c r="AB56" s="16"/>
       <c r="AC56" s="8"/>
       <c r="AD56" s="9"/>
-      <c r="AF56" s="37"/>
+      <c r="AF56" s="39"/>
       <c r="AG56" s="16"/>
       <c r="AH56" s="8"/>
       <c r="AI56" s="9"/>
@@ -14064,7 +14097,7 @@
       <c r="AR56" s="9"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="D57" s="37"/>
+      <c r="D57" s="39"/>
       <c r="E57" s="18"/>
       <c r="F57" s="8"/>
       <c r="G57" s="9"/>
@@ -14077,7 +14110,7 @@
       <c r="N57" s="18"/>
       <c r="O57" s="8"/>
       <c r="P57" s="9"/>
-      <c r="R57" s="37"/>
+      <c r="R57" s="39"/>
       <c r="S57" s="18"/>
       <c r="T57" s="8"/>
       <c r="U57" s="9"/>
@@ -14090,7 +14123,7 @@
       <c r="AB57" s="18"/>
       <c r="AC57" s="8"/>
       <c r="AD57" s="9"/>
-      <c r="AF57" s="37"/>
+      <c r="AF57" s="39"/>
       <c r="AG57" s="18"/>
       <c r="AH57" s="8"/>
       <c r="AI57" s="9"/>
@@ -14105,7 +14138,7 @@
       <c r="AR57" s="9"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="D58" s="37"/>
+      <c r="D58" s="39"/>
       <c r="E58" s="21"/>
       <c r="F58" s="22"/>
       <c r="G58" s="23"/>
@@ -14118,7 +14151,7 @@
       <c r="N58" s="16"/>
       <c r="O58" s="8"/>
       <c r="P58" s="9"/>
-      <c r="R58" s="37"/>
+      <c r="R58" s="39"/>
       <c r="S58" s="16"/>
       <c r="T58" s="8"/>
       <c r="U58" s="9"/>
@@ -14131,7 +14164,7 @@
       <c r="AB58" s="16"/>
       <c r="AC58" s="8"/>
       <c r="AD58" s="9"/>
-      <c r="AF58" s="37"/>
+      <c r="AF58" s="39"/>
       <c r="AG58" s="16"/>
       <c r="AH58" s="8"/>
       <c r="AI58" s="9"/>
@@ -14146,20 +14179,20 @@
       <c r="AR58" s="9"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="D59" s="37"/>
+      <c r="D59" s="39"/>
       <c r="E59" s="25"/>
       <c r="F59" s="22"/>
       <c r="G59" s="23"/>
-      <c r="H59" s="31"/>
+      <c r="H59" s="33"/>
       <c r="I59" s="22"/>
       <c r="J59" s="23"/>
-      <c r="K59" s="31"/>
+      <c r="K59" s="33"/>
       <c r="L59" s="22"/>
       <c r="M59" s="23"/>
       <c r="N59" s="18"/>
       <c r="O59" s="8"/>
       <c r="P59" s="9"/>
-      <c r="R59" s="37"/>
+      <c r="R59" s="39"/>
       <c r="S59" s="18"/>
       <c r="T59" s="8"/>
       <c r="U59" s="9"/>
@@ -14172,7 +14205,7 @@
       <c r="AB59" s="18"/>
       <c r="AC59" s="8"/>
       <c r="AD59" s="9"/>
-      <c r="AF59" s="37"/>
+      <c r="AF59" s="39"/>
       <c r="AG59" s="18"/>
       <c r="AH59" s="8"/>
       <c r="AI59" s="9"/>
@@ -14187,7 +14220,7 @@
       <c r="AR59" s="9"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="D60" s="37"/>
+      <c r="D60" s="39"/>
       <c r="E60" s="21"/>
       <c r="F60" s="22"/>
       <c r="G60" s="23"/>
@@ -14200,7 +14233,7 @@
       <c r="N60" s="16"/>
       <c r="O60" s="8"/>
       <c r="P60" s="9"/>
-      <c r="R60" s="37"/>
+      <c r="R60" s="39"/>
       <c r="S60" s="16"/>
       <c r="T60" s="8"/>
       <c r="U60" s="9"/>
@@ -14213,7 +14246,7 @@
       <c r="AB60" s="16"/>
       <c r="AC60" s="8"/>
       <c r="AD60" s="9"/>
-      <c r="AF60" s="37"/>
+      <c r="AF60" s="39"/>
       <c r="AG60" s="16"/>
       <c r="AH60" s="8"/>
       <c r="AI60" s="9"/>
@@ -14228,20 +14261,20 @@
       <c r="AR60" s="9"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="D61" s="37"/>
+      <c r="D61" s="39"/>
       <c r="E61" s="25"/>
       <c r="F61" s="22"/>
       <c r="G61" s="23"/>
-      <c r="H61" s="31"/>
+      <c r="H61" s="33"/>
       <c r="I61" s="22"/>
       <c r="J61" s="23"/>
-      <c r="K61" s="31"/>
+      <c r="K61" s="33"/>
       <c r="L61" s="22"/>
       <c r="M61" s="23"/>
       <c r="N61" s="18"/>
       <c r="O61" s="8"/>
       <c r="P61" s="9"/>
-      <c r="R61" s="37"/>
+      <c r="R61" s="39"/>
       <c r="S61" s="18"/>
       <c r="T61" s="8"/>
       <c r="U61" s="9"/>
@@ -14254,7 +14287,7 @@
       <c r="AB61" s="18"/>
       <c r="AC61" s="8"/>
       <c r="AD61" s="9"/>
-      <c r="AF61" s="37"/>
+      <c r="AF61" s="39"/>
       <c r="AG61" s="18"/>
       <c r="AH61" s="8"/>
       <c r="AI61" s="9"/>
@@ -14269,7 +14302,7 @@
       <c r="AR61" s="9"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="D62" s="37"/>
+      <c r="D62" s="39"/>
       <c r="E62" s="21"/>
       <c r="F62" s="22"/>
       <c r="G62" s="23"/>
@@ -14282,7 +14315,7 @@
       <c r="N62" s="16"/>
       <c r="O62" s="8"/>
       <c r="P62" s="9"/>
-      <c r="R62" s="37"/>
+      <c r="R62" s="39"/>
       <c r="S62" s="16"/>
       <c r="T62" s="8"/>
       <c r="U62" s="9"/>
@@ -14295,7 +14328,7 @@
       <c r="AB62" s="16"/>
       <c r="AC62" s="8"/>
       <c r="AD62" s="9"/>
-      <c r="AF62" s="37"/>
+      <c r="AF62" s="39"/>
       <c r="AG62" s="16"/>
       <c r="AH62" s="8"/>
       <c r="AI62" s="9"/>
@@ -14310,20 +14343,20 @@
       <c r="AR62" s="9"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="D63" s="37"/>
+      <c r="D63" s="39"/>
       <c r="E63" s="25"/>
       <c r="F63" s="22"/>
       <c r="G63" s="23"/>
-      <c r="H63" s="31"/>
+      <c r="H63" s="33"/>
       <c r="I63" s="22"/>
       <c r="J63" s="23"/>
-      <c r="K63" s="31"/>
+      <c r="K63" s="33"/>
       <c r="L63" s="22"/>
       <c r="M63" s="23"/>
       <c r="N63" s="18"/>
       <c r="O63" s="8"/>
       <c r="P63" s="9"/>
-      <c r="R63" s="37"/>
+      <c r="R63" s="39"/>
       <c r="S63" s="18"/>
       <c r="T63" s="8"/>
       <c r="U63" s="9"/>
@@ -14336,7 +14369,7 @@
       <c r="AB63" s="18"/>
       <c r="AC63" s="8"/>
       <c r="AD63" s="9"/>
-      <c r="AF63" s="37"/>
+      <c r="AF63" s="39"/>
       <c r="AG63" s="18"/>
       <c r="AH63" s="8"/>
       <c r="AI63" s="9"/>
@@ -14351,7 +14384,7 @@
       <c r="AR63" s="9"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="D64" s="37"/>
+      <c r="D64" s="39"/>
       <c r="E64" s="16"/>
       <c r="F64" s="8"/>
       <c r="G64" s="9"/>
@@ -14364,7 +14397,7 @@
       <c r="N64" s="16"/>
       <c r="O64" s="8"/>
       <c r="P64" s="9"/>
-      <c r="R64" s="37"/>
+      <c r="R64" s="39"/>
       <c r="S64" s="16"/>
       <c r="T64" s="8"/>
       <c r="U64" s="9"/>
@@ -14377,7 +14410,7 @@
       <c r="AB64" s="16"/>
       <c r="AC64" s="8"/>
       <c r="AD64" s="9"/>
-      <c r="AF64" s="37"/>
+      <c r="AF64" s="39"/>
       <c r="AG64" s="16"/>
       <c r="AH64" s="8"/>
       <c r="AI64" s="9"/>
@@ -14392,7 +14425,7 @@
       <c r="AR64" s="9"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="D65" s="37"/>
+      <c r="D65" s="39"/>
       <c r="E65" s="18"/>
       <c r="F65" s="8"/>
       <c r="G65" s="9"/>
@@ -14405,7 +14438,7 @@
       <c r="N65" s="18"/>
       <c r="O65" s="8"/>
       <c r="P65" s="9"/>
-      <c r="R65" s="37"/>
+      <c r="R65" s="39"/>
       <c r="S65" s="18"/>
       <c r="T65" s="8"/>
       <c r="U65" s="9"/>
@@ -14418,7 +14451,7 @@
       <c r="AB65" s="18"/>
       <c r="AC65" s="8"/>
       <c r="AD65" s="9"/>
-      <c r="AF65" s="37"/>
+      <c r="AF65" s="39"/>
       <c r="AG65" s="18"/>
       <c r="AH65" s="8"/>
       <c r="AI65" s="9"/>
@@ -14433,7 +14466,7 @@
       <c r="AR65" s="9"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="D66" s="37"/>
+      <c r="D66" s="39"/>
       <c r="E66" s="16"/>
       <c r="F66" s="8"/>
       <c r="G66" s="9"/>
@@ -14446,7 +14479,7 @@
       <c r="N66" s="16"/>
       <c r="O66" s="8"/>
       <c r="P66" s="9"/>
-      <c r="R66" s="37"/>
+      <c r="R66" s="39"/>
       <c r="S66" s="16"/>
       <c r="T66" s="8"/>
       <c r="U66" s="9"/>
@@ -14459,7 +14492,7 @@
       <c r="AB66" s="16"/>
       <c r="AC66" s="8"/>
       <c r="AD66" s="9"/>
-      <c r="AF66" s="37"/>
+      <c r="AF66" s="39"/>
       <c r="AG66" s="16"/>
       <c r="AH66" s="8"/>
       <c r="AI66" s="9"/>
@@ -14474,7 +14507,7 @@
       <c r="AR66" s="9"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="D67" s="37"/>
+      <c r="D67" s="39"/>
       <c r="E67" s="18"/>
       <c r="F67" s="8"/>
       <c r="G67" s="9"/>
@@ -14487,7 +14520,7 @@
       <c r="N67" s="18"/>
       <c r="O67" s="8"/>
       <c r="P67" s="9"/>
-      <c r="R67" s="37"/>
+      <c r="R67" s="39"/>
       <c r="S67" s="18"/>
       <c r="T67" s="8"/>
       <c r="U67" s="9"/>
@@ -14500,7 +14533,7 @@
       <c r="AB67" s="18"/>
       <c r="AC67" s="8"/>
       <c r="AD67" s="9"/>
-      <c r="AF67" s="37"/>
+      <c r="AF67" s="39"/>
       <c r="AG67" s="18"/>
       <c r="AH67" s="8"/>
       <c r="AI67" s="9"/>
@@ -14515,7 +14548,7 @@
       <c r="AR67" s="9"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="D68" s="37"/>
+      <c r="D68" s="39"/>
       <c r="E68" s="16"/>
       <c r="F68" s="8"/>
       <c r="G68" s="9"/>
@@ -14528,7 +14561,7 @@
       <c r="N68" s="16"/>
       <c r="O68" s="8"/>
       <c r="P68" s="9"/>
-      <c r="R68" s="37"/>
+      <c r="R68" s="39"/>
       <c r="S68" s="16"/>
       <c r="T68" s="8"/>
       <c r="U68" s="9"/>
@@ -14541,7 +14574,7 @@
       <c r="AB68" s="16"/>
       <c r="AC68" s="8"/>
       <c r="AD68" s="9"/>
-      <c r="AF68" s="37"/>
+      <c r="AF68" s="39"/>
       <c r="AG68" s="16"/>
       <c r="AH68" s="8"/>
       <c r="AI68" s="9"/>
@@ -14556,7 +14589,7 @@
       <c r="AR68" s="9"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="D69" s="37"/>
+      <c r="D69" s="39"/>
       <c r="E69" s="18"/>
       <c r="F69" s="8"/>
       <c r="G69" s="9"/>
@@ -14569,7 +14602,7 @@
       <c r="N69" s="18"/>
       <c r="O69" s="8"/>
       <c r="P69" s="9"/>
-      <c r="R69" s="37"/>
+      <c r="R69" s="39"/>
       <c r="S69" s="18"/>
       <c r="T69" s="8"/>
       <c r="U69" s="9"/>
@@ -14582,7 +14615,7 @@
       <c r="AB69" s="18"/>
       <c r="AC69" s="8"/>
       <c r="AD69" s="9"/>
-      <c r="AF69" s="37"/>
+      <c r="AF69" s="39"/>
       <c r="AG69" s="18"/>
       <c r="AH69" s="8"/>
       <c r="AI69" s="9"/>
@@ -14597,7 +14630,7 @@
       <c r="AR69" s="9"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="D70" s="37"/>
+      <c r="D70" s="39"/>
       <c r="E70" s="16"/>
       <c r="F70" s="8"/>
       <c r="G70" s="9"/>
@@ -14610,7 +14643,7 @@
       <c r="N70" s="16"/>
       <c r="O70" s="8"/>
       <c r="P70" s="9"/>
-      <c r="R70" s="37"/>
+      <c r="R70" s="39"/>
       <c r="S70" s="16"/>
       <c r="T70" s="8"/>
       <c r="U70" s="9"/>
@@ -14623,7 +14656,7 @@
       <c r="AB70" s="16"/>
       <c r="AC70" s="8"/>
       <c r="AD70" s="9"/>
-      <c r="AF70" s="37"/>
+      <c r="AF70" s="39"/>
       <c r="AG70" s="16"/>
       <c r="AH70" s="8"/>
       <c r="AI70" s="9"/>
@@ -14638,20 +14671,20 @@
       <c r="AR70" s="9"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="D71" s="37"/>
+      <c r="D71" s="39"/>
       <c r="E71" s="25"/>
       <c r="F71" s="22"/>
       <c r="G71" s="23"/>
-      <c r="H71" s="31"/>
+      <c r="H71" s="33"/>
       <c r="I71" s="22"/>
       <c r="J71" s="23"/>
-      <c r="K71" s="31"/>
+      <c r="K71" s="33"/>
       <c r="L71" s="22"/>
       <c r="M71" s="23"/>
       <c r="N71" s="18"/>
       <c r="O71" s="8"/>
       <c r="P71" s="9"/>
-      <c r="R71" s="37"/>
+      <c r="R71" s="39"/>
       <c r="S71" s="18"/>
       <c r="T71" s="8"/>
       <c r="U71" s="9"/>
@@ -14664,7 +14697,7 @@
       <c r="AB71" s="18"/>
       <c r="AC71" s="8"/>
       <c r="AD71" s="9"/>
-      <c r="AF71" s="37"/>
+      <c r="AF71" s="39"/>
       <c r="AG71" s="18"/>
       <c r="AH71" s="8"/>
       <c r="AI71" s="9"/>
@@ -14679,7 +14712,7 @@
       <c r="AR71" s="9"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="D72" s="37"/>
+      <c r="D72" s="39"/>
       <c r="E72" s="21"/>
       <c r="F72" s="22"/>
       <c r="G72" s="23"/>
@@ -14692,7 +14725,7 @@
       <c r="N72" s="16"/>
       <c r="O72" s="8"/>
       <c r="P72" s="9"/>
-      <c r="R72" s="37"/>
+      <c r="R72" s="39"/>
       <c r="S72" s="16"/>
       <c r="T72" s="8"/>
       <c r="U72" s="9"/>
@@ -14705,7 +14738,7 @@
       <c r="AB72" s="16"/>
       <c r="AC72" s="8"/>
       <c r="AD72" s="9"/>
-      <c r="AF72" s="37"/>
+      <c r="AF72" s="39"/>
       <c r="AG72" s="16"/>
       <c r="AH72" s="8"/>
       <c r="AI72" s="9"/>
@@ -14720,20 +14753,20 @@
       <c r="AR72" s="9"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="D73" s="37"/>
+      <c r="D73" s="39"/>
       <c r="E73" s="25"/>
       <c r="F73" s="22"/>
       <c r="G73" s="23"/>
-      <c r="H73" s="31"/>
+      <c r="H73" s="33"/>
       <c r="I73" s="22"/>
       <c r="J73" s="23"/>
-      <c r="K73" s="31"/>
+      <c r="K73" s="33"/>
       <c r="L73" s="22"/>
       <c r="M73" s="23"/>
       <c r="N73" s="18"/>
       <c r="O73" s="8"/>
       <c r="P73" s="9"/>
-      <c r="R73" s="37"/>
+      <c r="R73" s="39"/>
       <c r="S73" s="18"/>
       <c r="T73" s="8"/>
       <c r="U73" s="9"/>
@@ -14746,7 +14779,7 @@
       <c r="AB73" s="18"/>
       <c r="AC73" s="8"/>
       <c r="AD73" s="9"/>
-      <c r="AF73" s="37"/>
+      <c r="AF73" s="39"/>
       <c r="AG73" s="18"/>
       <c r="AH73" s="8"/>
       <c r="AI73" s="9"/>
@@ -14761,7 +14794,7 @@
       <c r="AR73" s="9"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="D74" s="37"/>
+      <c r="D74" s="39"/>
       <c r="E74" s="21"/>
       <c r="F74" s="22"/>
       <c r="G74" s="23"/>
@@ -14774,7 +14807,7 @@
       <c r="N74" s="16"/>
       <c r="O74" s="8"/>
       <c r="P74" s="9"/>
-      <c r="R74" s="37"/>
+      <c r="R74" s="39"/>
       <c r="S74" s="16"/>
       <c r="T74" s="8"/>
       <c r="U74" s="9"/>
@@ -14787,7 +14820,7 @@
       <c r="AB74" s="16"/>
       <c r="AC74" s="8"/>
       <c r="AD74" s="9"/>
-      <c r="AF74" s="37"/>
+      <c r="AF74" s="39"/>
       <c r="AG74" s="16"/>
       <c r="AH74" s="8"/>
       <c r="AI74" s="9"/>
@@ -14802,20 +14835,20 @@
       <c r="AR74" s="9"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="D75" s="37"/>
+      <c r="D75" s="39"/>
       <c r="E75" s="25"/>
       <c r="F75" s="22"/>
       <c r="G75" s="23"/>
-      <c r="H75" s="31"/>
+      <c r="H75" s="33"/>
       <c r="I75" s="22"/>
       <c r="J75" s="23"/>
-      <c r="K75" s="31"/>
+      <c r="K75" s="33"/>
       <c r="L75" s="22"/>
       <c r="M75" s="23"/>
       <c r="N75" s="18"/>
       <c r="O75" s="8"/>
       <c r="P75" s="9"/>
-      <c r="R75" s="37"/>
+      <c r="R75" s="39"/>
       <c r="S75" s="18"/>
       <c r="T75" s="8"/>
       <c r="U75" s="9"/>
@@ -14828,7 +14861,7 @@
       <c r="AB75" s="18"/>
       <c r="AC75" s="8"/>
       <c r="AD75" s="9"/>
-      <c r="AF75" s="37"/>
+      <c r="AF75" s="39"/>
       <c r="AG75" s="18"/>
       <c r="AH75" s="8"/>
       <c r="AI75" s="9"/>
@@ -14843,7 +14876,7 @@
       <c r="AR75" s="9"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="D76" s="37"/>
+      <c r="D76" s="39"/>
       <c r="E76" s="21"/>
       <c r="F76" s="22"/>
       <c r="G76" s="23"/>
@@ -14856,7 +14889,7 @@
       <c r="N76" s="16"/>
       <c r="O76" s="8"/>
       <c r="P76" s="9"/>
-      <c r="R76" s="37"/>
+      <c r="R76" s="39"/>
       <c r="S76" s="16"/>
       <c r="T76" s="8"/>
       <c r="U76" s="9"/>
@@ -14869,7 +14902,7 @@
       <c r="AB76" s="16"/>
       <c r="AC76" s="8"/>
       <c r="AD76" s="9"/>
-      <c r="AF76" s="37"/>
+      <c r="AF76" s="39"/>
       <c r="AG76" s="16"/>
       <c r="AH76" s="8"/>
       <c r="AI76" s="9"/>
@@ -14884,7 +14917,7 @@
       <c r="AR76" s="9"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="D77" s="37"/>
+      <c r="D77" s="39"/>
       <c r="E77" s="25"/>
       <c r="F77" s="22"/>
       <c r="G77" s="23"/>
@@ -14897,7 +14930,7 @@
       <c r="N77" s="18"/>
       <c r="O77" s="8"/>
       <c r="P77" s="9"/>
-      <c r="R77" s="37"/>
+      <c r="R77" s="39"/>
       <c r="S77" s="18"/>
       <c r="T77" s="8"/>
       <c r="U77" s="9"/>
@@ -14910,7 +14943,7 @@
       <c r="AB77" s="18"/>
       <c r="AC77" s="8"/>
       <c r="AD77" s="9"/>
-      <c r="AF77" s="37"/>
+      <c r="AF77" s="39"/>
       <c r="AG77" s="18"/>
       <c r="AH77" s="8"/>
       <c r="AI77" s="9"/>
@@ -14925,7 +14958,7 @@
       <c r="AR77" s="9"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="D78" s="37"/>
+      <c r="D78" s="39"/>
       <c r="E78" s="21"/>
       <c r="F78" s="22"/>
       <c r="G78" s="23"/>
@@ -14938,7 +14971,7 @@
       <c r="N78" s="16"/>
       <c r="O78" s="8"/>
       <c r="P78" s="9"/>
-      <c r="R78" s="37"/>
+      <c r="R78" s="39"/>
       <c r="S78" s="16"/>
       <c r="T78" s="8"/>
       <c r="U78" s="9"/>
@@ -14951,7 +14984,7 @@
       <c r="AB78" s="16"/>
       <c r="AC78" s="8"/>
       <c r="AD78" s="9"/>
-      <c r="AF78" s="37"/>
+      <c r="AF78" s="39"/>
       <c r="AG78" s="16"/>
       <c r="AH78" s="8"/>
       <c r="AI78" s="9"/>
@@ -14966,7 +14999,7 @@
       <c r="AR78" s="9"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="D79" s="37"/>
+      <c r="D79" s="39"/>
       <c r="E79" s="25"/>
       <c r="F79" s="22"/>
       <c r="G79" s="23"/>
@@ -14979,7 +15012,7 @@
       <c r="N79" s="18"/>
       <c r="O79" s="8"/>
       <c r="P79" s="9"/>
-      <c r="R79" s="37"/>
+      <c r="R79" s="39"/>
       <c r="S79" s="18"/>
       <c r="T79" s="8"/>
       <c r="U79" s="9"/>
@@ -14992,7 +15025,7 @@
       <c r="AB79" s="18"/>
       <c r="AC79" s="8"/>
       <c r="AD79" s="9"/>
-      <c r="AF79" s="37"/>
+      <c r="AF79" s="39"/>
       <c r="AG79" s="18"/>
       <c r="AH79" s="8"/>
       <c r="AI79" s="9"/>
@@ -15007,7 +15040,7 @@
       <c r="AR79" s="9"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="D80" s="37"/>
+      <c r="D80" s="39"/>
       <c r="E80" s="16"/>
       <c r="F80" s="8"/>
       <c r="G80" s="9"/>
@@ -15020,7 +15053,7 @@
       <c r="N80" s="16"/>
       <c r="O80" s="8"/>
       <c r="P80" s="9"/>
-      <c r="R80" s="37"/>
+      <c r="R80" s="39"/>
       <c r="S80" s="16"/>
       <c r="T80" s="8"/>
       <c r="U80" s="9"/>
@@ -15033,7 +15066,7 @@
       <c r="AB80" s="16"/>
       <c r="AC80" s="8"/>
       <c r="AD80" s="9"/>
-      <c r="AF80" s="37"/>
+      <c r="AF80" s="39"/>
       <c r="AG80" s="16"/>
       <c r="AH80" s="8"/>
       <c r="AI80" s="9"/>
@@ -15048,7 +15081,7 @@
       <c r="AR80" s="9"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="D81" s="37"/>
+      <c r="D81" s="39"/>
       <c r="E81" s="18"/>
       <c r="F81" s="8"/>
       <c r="G81" s="9"/>
@@ -15061,7 +15094,7 @@
       <c r="N81" s="18"/>
       <c r="O81" s="8"/>
       <c r="P81" s="9"/>
-      <c r="R81" s="37"/>
+      <c r="R81" s="39"/>
       <c r="S81" s="18"/>
       <c r="T81" s="8"/>
       <c r="U81" s="9"/>
@@ -15074,7 +15107,7 @@
       <c r="AB81" s="18"/>
       <c r="AC81" s="8"/>
       <c r="AD81" s="9"/>
-      <c r="AF81" s="37"/>
+      <c r="AF81" s="39"/>
       <c r="AG81" s="18"/>
       <c r="AH81" s="8"/>
       <c r="AI81" s="9"/>
@@ -16979,10 +17012,10 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -16990,7 +17023,7 @@
     <row r="2" ht="15.75" customHeight="1"/>
     <row r="3" ht="15.75" customHeight="1">
       <c r="D3" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E3" s="4"/>
     </row>
@@ -17000,11 +17033,11 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="R4" s="33" t="s">
+      <c r="R4" s="35" t="s">
         <v>4</v>
       </c>
       <c r="S4" s="2"/>
-      <c r="AF4" s="34" t="s">
+      <c r="AF4" s="36" t="s">
         <v>5</v>
       </c>
       <c r="AG4" s="2"/>
@@ -17015,11 +17048,11 @@
         <v>6</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="37" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="9"/>
@@ -17034,16 +17067,16 @@
       <c r="L5" s="8"/>
       <c r="M5" s="9"/>
       <c r="N5" s="13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="2"/>
-      <c r="R5" s="35" t="s">
+      <c r="R5" s="37" t="s">
         <v>7</v>
       </c>
       <c r="S5" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="T5" s="8"/>
       <c r="U5" s="9"/>
@@ -17058,15 +17091,15 @@
       <c r="Z5" s="8"/>
       <c r="AA5" s="9"/>
       <c r="AB5" s="13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AC5" s="8"/>
       <c r="AD5" s="9"/>
-      <c r="AF5" s="35" t="s">
+      <c r="AF5" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="AG5" s="36" t="s">
-        <v>133</v>
+      <c r="AG5" s="38" t="s">
+        <v>138</v>
       </c>
       <c r="AH5" s="22"/>
       <c r="AI5" s="23"/>
@@ -17081,7 +17114,7 @@
       <c r="AN5" s="8"/>
       <c r="AO5" s="9"/>
       <c r="AP5" s="13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AQ5" s="8"/>
       <c r="AR5" s="9"/>
@@ -17091,21 +17124,21 @@
         <v>11</v>
       </c>
       <c r="B6" s="9"/>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="39" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
       <c r="H6" s="16" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="9"/>
       <c r="K6" s="16" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="9"/>
@@ -17113,7 +17146,7 @@
       <c r="O6" s="8"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="37"/>
+      <c r="R6" s="39"/>
       <c r="S6" s="16"/>
       <c r="T6" s="8"/>
       <c r="U6" s="9"/>
@@ -17126,7 +17159,7 @@
       <c r="AB6" s="16"/>
       <c r="AC6" s="8"/>
       <c r="AD6" s="9"/>
-      <c r="AF6" s="37"/>
+      <c r="AF6" s="39"/>
       <c r="AG6" s="16"/>
       <c r="AH6" s="8"/>
       <c r="AI6" s="9"/>
@@ -17145,19 +17178,19 @@
         <v>16</v>
       </c>
       <c r="B7" s="9"/>
-      <c r="D7" s="37"/>
+      <c r="D7" s="39"/>
       <c r="E7" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="9"/>
       <c r="H7" s="18" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="9"/>
       <c r="K7" s="18" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="9"/>
@@ -17165,7 +17198,7 @@
       <c r="O7" s="8"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="37"/>
+      <c r="R7" s="39"/>
       <c r="S7" s="18"/>
       <c r="T7" s="8"/>
       <c r="U7" s="9"/>
@@ -17178,7 +17211,7 @@
       <c r="AB7" s="18"/>
       <c r="AC7" s="8"/>
       <c r="AD7" s="9"/>
-      <c r="AF7" s="37"/>
+      <c r="AF7" s="39"/>
       <c r="AG7" s="18"/>
       <c r="AH7" s="8"/>
       <c r="AI7" s="9"/>
@@ -17197,7 +17230,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="9"/>
-      <c r="D8" s="37"/>
+      <c r="D8" s="39"/>
       <c r="E8" s="16"/>
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
@@ -17211,7 +17244,7 @@
       <c r="O8" s="8"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="2"/>
-      <c r="R8" s="37"/>
+      <c r="R8" s="39"/>
       <c r="S8" s="16"/>
       <c r="T8" s="8"/>
       <c r="U8" s="9"/>
@@ -17224,7 +17257,7 @@
       <c r="AB8" s="16"/>
       <c r="AC8" s="8"/>
       <c r="AD8" s="9"/>
-      <c r="AF8" s="37"/>
+      <c r="AF8" s="39"/>
       <c r="AG8" s="16"/>
       <c r="AH8" s="8"/>
       <c r="AI8" s="9"/>
@@ -17239,7 +17272,7 @@
       <c r="AR8" s="9"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="D9" s="37"/>
+      <c r="D9" s="39"/>
       <c r="E9" s="18"/>
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
@@ -17253,7 +17286,7 @@
       <c r="O9" s="8"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="2"/>
-      <c r="R9" s="37"/>
+      <c r="R9" s="39"/>
       <c r="S9" s="18"/>
       <c r="T9" s="8"/>
       <c r="U9" s="9"/>
@@ -17266,7 +17299,7 @@
       <c r="AB9" s="18"/>
       <c r="AC9" s="8"/>
       <c r="AD9" s="9"/>
-      <c r="AF9" s="37"/>
+      <c r="AF9" s="39"/>
       <c r="AG9" s="18"/>
       <c r="AH9" s="8"/>
       <c r="AI9" s="9"/>
@@ -17281,7 +17314,7 @@
       <c r="AR9" s="9"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="D10" s="37"/>
+      <c r="D10" s="39"/>
       <c r="E10" s="16"/>
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
@@ -17295,7 +17328,7 @@
       <c r="O10" s="8"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="37"/>
+      <c r="R10" s="39"/>
       <c r="S10" s="16"/>
       <c r="T10" s="8"/>
       <c r="U10" s="9"/>
@@ -17308,7 +17341,7 @@
       <c r="AB10" s="16"/>
       <c r="AC10" s="8"/>
       <c r="AD10" s="9"/>
-      <c r="AF10" s="37"/>
+      <c r="AF10" s="39"/>
       <c r="AG10" s="16"/>
       <c r="AH10" s="8"/>
       <c r="AI10" s="9"/>
@@ -17324,10 +17357,10 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="D11" s="37"/>
+      <c r="D11" s="39"/>
       <c r="E11" s="18"/>
       <c r="F11" s="8"/>
       <c r="G11" s="9"/>
@@ -17341,7 +17374,7 @@
       <c r="O11" s="8"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="2"/>
-      <c r="R11" s="37"/>
+      <c r="R11" s="39"/>
       <c r="S11" s="18"/>
       <c r="T11" s="8"/>
       <c r="U11" s="9"/>
@@ -17354,7 +17387,7 @@
       <c r="AB11" s="18"/>
       <c r="AC11" s="8"/>
       <c r="AD11" s="9"/>
-      <c r="AF11" s="37"/>
+      <c r="AF11" s="39"/>
       <c r="AG11" s="18"/>
       <c r="AH11" s="8"/>
       <c r="AI11" s="9"/>
@@ -17369,7 +17402,7 @@
       <c r="AR11" s="9"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="D12" s="37"/>
+      <c r="D12" s="39"/>
       <c r="E12" s="16"/>
       <c r="F12" s="8"/>
       <c r="G12" s="9"/>
@@ -17383,7 +17416,7 @@
       <c r="O12" s="8"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="2"/>
-      <c r="R12" s="37"/>
+      <c r="R12" s="39"/>
       <c r="S12" s="16"/>
       <c r="T12" s="8"/>
       <c r="U12" s="9"/>
@@ -17396,7 +17429,7 @@
       <c r="AB12" s="16"/>
       <c r="AC12" s="8"/>
       <c r="AD12" s="9"/>
-      <c r="AF12" s="37"/>
+      <c r="AF12" s="39"/>
       <c r="AG12" s="16"/>
       <c r="AH12" s="8"/>
       <c r="AI12" s="9"/>
@@ -17411,7 +17444,7 @@
       <c r="AR12" s="9"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="D13" s="37"/>
+      <c r="D13" s="39"/>
       <c r="E13" s="18"/>
       <c r="F13" s="8"/>
       <c r="G13" s="9"/>
@@ -17425,7 +17458,7 @@
       <c r="O13" s="8"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="2"/>
-      <c r="R13" s="37"/>
+      <c r="R13" s="39"/>
       <c r="S13" s="18"/>
       <c r="T13" s="8"/>
       <c r="U13" s="9"/>
@@ -17438,7 +17471,7 @@
       <c r="AB13" s="18"/>
       <c r="AC13" s="8"/>
       <c r="AD13" s="9"/>
-      <c r="AF13" s="37"/>
+      <c r="AF13" s="39"/>
       <c r="AG13" s="18"/>
       <c r="AH13" s="8"/>
       <c r="AI13" s="9"/>
@@ -17453,7 +17486,7 @@
       <c r="AR13" s="9"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="D14" s="37"/>
+      <c r="D14" s="39"/>
       <c r="E14" s="16"/>
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
@@ -17467,7 +17500,7 @@
       <c r="O14" s="8"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="2"/>
-      <c r="R14" s="37"/>
+      <c r="R14" s="39"/>
       <c r="S14" s="16"/>
       <c r="T14" s="8"/>
       <c r="U14" s="9"/>
@@ -17480,7 +17513,7 @@
       <c r="AB14" s="16"/>
       <c r="AC14" s="8"/>
       <c r="AD14" s="9"/>
-      <c r="AF14" s="37"/>
+      <c r="AF14" s="39"/>
       <c r="AG14" s="16"/>
       <c r="AH14" s="8"/>
       <c r="AI14" s="9"/>
@@ -17496,10 +17529,10 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="D15" s="37"/>
+      <c r="D15" s="39"/>
       <c r="E15" s="18"/>
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
@@ -17513,7 +17546,7 @@
       <c r="O15" s="8"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="37"/>
+      <c r="R15" s="39"/>
       <c r="S15" s="18"/>
       <c r="T15" s="8"/>
       <c r="U15" s="9"/>
@@ -17526,7 +17559,7 @@
       <c r="AB15" s="18"/>
       <c r="AC15" s="8"/>
       <c r="AD15" s="9"/>
-      <c r="AF15" s="37"/>
+      <c r="AF15" s="39"/>
       <c r="AG15" s="18"/>
       <c r="AH15" s="8"/>
       <c r="AI15" s="9"/>
@@ -17541,7 +17574,7 @@
       <c r="AR15" s="9"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="D16" s="37"/>
+      <c r="D16" s="39"/>
       <c r="E16" s="16"/>
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
@@ -17555,7 +17588,7 @@
       <c r="O16" s="8"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="37"/>
+      <c r="R16" s="39"/>
       <c r="S16" s="16"/>
       <c r="T16" s="8"/>
       <c r="U16" s="9"/>
@@ -17568,7 +17601,7 @@
       <c r="AB16" s="16"/>
       <c r="AC16" s="8"/>
       <c r="AD16" s="9"/>
-      <c r="AF16" s="37"/>
+      <c r="AF16" s="39"/>
       <c r="AG16" s="16"/>
       <c r="AH16" s="8"/>
       <c r="AI16" s="9"/>
@@ -17583,21 +17616,21 @@
       <c r="AR16" s="9"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="D17" s="37"/>
+      <c r="D17" s="39"/>
       <c r="E17" s="25"/>
       <c r="F17" s="22"/>
       <c r="G17" s="23"/>
-      <c r="H17" s="31"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="22"/>
       <c r="J17" s="23"/>
-      <c r="K17" s="31"/>
+      <c r="K17" s="33"/>
       <c r="L17" s="22"/>
       <c r="M17" s="23"/>
       <c r="N17" s="18"/>
       <c r="O17" s="8"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="37"/>
+      <c r="R17" s="39"/>
       <c r="S17" s="18"/>
       <c r="T17" s="8"/>
       <c r="U17" s="9"/>
@@ -17610,7 +17643,7 @@
       <c r="AB17" s="18"/>
       <c r="AC17" s="8"/>
       <c r="AD17" s="9"/>
-      <c r="AF17" s="37"/>
+      <c r="AF17" s="39"/>
       <c r="AG17" s="18"/>
       <c r="AH17" s="8"/>
       <c r="AI17" s="9"/>
@@ -17625,7 +17658,7 @@
       <c r="AR17" s="9"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="D18" s="37"/>
+      <c r="D18" s="39"/>
       <c r="E18" s="21"/>
       <c r="F18" s="22"/>
       <c r="G18" s="23"/>
@@ -17639,7 +17672,7 @@
       <c r="O18" s="8"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="2"/>
-      <c r="R18" s="37"/>
+      <c r="R18" s="39"/>
       <c r="S18" s="16"/>
       <c r="T18" s="8"/>
       <c r="U18" s="9"/>
@@ -17652,7 +17685,7 @@
       <c r="AB18" s="16"/>
       <c r="AC18" s="8"/>
       <c r="AD18" s="9"/>
-      <c r="AF18" s="37"/>
+      <c r="AF18" s="39"/>
       <c r="AG18" s="16"/>
       <c r="AH18" s="8"/>
       <c r="AI18" s="9"/>
@@ -17667,21 +17700,21 @@
       <c r="AR18" s="9"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="D19" s="37"/>
+      <c r="D19" s="39"/>
       <c r="E19" s="25"/>
       <c r="F19" s="22"/>
       <c r="G19" s="23"/>
-      <c r="H19" s="31"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="22"/>
       <c r="J19" s="23"/>
-      <c r="K19" s="31"/>
+      <c r="K19" s="33"/>
       <c r="L19" s="22"/>
       <c r="M19" s="23"/>
       <c r="N19" s="18"/>
       <c r="O19" s="8"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="2"/>
-      <c r="R19" s="37"/>
+      <c r="R19" s="39"/>
       <c r="S19" s="18"/>
       <c r="T19" s="8"/>
       <c r="U19" s="9"/>
@@ -17694,7 +17727,7 @@
       <c r="AB19" s="18"/>
       <c r="AC19" s="8"/>
       <c r="AD19" s="9"/>
-      <c r="AF19" s="37"/>
+      <c r="AF19" s="39"/>
       <c r="AG19" s="18"/>
       <c r="AH19" s="8"/>
       <c r="AI19" s="9"/>
@@ -17709,7 +17742,7 @@
       <c r="AR19" s="9"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="D20" s="37"/>
+      <c r="D20" s="39"/>
       <c r="E20" s="16"/>
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
@@ -17723,7 +17756,7 @@
       <c r="O20" s="8"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
-      <c r="R20" s="37"/>
+      <c r="R20" s="39"/>
       <c r="S20" s="16"/>
       <c r="T20" s="8"/>
       <c r="U20" s="9"/>
@@ -17736,7 +17769,7 @@
       <c r="AB20" s="16"/>
       <c r="AC20" s="8"/>
       <c r="AD20" s="9"/>
-      <c r="AF20" s="37"/>
+      <c r="AF20" s="39"/>
       <c r="AG20" s="16"/>
       <c r="AH20" s="8"/>
       <c r="AI20" s="9"/>
@@ -17751,7 +17784,7 @@
       <c r="AR20" s="9"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="D21" s="37"/>
+      <c r="D21" s="39"/>
       <c r="E21" s="18"/>
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
@@ -17765,7 +17798,7 @@
       <c r="O21" s="8"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="2"/>
-      <c r="R21" s="37"/>
+      <c r="R21" s="39"/>
       <c r="S21" s="18"/>
       <c r="T21" s="8"/>
       <c r="U21" s="9"/>
@@ -17778,7 +17811,7 @@
       <c r="AB21" s="18"/>
       <c r="AC21" s="8"/>
       <c r="AD21" s="9"/>
-      <c r="AF21" s="37"/>
+      <c r="AF21" s="39"/>
       <c r="AG21" s="18"/>
       <c r="AH21" s="8"/>
       <c r="AI21" s="9"/>
@@ -17793,7 +17826,7 @@
       <c r="AR21" s="9"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="D22" s="37"/>
+      <c r="D22" s="39"/>
       <c r="E22" s="16"/>
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
@@ -17807,7 +17840,7 @@
       <c r="O22" s="8"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="2"/>
-      <c r="R22" s="37"/>
+      <c r="R22" s="39"/>
       <c r="S22" s="16"/>
       <c r="T22" s="8"/>
       <c r="U22" s="9"/>
@@ -17820,7 +17853,7 @@
       <c r="AB22" s="16"/>
       <c r="AC22" s="8"/>
       <c r="AD22" s="9"/>
-      <c r="AF22" s="37"/>
+      <c r="AF22" s="39"/>
       <c r="AG22" s="16"/>
       <c r="AH22" s="8"/>
       <c r="AI22" s="9"/>
@@ -17835,7 +17868,7 @@
       <c r="AR22" s="9"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="D23" s="37"/>
+      <c r="D23" s="39"/>
       <c r="E23" s="18"/>
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
@@ -17849,7 +17882,7 @@
       <c r="O23" s="8"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="2"/>
-      <c r="R23" s="37"/>
+      <c r="R23" s="39"/>
       <c r="S23" s="18"/>
       <c r="T23" s="8"/>
       <c r="U23" s="9"/>
@@ -17862,7 +17895,7 @@
       <c r="AB23" s="18"/>
       <c r="AC23" s="8"/>
       <c r="AD23" s="9"/>
-      <c r="AF23" s="37"/>
+      <c r="AF23" s="39"/>
       <c r="AG23" s="18"/>
       <c r="AH23" s="8"/>
       <c r="AI23" s="9"/>
@@ -17877,7 +17910,7 @@
       <c r="AR23" s="9"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="D24" s="37"/>
+      <c r="D24" s="39"/>
       <c r="E24" s="16"/>
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
@@ -17891,7 +17924,7 @@
       <c r="O24" s="8"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="2"/>
-      <c r="R24" s="37"/>
+      <c r="R24" s="39"/>
       <c r="S24" s="16"/>
       <c r="T24" s="8"/>
       <c r="U24" s="9"/>
@@ -17904,7 +17937,7 @@
       <c r="AB24" s="16"/>
       <c r="AC24" s="8"/>
       <c r="AD24" s="9"/>
-      <c r="AF24" s="37"/>
+      <c r="AF24" s="39"/>
       <c r="AG24" s="16"/>
       <c r="AH24" s="8"/>
       <c r="AI24" s="9"/>
@@ -17919,7 +17952,7 @@
       <c r="AR24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="D25" s="37"/>
+      <c r="D25" s="39"/>
       <c r="E25" s="18"/>
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
@@ -17933,7 +17966,7 @@
       <c r="O25" s="8"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="2"/>
-      <c r="R25" s="37"/>
+      <c r="R25" s="39"/>
       <c r="S25" s="18"/>
       <c r="T25" s="8"/>
       <c r="U25" s="9"/>
@@ -17946,7 +17979,7 @@
       <c r="AB25" s="18"/>
       <c r="AC25" s="8"/>
       <c r="AD25" s="9"/>
-      <c r="AF25" s="37"/>
+      <c r="AF25" s="39"/>
       <c r="AG25" s="18"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="9"/>
@@ -17961,7 +17994,7 @@
       <c r="AR25" s="9"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="D26" s="37"/>
+      <c r="D26" s="39"/>
       <c r="E26" s="16"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
@@ -17975,7 +18008,7 @@
       <c r="O26" s="8"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="2"/>
-      <c r="R26" s="37"/>
+      <c r="R26" s="39"/>
       <c r="S26" s="16"/>
       <c r="T26" s="8"/>
       <c r="U26" s="9"/>
@@ -17988,7 +18021,7 @@
       <c r="AB26" s="16"/>
       <c r="AC26" s="8"/>
       <c r="AD26" s="9"/>
-      <c r="AF26" s="37"/>
+      <c r="AF26" s="39"/>
       <c r="AG26" s="16"/>
       <c r="AH26" s="8"/>
       <c r="AI26" s="9"/>
@@ -18003,7 +18036,7 @@
       <c r="AR26" s="9"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="D27" s="37"/>
+      <c r="D27" s="39"/>
       <c r="E27" s="18"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
@@ -18017,7 +18050,7 @@
       <c r="O27" s="8"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="2"/>
-      <c r="R27" s="37"/>
+      <c r="R27" s="39"/>
       <c r="S27" s="18"/>
       <c r="T27" s="8"/>
       <c r="U27" s="9"/>
@@ -18030,7 +18063,7 @@
       <c r="AB27" s="18"/>
       <c r="AC27" s="8"/>
       <c r="AD27" s="9"/>
-      <c r="AF27" s="37"/>
+      <c r="AF27" s="39"/>
       <c r="AG27" s="18"/>
       <c r="AH27" s="8"/>
       <c r="AI27" s="9"/>
@@ -18045,7 +18078,7 @@
       <c r="AR27" s="9"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="D28" s="37"/>
+      <c r="D28" s="39"/>
       <c r="E28" s="16"/>
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
@@ -18059,7 +18092,7 @@
       <c r="O28" s="8"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="2"/>
-      <c r="R28" s="37"/>
+      <c r="R28" s="39"/>
       <c r="S28" s="16"/>
       <c r="T28" s="8"/>
       <c r="U28" s="9"/>
@@ -18072,7 +18105,7 @@
       <c r="AB28" s="16"/>
       <c r="AC28" s="8"/>
       <c r="AD28" s="9"/>
-      <c r="AF28" s="37"/>
+      <c r="AF28" s="39"/>
       <c r="AG28" s="16"/>
       <c r="AH28" s="8"/>
       <c r="AI28" s="9"/>
@@ -18087,7 +18120,7 @@
       <c r="AR28" s="9"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="D29" s="37"/>
+      <c r="D29" s="39"/>
       <c r="E29" s="18"/>
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
@@ -18101,7 +18134,7 @@
       <c r="O29" s="8"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="2"/>
-      <c r="R29" s="37"/>
+      <c r="R29" s="39"/>
       <c r="S29" s="18"/>
       <c r="T29" s="8"/>
       <c r="U29" s="9"/>
@@ -18114,7 +18147,7 @@
       <c r="AB29" s="18"/>
       <c r="AC29" s="8"/>
       <c r="AD29" s="9"/>
-      <c r="AF29" s="37"/>
+      <c r="AF29" s="39"/>
       <c r="AG29" s="18"/>
       <c r="AH29" s="8"/>
       <c r="AI29" s="9"/>
@@ -18129,7 +18162,7 @@
       <c r="AR29" s="9"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="D30" s="37"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="16"/>
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
@@ -18143,7 +18176,7 @@
       <c r="O30" s="8"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="2"/>
-      <c r="R30" s="37"/>
+      <c r="R30" s="39"/>
       <c r="S30" s="16"/>
       <c r="T30" s="8"/>
       <c r="U30" s="9"/>
@@ -18156,7 +18189,7 @@
       <c r="AB30" s="16"/>
       <c r="AC30" s="8"/>
       <c r="AD30" s="9"/>
-      <c r="AF30" s="37"/>
+      <c r="AF30" s="39"/>
       <c r="AG30" s="16"/>
       <c r="AH30" s="8"/>
       <c r="AI30" s="9"/>
@@ -18171,7 +18204,7 @@
       <c r="AR30" s="9"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="D31" s="37"/>
+      <c r="D31" s="39"/>
       <c r="E31" s="18"/>
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
@@ -18185,7 +18218,7 @@
       <c r="O31" s="8"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="2"/>
-      <c r="R31" s="37"/>
+      <c r="R31" s="39"/>
       <c r="S31" s="18"/>
       <c r="T31" s="8"/>
       <c r="U31" s="9"/>
@@ -18198,7 +18231,7 @@
       <c r="AB31" s="18"/>
       <c r="AC31" s="8"/>
       <c r="AD31" s="9"/>
-      <c r="AF31" s="37"/>
+      <c r="AF31" s="39"/>
       <c r="AG31" s="18"/>
       <c r="AH31" s="8"/>
       <c r="AI31" s="9"/>
@@ -18213,7 +18246,7 @@
       <c r="AR31" s="9"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="D32" s="37"/>
+      <c r="D32" s="39"/>
       <c r="E32" s="16"/>
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
@@ -18227,7 +18260,7 @@
       <c r="O32" s="8"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="2"/>
-      <c r="R32" s="37"/>
+      <c r="R32" s="39"/>
       <c r="S32" s="16"/>
       <c r="T32" s="8"/>
       <c r="U32" s="9"/>
@@ -18240,7 +18273,7 @@
       <c r="AB32" s="16"/>
       <c r="AC32" s="8"/>
       <c r="AD32" s="9"/>
-      <c r="AF32" s="37"/>
+      <c r="AF32" s="39"/>
       <c r="AG32" s="16"/>
       <c r="AH32" s="8"/>
       <c r="AI32" s="9"/>
@@ -18255,7 +18288,7 @@
       <c r="AR32" s="9"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="D33" s="37"/>
+      <c r="D33" s="39"/>
       <c r="E33" s="18"/>
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
@@ -18269,7 +18302,7 @@
       <c r="O33" s="8"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="2"/>
-      <c r="R33" s="37"/>
+      <c r="R33" s="39"/>
       <c r="S33" s="18"/>
       <c r="T33" s="8"/>
       <c r="U33" s="9"/>
@@ -18282,7 +18315,7 @@
       <c r="AB33" s="18"/>
       <c r="AC33" s="8"/>
       <c r="AD33" s="9"/>
-      <c r="AF33" s="37"/>
+      <c r="AF33" s="39"/>
       <c r="AG33" s="18"/>
       <c r="AH33" s="8"/>
       <c r="AI33" s="9"/>
@@ -18297,7 +18330,7 @@
       <c r="AR33" s="9"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="D34" s="37"/>
+      <c r="D34" s="39"/>
       <c r="E34" s="16"/>
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
@@ -18311,7 +18344,7 @@
       <c r="O34" s="8"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="2"/>
-      <c r="R34" s="37"/>
+      <c r="R34" s="39"/>
       <c r="S34" s="16"/>
       <c r="T34" s="8"/>
       <c r="U34" s="9"/>
@@ -18324,7 +18357,7 @@
       <c r="AB34" s="16"/>
       <c r="AC34" s="8"/>
       <c r="AD34" s="9"/>
-      <c r="AF34" s="37"/>
+      <c r="AF34" s="39"/>
       <c r="AG34" s="16"/>
       <c r="AH34" s="8"/>
       <c r="AI34" s="9"/>
@@ -18339,7 +18372,7 @@
       <c r="AR34" s="9"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="D35" s="37"/>
+      <c r="D35" s="39"/>
       <c r="E35" s="18"/>
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
@@ -18353,7 +18386,7 @@
       <c r="O35" s="8"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="2"/>
-      <c r="R35" s="37"/>
+      <c r="R35" s="39"/>
       <c r="S35" s="18"/>
       <c r="T35" s="8"/>
       <c r="U35" s="9"/>
@@ -18366,7 +18399,7 @@
       <c r="AB35" s="18"/>
       <c r="AC35" s="8"/>
       <c r="AD35" s="9"/>
-      <c r="AF35" s="37"/>
+      <c r="AF35" s="39"/>
       <c r="AG35" s="18"/>
       <c r="AH35" s="8"/>
       <c r="AI35" s="9"/>
@@ -18381,7 +18414,7 @@
       <c r="AR35" s="9"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="D36" s="37"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="16"/>
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
@@ -18395,7 +18428,7 @@
       <c r="O36" s="8"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="2"/>
-      <c r="R36" s="37"/>
+      <c r="R36" s="39"/>
       <c r="S36" s="16"/>
       <c r="T36" s="8"/>
       <c r="U36" s="9"/>
@@ -18408,7 +18441,7 @@
       <c r="AB36" s="16"/>
       <c r="AC36" s="8"/>
       <c r="AD36" s="9"/>
-      <c r="AF36" s="37"/>
+      <c r="AF36" s="39"/>
       <c r="AG36" s="16"/>
       <c r="AH36" s="8"/>
       <c r="AI36" s="9"/>
@@ -18423,7 +18456,7 @@
       <c r="AR36" s="9"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="D37" s="37"/>
+      <c r="D37" s="39"/>
       <c r="E37" s="18"/>
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
@@ -18437,7 +18470,7 @@
       <c r="O37" s="8"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="2"/>
-      <c r="R37" s="37"/>
+      <c r="R37" s="39"/>
       <c r="S37" s="18"/>
       <c r="T37" s="8"/>
       <c r="U37" s="9"/>
@@ -18450,7 +18483,7 @@
       <c r="AB37" s="18"/>
       <c r="AC37" s="8"/>
       <c r="AD37" s="9"/>
-      <c r="AF37" s="37"/>
+      <c r="AF37" s="39"/>
       <c r="AG37" s="18"/>
       <c r="AH37" s="8"/>
       <c r="AI37" s="9"/>
@@ -18465,7 +18498,7 @@
       <c r="AR37" s="9"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="D38" s="37"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="16"/>
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
@@ -18479,7 +18512,7 @@
       <c r="O38" s="8"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="2"/>
-      <c r="R38" s="37"/>
+      <c r="R38" s="39"/>
       <c r="S38" s="16"/>
       <c r="T38" s="8"/>
       <c r="U38" s="9"/>
@@ -18492,7 +18525,7 @@
       <c r="AB38" s="16"/>
       <c r="AC38" s="8"/>
       <c r="AD38" s="9"/>
-      <c r="AF38" s="37"/>
+      <c r="AF38" s="39"/>
       <c r="AG38" s="16"/>
       <c r="AH38" s="8"/>
       <c r="AI38" s="9"/>
@@ -18507,7 +18540,7 @@
       <c r="AR38" s="9"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="D39" s="37"/>
+      <c r="D39" s="39"/>
       <c r="E39" s="18"/>
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
@@ -18521,7 +18554,7 @@
       <c r="O39" s="8"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="2"/>
-      <c r="R39" s="37"/>
+      <c r="R39" s="39"/>
       <c r="S39" s="18"/>
       <c r="T39" s="8"/>
       <c r="U39" s="9"/>
@@ -18534,7 +18567,7 @@
       <c r="AB39" s="18"/>
       <c r="AC39" s="8"/>
       <c r="AD39" s="9"/>
-      <c r="AF39" s="37"/>
+      <c r="AF39" s="39"/>
       <c r="AG39" s="18"/>
       <c r="AH39" s="8"/>
       <c r="AI39" s="9"/>
@@ -18549,7 +18582,7 @@
       <c r="AR39" s="9"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="D40" s="37"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="16"/>
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
@@ -18563,7 +18596,7 @@
       <c r="O40" s="8"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="2"/>
-      <c r="R40" s="37"/>
+      <c r="R40" s="39"/>
       <c r="S40" s="16"/>
       <c r="T40" s="8"/>
       <c r="U40" s="9"/>
@@ -18576,7 +18609,7 @@
       <c r="AB40" s="16"/>
       <c r="AC40" s="8"/>
       <c r="AD40" s="9"/>
-      <c r="AF40" s="37"/>
+      <c r="AF40" s="39"/>
       <c r="AG40" s="16"/>
       <c r="AH40" s="8"/>
       <c r="AI40" s="9"/>
@@ -18591,7 +18624,7 @@
       <c r="AR40" s="9"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="D41" s="37"/>
+      <c r="D41" s="39"/>
       <c r="E41" s="18"/>
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
@@ -18605,7 +18638,7 @@
       <c r="O41" s="8"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="2"/>
-      <c r="R41" s="37"/>
+      <c r="R41" s="39"/>
       <c r="S41" s="18"/>
       <c r="T41" s="8"/>
       <c r="U41" s="9"/>
@@ -18618,7 +18651,7 @@
       <c r="AB41" s="18"/>
       <c r="AC41" s="8"/>
       <c r="AD41" s="9"/>
-      <c r="AF41" s="37"/>
+      <c r="AF41" s="39"/>
       <c r="AG41" s="18"/>
       <c r="AH41" s="8"/>
       <c r="AI41" s="9"/>
@@ -18633,7 +18666,7 @@
       <c r="AR41" s="9"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="D42" s="37"/>
+      <c r="D42" s="39"/>
       <c r="E42" s="16"/>
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
@@ -18646,7 +18679,7 @@
       <c r="N42" s="16"/>
       <c r="O42" s="8"/>
       <c r="P42" s="9"/>
-      <c r="R42" s="37"/>
+      <c r="R42" s="39"/>
       <c r="S42" s="16"/>
       <c r="T42" s="8"/>
       <c r="U42" s="9"/>
@@ -18659,7 +18692,7 @@
       <c r="AB42" s="16"/>
       <c r="AC42" s="8"/>
       <c r="AD42" s="9"/>
-      <c r="AF42" s="37"/>
+      <c r="AF42" s="39"/>
       <c r="AG42" s="16"/>
       <c r="AH42" s="8"/>
       <c r="AI42" s="9"/>
@@ -18674,7 +18707,7 @@
       <c r="AR42" s="9"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="D43" s="37"/>
+      <c r="D43" s="39"/>
       <c r="E43" s="18"/>
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
@@ -18687,7 +18720,7 @@
       <c r="N43" s="18"/>
       <c r="O43" s="8"/>
       <c r="P43" s="9"/>
-      <c r="R43" s="37"/>
+      <c r="R43" s="39"/>
       <c r="S43" s="18"/>
       <c r="T43" s="8"/>
       <c r="U43" s="9"/>
@@ -18700,7 +18733,7 @@
       <c r="AB43" s="18"/>
       <c r="AC43" s="8"/>
       <c r="AD43" s="9"/>
-      <c r="AF43" s="37"/>
+      <c r="AF43" s="39"/>
       <c r="AG43" s="18"/>
       <c r="AH43" s="8"/>
       <c r="AI43" s="9"/>
@@ -18715,7 +18748,7 @@
       <c r="AR43" s="9"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="D44" s="37"/>
+      <c r="D44" s="39"/>
       <c r="E44" s="16"/>
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
@@ -18728,7 +18761,7 @@
       <c r="N44" s="16"/>
       <c r="O44" s="8"/>
       <c r="P44" s="9"/>
-      <c r="R44" s="37"/>
+      <c r="R44" s="39"/>
       <c r="S44" s="16"/>
       <c r="T44" s="8"/>
       <c r="U44" s="9"/>
@@ -18741,7 +18774,7 @@
       <c r="AB44" s="16"/>
       <c r="AC44" s="8"/>
       <c r="AD44" s="9"/>
-      <c r="AF44" s="37"/>
+      <c r="AF44" s="39"/>
       <c r="AG44" s="16"/>
       <c r="AH44" s="8"/>
       <c r="AI44" s="9"/>
@@ -18756,7 +18789,7 @@
       <c r="AR44" s="9"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="D45" s="37"/>
+      <c r="D45" s="39"/>
       <c r="E45" s="18"/>
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
@@ -18769,7 +18802,7 @@
       <c r="N45" s="18"/>
       <c r="O45" s="8"/>
       <c r="P45" s="9"/>
-      <c r="R45" s="37"/>
+      <c r="R45" s="39"/>
       <c r="S45" s="18"/>
       <c r="T45" s="8"/>
       <c r="U45" s="9"/>
@@ -18782,7 +18815,7 @@
       <c r="AB45" s="18"/>
       <c r="AC45" s="8"/>
       <c r="AD45" s="9"/>
-      <c r="AF45" s="37"/>
+      <c r="AF45" s="39"/>
       <c r="AG45" s="18"/>
       <c r="AH45" s="8"/>
       <c r="AI45" s="9"/>
@@ -18797,7 +18830,7 @@
       <c r="AR45" s="9"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="D46" s="37"/>
+      <c r="D46" s="39"/>
       <c r="E46" s="16"/>
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
@@ -18810,7 +18843,7 @@
       <c r="N46" s="16"/>
       <c r="O46" s="8"/>
       <c r="P46" s="9"/>
-      <c r="R46" s="37"/>
+      <c r="R46" s="39"/>
       <c r="S46" s="16"/>
       <c r="T46" s="8"/>
       <c r="U46" s="9"/>
@@ -18823,7 +18856,7 @@
       <c r="AB46" s="16"/>
       <c r="AC46" s="8"/>
       <c r="AD46" s="9"/>
-      <c r="AF46" s="37"/>
+      <c r="AF46" s="39"/>
       <c r="AG46" s="16"/>
       <c r="AH46" s="8"/>
       <c r="AI46" s="9"/>
@@ -18838,7 +18871,7 @@
       <c r="AR46" s="9"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="D47" s="37"/>
+      <c r="D47" s="39"/>
       <c r="E47" s="18"/>
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
@@ -18851,7 +18884,7 @@
       <c r="N47" s="18"/>
       <c r="O47" s="8"/>
       <c r="P47" s="9"/>
-      <c r="R47" s="37"/>
+      <c r="R47" s="39"/>
       <c r="S47" s="18"/>
       <c r="T47" s="8"/>
       <c r="U47" s="9"/>
@@ -18864,7 +18897,7 @@
       <c r="AB47" s="18"/>
       <c r="AC47" s="8"/>
       <c r="AD47" s="9"/>
-      <c r="AF47" s="37"/>
+      <c r="AF47" s="39"/>
       <c r="AG47" s="18"/>
       <c r="AH47" s="8"/>
       <c r="AI47" s="9"/>
@@ -18879,7 +18912,7 @@
       <c r="AR47" s="9"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="D48" s="37"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="21"/>
       <c r="F48" s="22"/>
       <c r="G48" s="23"/>
@@ -18892,7 +18925,7 @@
       <c r="N48" s="16"/>
       <c r="O48" s="8"/>
       <c r="P48" s="9"/>
-      <c r="R48" s="37"/>
+      <c r="R48" s="39"/>
       <c r="S48" s="16"/>
       <c r="T48" s="8"/>
       <c r="U48" s="9"/>
@@ -18905,7 +18938,7 @@
       <c r="AB48" s="16"/>
       <c r="AC48" s="8"/>
       <c r="AD48" s="9"/>
-      <c r="AF48" s="37"/>
+      <c r="AF48" s="39"/>
       <c r="AG48" s="16"/>
       <c r="AH48" s="8"/>
       <c r="AI48" s="9"/>
@@ -18920,7 +18953,7 @@
       <c r="AR48" s="9"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="D49" s="37"/>
+      <c r="D49" s="39"/>
       <c r="E49" s="25"/>
       <c r="F49" s="22"/>
       <c r="G49" s="23"/>
@@ -18933,7 +18966,7 @@
       <c r="N49" s="18"/>
       <c r="O49" s="8"/>
       <c r="P49" s="9"/>
-      <c r="R49" s="37"/>
+      <c r="R49" s="39"/>
       <c r="S49" s="18"/>
       <c r="T49" s="8"/>
       <c r="U49" s="9"/>
@@ -18946,7 +18979,7 @@
       <c r="AB49" s="18"/>
       <c r="AC49" s="8"/>
       <c r="AD49" s="9"/>
-      <c r="AF49" s="37"/>
+      <c r="AF49" s="39"/>
       <c r="AG49" s="18"/>
       <c r="AH49" s="8"/>
       <c r="AI49" s="9"/>
@@ -18961,7 +18994,7 @@
       <c r="AR49" s="9"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="D50" s="37"/>
+      <c r="D50" s="39"/>
       <c r="E50" s="21"/>
       <c r="F50" s="22"/>
       <c r="G50" s="23"/>
@@ -18974,7 +19007,7 @@
       <c r="N50" s="16"/>
       <c r="O50" s="8"/>
       <c r="P50" s="9"/>
-      <c r="R50" s="37"/>
+      <c r="R50" s="39"/>
       <c r="S50" s="16"/>
       <c r="T50" s="8"/>
       <c r="U50" s="9"/>
@@ -18987,7 +19020,7 @@
       <c r="AB50" s="16"/>
       <c r="AC50" s="8"/>
       <c r="AD50" s="9"/>
-      <c r="AF50" s="37"/>
+      <c r="AF50" s="39"/>
       <c r="AG50" s="16"/>
       <c r="AH50" s="8"/>
       <c r="AI50" s="9"/>
@@ -19002,7 +19035,7 @@
       <c r="AR50" s="9"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="D51" s="37"/>
+      <c r="D51" s="39"/>
       <c r="E51" s="18"/>
       <c r="F51" s="8"/>
       <c r="G51" s="9"/>
@@ -19015,7 +19048,7 @@
       <c r="N51" s="18"/>
       <c r="O51" s="8"/>
       <c r="P51" s="9"/>
-      <c r="R51" s="37"/>
+      <c r="R51" s="39"/>
       <c r="S51" s="18"/>
       <c r="T51" s="8"/>
       <c r="U51" s="9"/>
@@ -19028,7 +19061,7 @@
       <c r="AB51" s="18"/>
       <c r="AC51" s="8"/>
       <c r="AD51" s="9"/>
-      <c r="AF51" s="37"/>
+      <c r="AF51" s="39"/>
       <c r="AG51" s="18"/>
       <c r="AH51" s="8"/>
       <c r="AI51" s="9"/>
@@ -19043,7 +19076,7 @@
       <c r="AR51" s="9"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="D52" s="37"/>
+      <c r="D52" s="39"/>
       <c r="E52" s="16"/>
       <c r="F52" s="8"/>
       <c r="G52" s="9"/>
@@ -19056,7 +19089,7 @@
       <c r="N52" s="16"/>
       <c r="O52" s="8"/>
       <c r="P52" s="9"/>
-      <c r="R52" s="37"/>
+      <c r="R52" s="39"/>
       <c r="S52" s="16"/>
       <c r="T52" s="8"/>
       <c r="U52" s="9"/>
@@ -19069,7 +19102,7 @@
       <c r="AB52" s="16"/>
       <c r="AC52" s="8"/>
       <c r="AD52" s="9"/>
-      <c r="AF52" s="37"/>
+      <c r="AF52" s="39"/>
       <c r="AG52" s="16"/>
       <c r="AH52" s="8"/>
       <c r="AI52" s="9"/>
@@ -19084,7 +19117,7 @@
       <c r="AR52" s="9"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="D53" s="37"/>
+      <c r="D53" s="39"/>
       <c r="E53" s="18"/>
       <c r="F53" s="8"/>
       <c r="G53" s="9"/>
@@ -19097,7 +19130,7 @@
       <c r="N53" s="18"/>
       <c r="O53" s="8"/>
       <c r="P53" s="9"/>
-      <c r="R53" s="37"/>
+      <c r="R53" s="39"/>
       <c r="S53" s="18"/>
       <c r="T53" s="8"/>
       <c r="U53" s="9"/>
@@ -19110,7 +19143,7 @@
       <c r="AB53" s="18"/>
       <c r="AC53" s="8"/>
       <c r="AD53" s="9"/>
-      <c r="AF53" s="37"/>
+      <c r="AF53" s="39"/>
       <c r="AG53" s="18"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="9"/>
@@ -19125,7 +19158,7 @@
       <c r="AR53" s="9"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="D54" s="37"/>
+      <c r="D54" s="39"/>
       <c r="E54" s="16"/>
       <c r="F54" s="8"/>
       <c r="G54" s="9"/>
@@ -19138,7 +19171,7 @@
       <c r="N54" s="16"/>
       <c r="O54" s="8"/>
       <c r="P54" s="9"/>
-      <c r="R54" s="37"/>
+      <c r="R54" s="39"/>
       <c r="S54" s="16"/>
       <c r="T54" s="8"/>
       <c r="U54" s="9"/>
@@ -19151,7 +19184,7 @@
       <c r="AB54" s="16"/>
       <c r="AC54" s="8"/>
       <c r="AD54" s="9"/>
-      <c r="AF54" s="37"/>
+      <c r="AF54" s="39"/>
       <c r="AG54" s="16"/>
       <c r="AH54" s="8"/>
       <c r="AI54" s="9"/>
@@ -19166,7 +19199,7 @@
       <c r="AR54" s="9"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="D55" s="37"/>
+      <c r="D55" s="39"/>
       <c r="E55" s="18"/>
       <c r="F55" s="8"/>
       <c r="G55" s="9"/>
@@ -19179,7 +19212,7 @@
       <c r="N55" s="18"/>
       <c r="O55" s="8"/>
       <c r="P55" s="9"/>
-      <c r="R55" s="37"/>
+      <c r="R55" s="39"/>
       <c r="S55" s="18"/>
       <c r="T55" s="8"/>
       <c r="U55" s="9"/>
@@ -19192,7 +19225,7 @@
       <c r="AB55" s="18"/>
       <c r="AC55" s="8"/>
       <c r="AD55" s="9"/>
-      <c r="AF55" s="37"/>
+      <c r="AF55" s="39"/>
       <c r="AG55" s="18"/>
       <c r="AH55" s="8"/>
       <c r="AI55" s="9"/>
@@ -19207,7 +19240,7 @@
       <c r="AR55" s="9"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="D56" s="37"/>
+      <c r="D56" s="39"/>
       <c r="E56" s="16"/>
       <c r="F56" s="8"/>
       <c r="G56" s="9"/>
@@ -19220,7 +19253,7 @@
       <c r="N56" s="16"/>
       <c r="O56" s="8"/>
       <c r="P56" s="9"/>
-      <c r="R56" s="37"/>
+      <c r="R56" s="39"/>
       <c r="S56" s="16"/>
       <c r="T56" s="8"/>
       <c r="U56" s="9"/>
@@ -19233,7 +19266,7 @@
       <c r="AB56" s="16"/>
       <c r="AC56" s="8"/>
       <c r="AD56" s="9"/>
-      <c r="AF56" s="37"/>
+      <c r="AF56" s="39"/>
       <c r="AG56" s="16"/>
       <c r="AH56" s="8"/>
       <c r="AI56" s="9"/>
@@ -19248,7 +19281,7 @@
       <c r="AR56" s="9"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="D57" s="37"/>
+      <c r="D57" s="39"/>
       <c r="E57" s="18"/>
       <c r="F57" s="8"/>
       <c r="G57" s="9"/>
@@ -19261,7 +19294,7 @@
       <c r="N57" s="18"/>
       <c r="O57" s="8"/>
       <c r="P57" s="9"/>
-      <c r="R57" s="37"/>
+      <c r="R57" s="39"/>
       <c r="S57" s="18"/>
       <c r="T57" s="8"/>
       <c r="U57" s="9"/>
@@ -19274,7 +19307,7 @@
       <c r="AB57" s="18"/>
       <c r="AC57" s="8"/>
       <c r="AD57" s="9"/>
-      <c r="AF57" s="37"/>
+      <c r="AF57" s="39"/>
       <c r="AG57" s="18"/>
       <c r="AH57" s="8"/>
       <c r="AI57" s="9"/>
@@ -19289,7 +19322,7 @@
       <c r="AR57" s="9"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="D58" s="37"/>
+      <c r="D58" s="39"/>
       <c r="E58" s="21"/>
       <c r="F58" s="22"/>
       <c r="G58" s="23"/>
@@ -19302,7 +19335,7 @@
       <c r="N58" s="16"/>
       <c r="O58" s="8"/>
       <c r="P58" s="9"/>
-      <c r="R58" s="37"/>
+      <c r="R58" s="39"/>
       <c r="S58" s="16"/>
       <c r="T58" s="8"/>
       <c r="U58" s="9"/>
@@ -19315,7 +19348,7 @@
       <c r="AB58" s="16"/>
       <c r="AC58" s="8"/>
       <c r="AD58" s="9"/>
-      <c r="AF58" s="37"/>
+      <c r="AF58" s="39"/>
       <c r="AG58" s="16"/>
       <c r="AH58" s="8"/>
       <c r="AI58" s="9"/>
@@ -19330,20 +19363,20 @@
       <c r="AR58" s="9"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="D59" s="37"/>
+      <c r="D59" s="39"/>
       <c r="E59" s="25"/>
       <c r="F59" s="22"/>
       <c r="G59" s="23"/>
-      <c r="H59" s="31"/>
+      <c r="H59" s="33"/>
       <c r="I59" s="22"/>
       <c r="J59" s="23"/>
-      <c r="K59" s="31"/>
+      <c r="K59" s="33"/>
       <c r="L59" s="22"/>
       <c r="M59" s="23"/>
       <c r="N59" s="18"/>
       <c r="O59" s="8"/>
       <c r="P59" s="9"/>
-      <c r="R59" s="37"/>
+      <c r="R59" s="39"/>
       <c r="S59" s="18"/>
       <c r="T59" s="8"/>
       <c r="U59" s="9"/>
@@ -19356,7 +19389,7 @@
       <c r="AB59" s="18"/>
       <c r="AC59" s="8"/>
       <c r="AD59" s="9"/>
-      <c r="AF59" s="37"/>
+      <c r="AF59" s="39"/>
       <c r="AG59" s="18"/>
       <c r="AH59" s="8"/>
       <c r="AI59" s="9"/>
@@ -19371,7 +19404,7 @@
       <c r="AR59" s="9"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="D60" s="37"/>
+      <c r="D60" s="39"/>
       <c r="E60" s="21"/>
       <c r="F60" s="22"/>
       <c r="G60" s="23"/>
@@ -19384,7 +19417,7 @@
       <c r="N60" s="16"/>
       <c r="O60" s="8"/>
       <c r="P60" s="9"/>
-      <c r="R60" s="37"/>
+      <c r="R60" s="39"/>
       <c r="S60" s="16"/>
       <c r="T60" s="8"/>
       <c r="U60" s="9"/>
@@ -19397,7 +19430,7 @@
       <c r="AB60" s="16"/>
       <c r="AC60" s="8"/>
       <c r="AD60" s="9"/>
-      <c r="AF60" s="37"/>
+      <c r="AF60" s="39"/>
       <c r="AG60" s="16"/>
       <c r="AH60" s="8"/>
       <c r="AI60" s="9"/>
@@ -19412,20 +19445,20 @@
       <c r="AR60" s="9"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="D61" s="37"/>
+      <c r="D61" s="39"/>
       <c r="E61" s="25"/>
       <c r="F61" s="22"/>
       <c r="G61" s="23"/>
-      <c r="H61" s="31"/>
+      <c r="H61" s="33"/>
       <c r="I61" s="22"/>
       <c r="J61" s="23"/>
-      <c r="K61" s="31"/>
+      <c r="K61" s="33"/>
       <c r="L61" s="22"/>
       <c r="M61" s="23"/>
       <c r="N61" s="18"/>
       <c r="O61" s="8"/>
       <c r="P61" s="9"/>
-      <c r="R61" s="37"/>
+      <c r="R61" s="39"/>
       <c r="S61" s="18"/>
       <c r="T61" s="8"/>
       <c r="U61" s="9"/>
@@ -19438,7 +19471,7 @@
       <c r="AB61" s="18"/>
       <c r="AC61" s="8"/>
       <c r="AD61" s="9"/>
-      <c r="AF61" s="37"/>
+      <c r="AF61" s="39"/>
       <c r="AG61" s="18"/>
       <c r="AH61" s="8"/>
       <c r="AI61" s="9"/>
@@ -19453,7 +19486,7 @@
       <c r="AR61" s="9"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="D62" s="37"/>
+      <c r="D62" s="39"/>
       <c r="E62" s="21"/>
       <c r="F62" s="22"/>
       <c r="G62" s="23"/>
@@ -19466,7 +19499,7 @@
       <c r="N62" s="16"/>
       <c r="O62" s="8"/>
       <c r="P62" s="9"/>
-      <c r="R62" s="37"/>
+      <c r="R62" s="39"/>
       <c r="S62" s="16"/>
       <c r="T62" s="8"/>
       <c r="U62" s="9"/>
@@ -19479,7 +19512,7 @@
       <c r="AB62" s="16"/>
       <c r="AC62" s="8"/>
       <c r="AD62" s="9"/>
-      <c r="AF62" s="37"/>
+      <c r="AF62" s="39"/>
       <c r="AG62" s="16"/>
       <c r="AH62" s="8"/>
       <c r="AI62" s="9"/>
@@ -19494,20 +19527,20 @@
       <c r="AR62" s="9"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="D63" s="37"/>
+      <c r="D63" s="39"/>
       <c r="E63" s="25"/>
       <c r="F63" s="22"/>
       <c r="G63" s="23"/>
-      <c r="H63" s="31"/>
+      <c r="H63" s="33"/>
       <c r="I63" s="22"/>
       <c r="J63" s="23"/>
-      <c r="K63" s="31"/>
+      <c r="K63" s="33"/>
       <c r="L63" s="22"/>
       <c r="M63" s="23"/>
       <c r="N63" s="18"/>
       <c r="O63" s="8"/>
       <c r="P63" s="9"/>
-      <c r="R63" s="37"/>
+      <c r="R63" s="39"/>
       <c r="S63" s="18"/>
       <c r="T63" s="8"/>
       <c r="U63" s="9"/>
@@ -19520,7 +19553,7 @@
       <c r="AB63" s="18"/>
       <c r="AC63" s="8"/>
       <c r="AD63" s="9"/>
-      <c r="AF63" s="37"/>
+      <c r="AF63" s="39"/>
       <c r="AG63" s="18"/>
       <c r="AH63" s="8"/>
       <c r="AI63" s="9"/>
@@ -19535,7 +19568,7 @@
       <c r="AR63" s="9"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="D64" s="37"/>
+      <c r="D64" s="39"/>
       <c r="E64" s="16"/>
       <c r="F64" s="8"/>
       <c r="G64" s="9"/>
@@ -19548,7 +19581,7 @@
       <c r="N64" s="16"/>
       <c r="O64" s="8"/>
       <c r="P64" s="9"/>
-      <c r="R64" s="37"/>
+      <c r="R64" s="39"/>
       <c r="S64" s="16"/>
       <c r="T64" s="8"/>
       <c r="U64" s="9"/>
@@ -19561,7 +19594,7 @@
       <c r="AB64" s="16"/>
       <c r="AC64" s="8"/>
       <c r="AD64" s="9"/>
-      <c r="AF64" s="37"/>
+      <c r="AF64" s="39"/>
       <c r="AG64" s="16"/>
       <c r="AH64" s="8"/>
       <c r="AI64" s="9"/>
@@ -19576,7 +19609,7 @@
       <c r="AR64" s="9"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="D65" s="37"/>
+      <c r="D65" s="39"/>
       <c r="E65" s="18"/>
       <c r="F65" s="8"/>
       <c r="G65" s="9"/>
@@ -19589,7 +19622,7 @@
       <c r="N65" s="18"/>
       <c r="O65" s="8"/>
       <c r="P65" s="9"/>
-      <c r="R65" s="37"/>
+      <c r="R65" s="39"/>
       <c r="S65" s="18"/>
       <c r="T65" s="8"/>
       <c r="U65" s="9"/>
@@ -19602,7 +19635,7 @@
       <c r="AB65" s="18"/>
       <c r="AC65" s="8"/>
       <c r="AD65" s="9"/>
-      <c r="AF65" s="37"/>
+      <c r="AF65" s="39"/>
       <c r="AG65" s="18"/>
       <c r="AH65" s="8"/>
       <c r="AI65" s="9"/>
@@ -19617,7 +19650,7 @@
       <c r="AR65" s="9"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="D66" s="37"/>
+      <c r="D66" s="39"/>
       <c r="E66" s="16"/>
       <c r="F66" s="8"/>
       <c r="G66" s="9"/>
@@ -19630,7 +19663,7 @@
       <c r="N66" s="16"/>
       <c r="O66" s="8"/>
       <c r="P66" s="9"/>
-      <c r="R66" s="37"/>
+      <c r="R66" s="39"/>
       <c r="S66" s="16"/>
       <c r="T66" s="8"/>
       <c r="U66" s="9"/>
@@ -19643,7 +19676,7 @@
       <c r="AB66" s="16"/>
       <c r="AC66" s="8"/>
       <c r="AD66" s="9"/>
-      <c r="AF66" s="37"/>
+      <c r="AF66" s="39"/>
       <c r="AG66" s="16"/>
       <c r="AH66" s="8"/>
       <c r="AI66" s="9"/>
@@ -19658,7 +19691,7 @@
       <c r="AR66" s="9"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="D67" s="37"/>
+      <c r="D67" s="39"/>
       <c r="E67" s="18"/>
       <c r="F67" s="8"/>
       <c r="G67" s="9"/>
@@ -19671,7 +19704,7 @@
       <c r="N67" s="18"/>
       <c r="O67" s="8"/>
       <c r="P67" s="9"/>
-      <c r="R67" s="37"/>
+      <c r="R67" s="39"/>
       <c r="S67" s="18"/>
       <c r="T67" s="8"/>
       <c r="U67" s="9"/>
@@ -19684,7 +19717,7 @@
       <c r="AB67" s="18"/>
       <c r="AC67" s="8"/>
       <c r="AD67" s="9"/>
-      <c r="AF67" s="37"/>
+      <c r="AF67" s="39"/>
       <c r="AG67" s="18"/>
       <c r="AH67" s="8"/>
       <c r="AI67" s="9"/>
@@ -19699,7 +19732,7 @@
       <c r="AR67" s="9"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="D68" s="37"/>
+      <c r="D68" s="39"/>
       <c r="E68" s="16"/>
       <c r="F68" s="8"/>
       <c r="G68" s="9"/>
@@ -19712,7 +19745,7 @@
       <c r="N68" s="16"/>
       <c r="O68" s="8"/>
       <c r="P68" s="9"/>
-      <c r="R68" s="37"/>
+      <c r="R68" s="39"/>
       <c r="S68" s="16"/>
       <c r="T68" s="8"/>
       <c r="U68" s="9"/>
@@ -19725,7 +19758,7 @@
       <c r="AB68" s="16"/>
       <c r="AC68" s="8"/>
       <c r="AD68" s="9"/>
-      <c r="AF68" s="37"/>
+      <c r="AF68" s="39"/>
       <c r="AG68" s="16"/>
       <c r="AH68" s="8"/>
       <c r="AI68" s="9"/>
@@ -19740,7 +19773,7 @@
       <c r="AR68" s="9"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="D69" s="37"/>
+      <c r="D69" s="39"/>
       <c r="E69" s="18"/>
       <c r="F69" s="8"/>
       <c r="G69" s="9"/>
@@ -19753,7 +19786,7 @@
       <c r="N69" s="18"/>
       <c r="O69" s="8"/>
       <c r="P69" s="9"/>
-      <c r="R69" s="37"/>
+      <c r="R69" s="39"/>
       <c r="S69" s="18"/>
       <c r="T69" s="8"/>
       <c r="U69" s="9"/>
@@ -19766,7 +19799,7 @@
       <c r="AB69" s="18"/>
       <c r="AC69" s="8"/>
       <c r="AD69" s="9"/>
-      <c r="AF69" s="37"/>
+      <c r="AF69" s="39"/>
       <c r="AG69" s="18"/>
       <c r="AH69" s="8"/>
       <c r="AI69" s="9"/>
@@ -19781,7 +19814,7 @@
       <c r="AR69" s="9"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="D70" s="37"/>
+      <c r="D70" s="39"/>
       <c r="E70" s="16"/>
       <c r="F70" s="8"/>
       <c r="G70" s="9"/>
@@ -19794,7 +19827,7 @@
       <c r="N70" s="16"/>
       <c r="O70" s="8"/>
       <c r="P70" s="9"/>
-      <c r="R70" s="37"/>
+      <c r="R70" s="39"/>
       <c r="S70" s="16"/>
       <c r="T70" s="8"/>
       <c r="U70" s="9"/>
@@ -19807,7 +19840,7 @@
       <c r="AB70" s="16"/>
       <c r="AC70" s="8"/>
       <c r="AD70" s="9"/>
-      <c r="AF70" s="37"/>
+      <c r="AF70" s="39"/>
       <c r="AG70" s="16"/>
       <c r="AH70" s="8"/>
       <c r="AI70" s="9"/>
@@ -19822,20 +19855,20 @@
       <c r="AR70" s="9"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="D71" s="37"/>
+      <c r="D71" s="39"/>
       <c r="E71" s="25"/>
       <c r="F71" s="22"/>
       <c r="G71" s="23"/>
-      <c r="H71" s="31"/>
+      <c r="H71" s="33"/>
       <c r="I71" s="22"/>
       <c r="J71" s="23"/>
-      <c r="K71" s="31"/>
+      <c r="K71" s="33"/>
       <c r="L71" s="22"/>
       <c r="M71" s="23"/>
       <c r="N71" s="18"/>
       <c r="O71" s="8"/>
       <c r="P71" s="9"/>
-      <c r="R71" s="37"/>
+      <c r="R71" s="39"/>
       <c r="S71" s="18"/>
       <c r="T71" s="8"/>
       <c r="U71" s="9"/>
@@ -19848,7 +19881,7 @@
       <c r="AB71" s="18"/>
       <c r="AC71" s="8"/>
       <c r="AD71" s="9"/>
-      <c r="AF71" s="37"/>
+      <c r="AF71" s="39"/>
       <c r="AG71" s="18"/>
       <c r="AH71" s="8"/>
       <c r="AI71" s="9"/>
@@ -19863,7 +19896,7 @@
       <c r="AR71" s="9"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="D72" s="37"/>
+      <c r="D72" s="39"/>
       <c r="E72" s="21"/>
       <c r="F72" s="22"/>
       <c r="G72" s="23"/>
@@ -19876,7 +19909,7 @@
       <c r="N72" s="16"/>
       <c r="O72" s="8"/>
       <c r="P72" s="9"/>
-      <c r="R72" s="37"/>
+      <c r="R72" s="39"/>
       <c r="S72" s="16"/>
       <c r="T72" s="8"/>
       <c r="U72" s="9"/>
@@ -19889,7 +19922,7 @@
       <c r="AB72" s="16"/>
       <c r="AC72" s="8"/>
       <c r="AD72" s="9"/>
-      <c r="AF72" s="37"/>
+      <c r="AF72" s="39"/>
       <c r="AG72" s="16"/>
       <c r="AH72" s="8"/>
       <c r="AI72" s="9"/>
@@ -19904,20 +19937,20 @@
       <c r="AR72" s="9"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="D73" s="37"/>
+      <c r="D73" s="39"/>
       <c r="E73" s="25"/>
       <c r="F73" s="22"/>
       <c r="G73" s="23"/>
-      <c r="H73" s="31"/>
+      <c r="H73" s="33"/>
       <c r="I73" s="22"/>
       <c r="J73" s="23"/>
-      <c r="K73" s="31"/>
+      <c r="K73" s="33"/>
       <c r="L73" s="22"/>
       <c r="M73" s="23"/>
       <c r="N73" s="18"/>
       <c r="O73" s="8"/>
       <c r="P73" s="9"/>
-      <c r="R73" s="37"/>
+      <c r="R73" s="39"/>
       <c r="S73" s="18"/>
       <c r="T73" s="8"/>
       <c r="U73" s="9"/>
@@ -19930,7 +19963,7 @@
       <c r="AB73" s="18"/>
       <c r="AC73" s="8"/>
       <c r="AD73" s="9"/>
-      <c r="AF73" s="37"/>
+      <c r="AF73" s="39"/>
       <c r="AG73" s="18"/>
       <c r="AH73" s="8"/>
       <c r="AI73" s="9"/>
@@ -19945,7 +19978,7 @@
       <c r="AR73" s="9"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="D74" s="37"/>
+      <c r="D74" s="39"/>
       <c r="E74" s="21"/>
       <c r="F74" s="22"/>
       <c r="G74" s="23"/>
@@ -19958,7 +19991,7 @@
       <c r="N74" s="16"/>
       <c r="O74" s="8"/>
       <c r="P74" s="9"/>
-      <c r="R74" s="37"/>
+      <c r="R74" s="39"/>
       <c r="S74" s="16"/>
       <c r="T74" s="8"/>
       <c r="U74" s="9"/>
@@ -19971,7 +20004,7 @@
       <c r="AB74" s="16"/>
       <c r="AC74" s="8"/>
       <c r="AD74" s="9"/>
-      <c r="AF74" s="37"/>
+      <c r="AF74" s="39"/>
       <c r="AG74" s="16"/>
       <c r="AH74" s="8"/>
       <c r="AI74" s="9"/>
@@ -19986,20 +20019,20 @@
       <c r="AR74" s="9"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="D75" s="37"/>
+      <c r="D75" s="39"/>
       <c r="E75" s="25"/>
       <c r="F75" s="22"/>
       <c r="G75" s="23"/>
-      <c r="H75" s="31"/>
+      <c r="H75" s="33"/>
       <c r="I75" s="22"/>
       <c r="J75" s="23"/>
-      <c r="K75" s="31"/>
+      <c r="K75" s="33"/>
       <c r="L75" s="22"/>
       <c r="M75" s="23"/>
       <c r="N75" s="18"/>
       <c r="O75" s="8"/>
       <c r="P75" s="9"/>
-      <c r="R75" s="37"/>
+      <c r="R75" s="39"/>
       <c r="S75" s="18"/>
       <c r="T75" s="8"/>
       <c r="U75" s="9"/>
@@ -20012,7 +20045,7 @@
       <c r="AB75" s="18"/>
       <c r="AC75" s="8"/>
       <c r="AD75" s="9"/>
-      <c r="AF75" s="37"/>
+      <c r="AF75" s="39"/>
       <c r="AG75" s="18"/>
       <c r="AH75" s="8"/>
       <c r="AI75" s="9"/>
@@ -20027,7 +20060,7 @@
       <c r="AR75" s="9"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="D76" s="37"/>
+      <c r="D76" s="39"/>
       <c r="E76" s="21"/>
       <c r="F76" s="22"/>
       <c r="G76" s="23"/>
@@ -20040,7 +20073,7 @@
       <c r="N76" s="16"/>
       <c r="O76" s="8"/>
       <c r="P76" s="9"/>
-      <c r="R76" s="37"/>
+      <c r="R76" s="39"/>
       <c r="S76" s="16"/>
       <c r="T76" s="8"/>
       <c r="U76" s="9"/>
@@ -20053,7 +20086,7 @@
       <c r="AB76" s="16"/>
       <c r="AC76" s="8"/>
       <c r="AD76" s="9"/>
-      <c r="AF76" s="37"/>
+      <c r="AF76" s="39"/>
       <c r="AG76" s="16"/>
       <c r="AH76" s="8"/>
       <c r="AI76" s="9"/>
@@ -20068,7 +20101,7 @@
       <c r="AR76" s="9"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="D77" s="37"/>
+      <c r="D77" s="39"/>
       <c r="E77" s="25"/>
       <c r="F77" s="22"/>
       <c r="G77" s="23"/>
@@ -20081,7 +20114,7 @@
       <c r="N77" s="18"/>
       <c r="O77" s="8"/>
       <c r="P77" s="9"/>
-      <c r="R77" s="37"/>
+      <c r="R77" s="39"/>
       <c r="S77" s="18"/>
       <c r="T77" s="8"/>
       <c r="U77" s="9"/>
@@ -20094,7 +20127,7 @@
       <c r="AB77" s="18"/>
       <c r="AC77" s="8"/>
       <c r="AD77" s="9"/>
-      <c r="AF77" s="37"/>
+      <c r="AF77" s="39"/>
       <c r="AG77" s="18"/>
       <c r="AH77" s="8"/>
       <c r="AI77" s="9"/>
@@ -20109,7 +20142,7 @@
       <c r="AR77" s="9"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="D78" s="37"/>
+      <c r="D78" s="39"/>
       <c r="E78" s="21"/>
       <c r="F78" s="22"/>
       <c r="G78" s="23"/>
@@ -20122,7 +20155,7 @@
       <c r="N78" s="16"/>
       <c r="O78" s="8"/>
       <c r="P78" s="9"/>
-      <c r="R78" s="37"/>
+      <c r="R78" s="39"/>
       <c r="S78" s="16"/>
       <c r="T78" s="8"/>
       <c r="U78" s="9"/>
@@ -20135,7 +20168,7 @@
       <c r="AB78" s="16"/>
       <c r="AC78" s="8"/>
       <c r="AD78" s="9"/>
-      <c r="AF78" s="37"/>
+      <c r="AF78" s="39"/>
       <c r="AG78" s="16"/>
       <c r="AH78" s="8"/>
       <c r="AI78" s="9"/>
@@ -20150,7 +20183,7 @@
       <c r="AR78" s="9"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="D79" s="37"/>
+      <c r="D79" s="39"/>
       <c r="E79" s="25"/>
       <c r="F79" s="22"/>
       <c r="G79" s="23"/>
@@ -20163,7 +20196,7 @@
       <c r="N79" s="18"/>
       <c r="O79" s="8"/>
       <c r="P79" s="9"/>
-      <c r="R79" s="37"/>
+      <c r="R79" s="39"/>
       <c r="S79" s="18"/>
       <c r="T79" s="8"/>
       <c r="U79" s="9"/>
@@ -20176,7 +20209,7 @@
       <c r="AB79" s="18"/>
       <c r="AC79" s="8"/>
       <c r="AD79" s="9"/>
-      <c r="AF79" s="37"/>
+      <c r="AF79" s="39"/>
       <c r="AG79" s="18"/>
       <c r="AH79" s="8"/>
       <c r="AI79" s="9"/>
@@ -20191,7 +20224,7 @@
       <c r="AR79" s="9"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="D80" s="37"/>
+      <c r="D80" s="39"/>
       <c r="E80" s="16"/>
       <c r="F80" s="8"/>
       <c r="G80" s="9"/>
@@ -20204,7 +20237,7 @@
       <c r="N80" s="16"/>
       <c r="O80" s="8"/>
       <c r="P80" s="9"/>
-      <c r="R80" s="37"/>
+      <c r="R80" s="39"/>
       <c r="S80" s="16"/>
       <c r="T80" s="8"/>
       <c r="U80" s="9"/>
@@ -20217,7 +20250,7 @@
       <c r="AB80" s="16"/>
       <c r="AC80" s="8"/>
       <c r="AD80" s="9"/>
-      <c r="AF80" s="37"/>
+      <c r="AF80" s="39"/>
       <c r="AG80" s="16"/>
       <c r="AH80" s="8"/>
       <c r="AI80" s="9"/>
@@ -20232,7 +20265,7 @@
       <c r="AR80" s="9"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="D81" s="37"/>
+      <c r="D81" s="39"/>
       <c r="E81" s="18"/>
       <c r="F81" s="8"/>
       <c r="G81" s="9"/>
@@ -20245,7 +20278,7 @@
       <c r="N81" s="18"/>
       <c r="O81" s="8"/>
       <c r="P81" s="9"/>
-      <c r="R81" s="37"/>
+      <c r="R81" s="39"/>
       <c r="S81" s="18"/>
       <c r="T81" s="8"/>
       <c r="U81" s="9"/>
@@ -20258,7 +20291,7 @@
       <c r="AB81" s="18"/>
       <c r="AC81" s="8"/>
       <c r="AD81" s="9"/>
-      <c r="AF81" s="37"/>
+      <c r="AF81" s="39"/>
       <c r="AG81" s="18"/>
       <c r="AH81" s="8"/>
       <c r="AI81" s="9"/>

--- a/To-Do/MainALR.xlsx
+++ b/To-Do/MainALR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmcdonnell1\Downloads\Cost-of-Betrayal\To-Do\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7C38A9-243B-4BE7-8160-0EB6FDEA863D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266356D0-C831-4220-B21A-167CD99E0F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42696" yWindow="144" windowWidth="17880" windowHeight="15348" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="148">
   <si>
     <t>MainALR</t>
   </si>
@@ -474,6 +474,15 @@
   <si>
     <t>Just a water dropping noise, for caves</t>
   </si>
+  <si>
+    <t>Advanced Music Player</t>
+  </si>
+  <si>
+    <t>Complex music player that'll allow for music to be stopped and started, crossfaded, and much more to get developers much more freedom when it comes to weaving music into levels and scenes</t>
+  </si>
+  <si>
+    <t>BPI_MusicHandler</t>
+  </si>
 </sst>
 </file>
 
@@ -809,8 +818,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2286,14 +2295,22 @@
       <c r="AM22" s="17"/>
     </row>
     <row r="23" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D23" s="8"/>
-      <c r="E23" s="18"/>
+      <c r="D23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>145</v>
+      </c>
       <c r="F23" s="16"/>
       <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
+      <c r="H23" s="18" t="s">
+        <v>147</v>
+      </c>
       <c r="I23" s="16"/>
       <c r="J23" s="17"/>
-      <c r="K23" s="18"/>
+      <c r="K23" s="18" t="s">
+        <v>146</v>
+      </c>
       <c r="L23" s="16"/>
       <c r="M23" s="17"/>
       <c r="N23" s="2"/>
@@ -6282,6 +6299,11 @@
     <mergeCell ref="R10:T10"/>
     <mergeCell ref="U10:W10"/>
     <mergeCell ref="X10:Z10"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="AB9:AD9"/>
+    <mergeCell ref="AE9:AG9"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="AK9:AM9"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="K5:M5"/>
@@ -6292,6 +6314,8 @@
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
     <mergeCell ref="AK83:AM83"/>
     <mergeCell ref="E83:G83"/>
     <mergeCell ref="H83:J83"/>
@@ -6393,6 +6417,11 @@
     <mergeCell ref="H93:J93"/>
     <mergeCell ref="K93:M93"/>
     <mergeCell ref="E94:G94"/>
+    <mergeCell ref="E91:G91"/>
+    <mergeCell ref="H91:J91"/>
+    <mergeCell ref="K91:M91"/>
+    <mergeCell ref="H90:J90"/>
+    <mergeCell ref="K90:M90"/>
     <mergeCell ref="H109:J109"/>
     <mergeCell ref="K109:M109"/>
     <mergeCell ref="E107:G107"/>
@@ -6420,14 +6449,6 @@
     <mergeCell ref="H102:J102"/>
     <mergeCell ref="K102:M102"/>
     <mergeCell ref="E103:G103"/>
-    <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="AB9:AD9"/>
-    <mergeCell ref="AE9:AG9"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="AK9:AM9"/>
-    <mergeCell ref="E91:G91"/>
-    <mergeCell ref="H91:J91"/>
-    <mergeCell ref="K91:M91"/>
     <mergeCell ref="H100:J100"/>
     <mergeCell ref="K100:M100"/>
     <mergeCell ref="E98:G98"/>
@@ -6437,8 +6458,6 @@
     <mergeCell ref="H99:J99"/>
     <mergeCell ref="K99:M99"/>
     <mergeCell ref="E100:G100"/>
-    <mergeCell ref="H90:J90"/>
-    <mergeCell ref="K90:M90"/>
     <mergeCell ref="E88:G88"/>
     <mergeCell ref="H88:J88"/>
     <mergeCell ref="K88:M88"/>
@@ -6448,6 +6467,21 @@
     <mergeCell ref="AB7:AD7"/>
     <mergeCell ref="AE7:AG7"/>
     <mergeCell ref="AH7:AJ7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="AB78:AD78"/>
+    <mergeCell ref="AE78:AG78"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="AB76:AD76"/>
+    <mergeCell ref="AE76:AG76"/>
+    <mergeCell ref="AH76:AJ76"/>
     <mergeCell ref="AK7:AM7"/>
     <mergeCell ref="O8:Q8"/>
     <mergeCell ref="R8:T8"/>
@@ -6457,6 +6491,9 @@
     <mergeCell ref="AE8:AG8"/>
     <mergeCell ref="AH8:AJ8"/>
     <mergeCell ref="AK8:AM8"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="U7:W7"/>
     <mergeCell ref="AE5:AG5"/>
     <mergeCell ref="AH5:AJ5"/>
     <mergeCell ref="AK5:AM5"/>
@@ -6479,23 +6516,6 @@
     <mergeCell ref="X5:Z5"/>
     <mergeCell ref="AB5:AD5"/>
     <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="R7:T7"/>
-    <mergeCell ref="U7:W7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="U9:W9"/>
-    <mergeCell ref="AB78:AD78"/>
-    <mergeCell ref="AE78:AG78"/>
-    <mergeCell ref="AH78:AJ78"/>
     <mergeCell ref="AK78:AM78"/>
     <mergeCell ref="E78:G78"/>
     <mergeCell ref="H78:J78"/>
@@ -6515,9 +6535,6 @@
     <mergeCell ref="R77:T77"/>
     <mergeCell ref="U77:W77"/>
     <mergeCell ref="X77:Z77"/>
-    <mergeCell ref="AB76:AD76"/>
-    <mergeCell ref="AE76:AG76"/>
-    <mergeCell ref="AH76:AJ76"/>
     <mergeCell ref="AK76:AM76"/>
     <mergeCell ref="E76:G76"/>
     <mergeCell ref="H76:J76"/>
@@ -6776,7 +6793,7 @@
       <c r="R4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="S4" s="37"/>
+      <c r="S4" s="36"/>
       <c r="T4" s="30"/>
       <c r="AF4" s="14" t="s">
         <v>5</v>
@@ -6839,7 +6856,7 @@
       <c r="AF5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="AG5" s="36" t="s">
+      <c r="AG5" s="37" t="s">
         <v>70</v>
       </c>
       <c r="AH5" s="21"/>
@@ -11607,6 +11624,12 @@
     <mergeCell ref="AB11:AD11"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AM6:AO6"/>
     <mergeCell ref="AP6:AR6"/>
     <mergeCell ref="AP8:AR8"/>
@@ -11623,11 +11646,6 @@
     <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="AM7:AO7"/>
     <mergeCell ref="AP7:AR7"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
     <mergeCell ref="S7:U7"/>
     <mergeCell ref="V5:X5"/>
     <mergeCell ref="Y5:AA5"/>
@@ -11645,7 +11663,21 @@
     <mergeCell ref="AG79:AI79"/>
     <mergeCell ref="AJ79:AL79"/>
     <mergeCell ref="AM79:AO79"/>
-    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AB77:AD77"/>
+    <mergeCell ref="AG77:AI77"/>
+    <mergeCell ref="AJ77:AL77"/>
+    <mergeCell ref="AM77:AO77"/>
+    <mergeCell ref="AB75:AD75"/>
+    <mergeCell ref="AG75:AI75"/>
+    <mergeCell ref="AJ75:AL75"/>
+    <mergeCell ref="AM75:AO75"/>
+    <mergeCell ref="AB73:AD73"/>
+    <mergeCell ref="AG73:AI73"/>
+    <mergeCell ref="AJ73:AL73"/>
+    <mergeCell ref="AM73:AO73"/>
+    <mergeCell ref="AB10:AD10"/>
+    <mergeCell ref="AG10:AI10"/>
+    <mergeCell ref="AJ10:AL10"/>
     <mergeCell ref="E79:G79"/>
     <mergeCell ref="H79:J79"/>
     <mergeCell ref="K79:M79"/>
@@ -11655,9 +11687,6 @@
     <mergeCell ref="Y79:AA79"/>
     <mergeCell ref="AB78:AD78"/>
     <mergeCell ref="AG78:AI78"/>
-    <mergeCell ref="AJ78:AL78"/>
-    <mergeCell ref="AM78:AO78"/>
-    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="E78:G78"/>
     <mergeCell ref="H78:J78"/>
     <mergeCell ref="K78:M78"/>
@@ -11665,11 +11694,6 @@
     <mergeCell ref="S78:U78"/>
     <mergeCell ref="V78:X78"/>
     <mergeCell ref="Y78:AA78"/>
-    <mergeCell ref="AB77:AD77"/>
-    <mergeCell ref="AG77:AI77"/>
-    <mergeCell ref="AJ77:AL77"/>
-    <mergeCell ref="AM77:AO77"/>
-    <mergeCell ref="AP77:AR77"/>
     <mergeCell ref="E77:G77"/>
     <mergeCell ref="H77:J77"/>
     <mergeCell ref="K77:M77"/>
@@ -11679,9 +11703,6 @@
     <mergeCell ref="Y77:AA77"/>
     <mergeCell ref="AB76:AD76"/>
     <mergeCell ref="AG76:AI76"/>
-    <mergeCell ref="AJ76:AL76"/>
-    <mergeCell ref="AM76:AO76"/>
-    <mergeCell ref="AP76:AR76"/>
     <mergeCell ref="E76:G76"/>
     <mergeCell ref="H76:J76"/>
     <mergeCell ref="K76:M76"/>
@@ -11689,11 +11710,6 @@
     <mergeCell ref="S76:U76"/>
     <mergeCell ref="V76:X76"/>
     <mergeCell ref="Y76:AA76"/>
-    <mergeCell ref="AB75:AD75"/>
-    <mergeCell ref="AG75:AI75"/>
-    <mergeCell ref="AJ75:AL75"/>
-    <mergeCell ref="AM75:AO75"/>
-    <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="E75:G75"/>
     <mergeCell ref="H75:J75"/>
     <mergeCell ref="K75:M75"/>
@@ -11703,9 +11719,6 @@
     <mergeCell ref="Y75:AA75"/>
     <mergeCell ref="AB74:AD74"/>
     <mergeCell ref="AG74:AI74"/>
-    <mergeCell ref="AJ74:AL74"/>
-    <mergeCell ref="AM74:AO74"/>
-    <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="E74:G74"/>
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="K74:M74"/>
@@ -11713,14 +11726,15 @@
     <mergeCell ref="S74:U74"/>
     <mergeCell ref="V74:X74"/>
     <mergeCell ref="Y74:AA74"/>
-    <mergeCell ref="AB73:AD73"/>
-    <mergeCell ref="AG73:AI73"/>
-    <mergeCell ref="AJ73:AL73"/>
-    <mergeCell ref="AM73:AO73"/>
-    <mergeCell ref="AP73:AR73"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="K73:M73"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="S81:U81"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="Y81:AA81"/>
+    <mergeCell ref="AB80:AD80"/>
+    <mergeCell ref="AG80:AI80"/>
     <mergeCell ref="N73:P73"/>
     <mergeCell ref="S73:U73"/>
     <mergeCell ref="V73:X73"/>
@@ -11730,16 +11744,20 @@
     <mergeCell ref="AJ81:AL81"/>
     <mergeCell ref="AM81:AO81"/>
     <mergeCell ref="AP81:AR81"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="H81:J81"/>
-    <mergeCell ref="K81:M81"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="S81:U81"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="Y81:AA81"/>
-    <mergeCell ref="AB10:AD10"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AJ80:AL80"/>
+    <mergeCell ref="AM80:AO80"/>
+    <mergeCell ref="AP75:AR75"/>
+    <mergeCell ref="AJ74:AL74"/>
+    <mergeCell ref="AM74:AO74"/>
+    <mergeCell ref="AP74:AR74"/>
+    <mergeCell ref="AP77:AR77"/>
+    <mergeCell ref="AJ76:AL76"/>
+    <mergeCell ref="AM76:AO76"/>
+    <mergeCell ref="AP76:AR76"/>
+    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AJ78:AL78"/>
+    <mergeCell ref="AM78:AO78"/>
+    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="AM10:AO10"/>
     <mergeCell ref="AP10:AR10"/>
     <mergeCell ref="E10:G10"/>
@@ -11749,7 +11767,6 @@
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AG9:AI9"/>
     <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AM9:AO9"/>
@@ -11770,10 +11787,6 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AB80:AD80"/>
-    <mergeCell ref="AG80:AI80"/>
-    <mergeCell ref="AJ80:AL80"/>
-    <mergeCell ref="AM80:AO80"/>
     <mergeCell ref="AP80:AR80"/>
     <mergeCell ref="E80:G80"/>
     <mergeCell ref="H80:J80"/>
@@ -11794,6 +11807,10 @@
     <mergeCell ref="S72:U72"/>
     <mergeCell ref="V72:X72"/>
     <mergeCell ref="Y72:AA72"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="K73:M73"/>
     <mergeCell ref="AB71:AD71"/>
     <mergeCell ref="AG71:AI71"/>
     <mergeCell ref="AJ71:AL71"/>
@@ -12007,7 +12024,7 @@
       <c r="R4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="S4" s="37"/>
+      <c r="S4" s="36"/>
       <c r="T4" s="30"/>
       <c r="AF4" s="14" t="s">
         <v>5</v>
@@ -12070,7 +12087,7 @@
       <c r="AF5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="AG5" s="36" t="s">
+      <c r="AG5" s="37" t="s">
         <v>99</v>
       </c>
       <c r="AH5" s="21"/>
@@ -16852,6 +16869,12 @@
     <mergeCell ref="AB11:AD11"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AM6:AO6"/>
     <mergeCell ref="AP6:AR6"/>
     <mergeCell ref="AP8:AR8"/>
@@ -16868,11 +16891,6 @@
     <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="AM7:AO7"/>
     <mergeCell ref="AP7:AR7"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
     <mergeCell ref="S7:U7"/>
     <mergeCell ref="V5:X5"/>
     <mergeCell ref="Y5:AA5"/>
@@ -16890,7 +16908,21 @@
     <mergeCell ref="AG79:AI79"/>
     <mergeCell ref="AJ79:AL79"/>
     <mergeCell ref="AM79:AO79"/>
-    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AB77:AD77"/>
+    <mergeCell ref="AG77:AI77"/>
+    <mergeCell ref="AJ77:AL77"/>
+    <mergeCell ref="AM77:AO77"/>
+    <mergeCell ref="AB75:AD75"/>
+    <mergeCell ref="AG75:AI75"/>
+    <mergeCell ref="AJ75:AL75"/>
+    <mergeCell ref="AM75:AO75"/>
+    <mergeCell ref="AB73:AD73"/>
+    <mergeCell ref="AG73:AI73"/>
+    <mergeCell ref="AJ73:AL73"/>
+    <mergeCell ref="AM73:AO73"/>
+    <mergeCell ref="AB10:AD10"/>
+    <mergeCell ref="AG10:AI10"/>
+    <mergeCell ref="AJ10:AL10"/>
     <mergeCell ref="E79:G79"/>
     <mergeCell ref="H79:J79"/>
     <mergeCell ref="K79:M79"/>
@@ -16900,9 +16932,6 @@
     <mergeCell ref="Y79:AA79"/>
     <mergeCell ref="AB78:AD78"/>
     <mergeCell ref="AG78:AI78"/>
-    <mergeCell ref="AJ78:AL78"/>
-    <mergeCell ref="AM78:AO78"/>
-    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="E78:G78"/>
     <mergeCell ref="H78:J78"/>
     <mergeCell ref="K78:M78"/>
@@ -16910,11 +16939,6 @@
     <mergeCell ref="S78:U78"/>
     <mergeCell ref="V78:X78"/>
     <mergeCell ref="Y78:AA78"/>
-    <mergeCell ref="AB77:AD77"/>
-    <mergeCell ref="AG77:AI77"/>
-    <mergeCell ref="AJ77:AL77"/>
-    <mergeCell ref="AM77:AO77"/>
-    <mergeCell ref="AP77:AR77"/>
     <mergeCell ref="E77:G77"/>
     <mergeCell ref="H77:J77"/>
     <mergeCell ref="K77:M77"/>
@@ -16924,9 +16948,6 @@
     <mergeCell ref="Y77:AA77"/>
     <mergeCell ref="AB76:AD76"/>
     <mergeCell ref="AG76:AI76"/>
-    <mergeCell ref="AJ76:AL76"/>
-    <mergeCell ref="AM76:AO76"/>
-    <mergeCell ref="AP76:AR76"/>
     <mergeCell ref="E76:G76"/>
     <mergeCell ref="H76:J76"/>
     <mergeCell ref="K76:M76"/>
@@ -16934,11 +16955,6 @@
     <mergeCell ref="S76:U76"/>
     <mergeCell ref="V76:X76"/>
     <mergeCell ref="Y76:AA76"/>
-    <mergeCell ref="AB75:AD75"/>
-    <mergeCell ref="AG75:AI75"/>
-    <mergeCell ref="AJ75:AL75"/>
-    <mergeCell ref="AM75:AO75"/>
-    <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="E75:G75"/>
     <mergeCell ref="H75:J75"/>
     <mergeCell ref="K75:M75"/>
@@ -16948,9 +16964,6 @@
     <mergeCell ref="Y75:AA75"/>
     <mergeCell ref="AB74:AD74"/>
     <mergeCell ref="AG74:AI74"/>
-    <mergeCell ref="AJ74:AL74"/>
-    <mergeCell ref="AM74:AO74"/>
-    <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="E74:G74"/>
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="K74:M74"/>
@@ -16958,14 +16971,15 @@
     <mergeCell ref="S74:U74"/>
     <mergeCell ref="V74:X74"/>
     <mergeCell ref="Y74:AA74"/>
-    <mergeCell ref="AB73:AD73"/>
-    <mergeCell ref="AG73:AI73"/>
-    <mergeCell ref="AJ73:AL73"/>
-    <mergeCell ref="AM73:AO73"/>
-    <mergeCell ref="AP73:AR73"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="K73:M73"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="S81:U81"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="Y81:AA81"/>
+    <mergeCell ref="AB80:AD80"/>
+    <mergeCell ref="AG80:AI80"/>
     <mergeCell ref="N73:P73"/>
     <mergeCell ref="S73:U73"/>
     <mergeCell ref="V73:X73"/>
@@ -16975,16 +16989,20 @@
     <mergeCell ref="AJ81:AL81"/>
     <mergeCell ref="AM81:AO81"/>
     <mergeCell ref="AP81:AR81"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="H81:J81"/>
-    <mergeCell ref="K81:M81"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="S81:U81"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="Y81:AA81"/>
-    <mergeCell ref="AB10:AD10"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AJ80:AL80"/>
+    <mergeCell ref="AM80:AO80"/>
+    <mergeCell ref="AP75:AR75"/>
+    <mergeCell ref="AJ74:AL74"/>
+    <mergeCell ref="AM74:AO74"/>
+    <mergeCell ref="AP74:AR74"/>
+    <mergeCell ref="AP77:AR77"/>
+    <mergeCell ref="AJ76:AL76"/>
+    <mergeCell ref="AM76:AO76"/>
+    <mergeCell ref="AP76:AR76"/>
+    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AJ78:AL78"/>
+    <mergeCell ref="AM78:AO78"/>
+    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="AM10:AO10"/>
     <mergeCell ref="AP10:AR10"/>
     <mergeCell ref="E10:G10"/>
@@ -16994,7 +17012,6 @@
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AG9:AI9"/>
     <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AM9:AO9"/>
@@ -17015,10 +17032,6 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AB80:AD80"/>
-    <mergeCell ref="AG80:AI80"/>
-    <mergeCell ref="AJ80:AL80"/>
-    <mergeCell ref="AM80:AO80"/>
     <mergeCell ref="AP80:AR80"/>
     <mergeCell ref="E80:G80"/>
     <mergeCell ref="H80:J80"/>
@@ -17039,6 +17052,10 @@
     <mergeCell ref="S72:U72"/>
     <mergeCell ref="V72:X72"/>
     <mergeCell ref="Y72:AA72"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="K73:M73"/>
     <mergeCell ref="AB71:AD71"/>
     <mergeCell ref="AG71:AI71"/>
     <mergeCell ref="AJ71:AL71"/>
@@ -17258,7 +17275,7 @@
       <c r="R4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="S4" s="37"/>
+      <c r="S4" s="36"/>
       <c r="T4" s="30"/>
       <c r="AF4" s="14" t="s">
         <v>5</v>
@@ -17321,7 +17338,7 @@
       <c r="AF5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="AG5" s="36" t="s">
+      <c r="AG5" s="37" t="s">
         <v>138</v>
       </c>
       <c r="AH5" s="21"/>
@@ -22035,6 +22052,12 @@
     <mergeCell ref="AB11:AD11"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AM6:AO6"/>
     <mergeCell ref="AP6:AR6"/>
     <mergeCell ref="AP8:AR8"/>
@@ -22051,11 +22074,6 @@
     <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="AM7:AO7"/>
     <mergeCell ref="AP7:AR7"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
     <mergeCell ref="S7:U7"/>
     <mergeCell ref="V5:X5"/>
     <mergeCell ref="Y5:AA5"/>
@@ -22073,7 +22091,21 @@
     <mergeCell ref="AG79:AI79"/>
     <mergeCell ref="AJ79:AL79"/>
     <mergeCell ref="AM79:AO79"/>
-    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AB77:AD77"/>
+    <mergeCell ref="AG77:AI77"/>
+    <mergeCell ref="AJ77:AL77"/>
+    <mergeCell ref="AM77:AO77"/>
+    <mergeCell ref="AB75:AD75"/>
+    <mergeCell ref="AG75:AI75"/>
+    <mergeCell ref="AJ75:AL75"/>
+    <mergeCell ref="AM75:AO75"/>
+    <mergeCell ref="AB73:AD73"/>
+    <mergeCell ref="AG73:AI73"/>
+    <mergeCell ref="AJ73:AL73"/>
+    <mergeCell ref="AM73:AO73"/>
+    <mergeCell ref="AB10:AD10"/>
+    <mergeCell ref="AG10:AI10"/>
+    <mergeCell ref="AJ10:AL10"/>
     <mergeCell ref="E79:G79"/>
     <mergeCell ref="H79:J79"/>
     <mergeCell ref="K79:M79"/>
@@ -22083,9 +22115,6 @@
     <mergeCell ref="Y79:AA79"/>
     <mergeCell ref="AB78:AD78"/>
     <mergeCell ref="AG78:AI78"/>
-    <mergeCell ref="AJ78:AL78"/>
-    <mergeCell ref="AM78:AO78"/>
-    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="E78:G78"/>
     <mergeCell ref="H78:J78"/>
     <mergeCell ref="K78:M78"/>
@@ -22093,11 +22122,6 @@
     <mergeCell ref="S78:U78"/>
     <mergeCell ref="V78:X78"/>
     <mergeCell ref="Y78:AA78"/>
-    <mergeCell ref="AB77:AD77"/>
-    <mergeCell ref="AG77:AI77"/>
-    <mergeCell ref="AJ77:AL77"/>
-    <mergeCell ref="AM77:AO77"/>
-    <mergeCell ref="AP77:AR77"/>
     <mergeCell ref="E77:G77"/>
     <mergeCell ref="H77:J77"/>
     <mergeCell ref="K77:M77"/>
@@ -22107,9 +22131,6 @@
     <mergeCell ref="Y77:AA77"/>
     <mergeCell ref="AB76:AD76"/>
     <mergeCell ref="AG76:AI76"/>
-    <mergeCell ref="AJ76:AL76"/>
-    <mergeCell ref="AM76:AO76"/>
-    <mergeCell ref="AP76:AR76"/>
     <mergeCell ref="E76:G76"/>
     <mergeCell ref="H76:J76"/>
     <mergeCell ref="K76:M76"/>
@@ -22117,11 +22138,6 @@
     <mergeCell ref="S76:U76"/>
     <mergeCell ref="V76:X76"/>
     <mergeCell ref="Y76:AA76"/>
-    <mergeCell ref="AB75:AD75"/>
-    <mergeCell ref="AG75:AI75"/>
-    <mergeCell ref="AJ75:AL75"/>
-    <mergeCell ref="AM75:AO75"/>
-    <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="E75:G75"/>
     <mergeCell ref="H75:J75"/>
     <mergeCell ref="K75:M75"/>
@@ -22131,9 +22147,6 @@
     <mergeCell ref="Y75:AA75"/>
     <mergeCell ref="AB74:AD74"/>
     <mergeCell ref="AG74:AI74"/>
-    <mergeCell ref="AJ74:AL74"/>
-    <mergeCell ref="AM74:AO74"/>
-    <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="E74:G74"/>
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="K74:M74"/>
@@ -22141,14 +22154,15 @@
     <mergeCell ref="S74:U74"/>
     <mergeCell ref="V74:X74"/>
     <mergeCell ref="Y74:AA74"/>
-    <mergeCell ref="AB73:AD73"/>
-    <mergeCell ref="AG73:AI73"/>
-    <mergeCell ref="AJ73:AL73"/>
-    <mergeCell ref="AM73:AO73"/>
-    <mergeCell ref="AP73:AR73"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="K73:M73"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="S81:U81"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="Y81:AA81"/>
+    <mergeCell ref="AB80:AD80"/>
+    <mergeCell ref="AG80:AI80"/>
     <mergeCell ref="N73:P73"/>
     <mergeCell ref="S73:U73"/>
     <mergeCell ref="V73:X73"/>
@@ -22158,16 +22172,20 @@
     <mergeCell ref="AJ81:AL81"/>
     <mergeCell ref="AM81:AO81"/>
     <mergeCell ref="AP81:AR81"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="H81:J81"/>
-    <mergeCell ref="K81:M81"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="S81:U81"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="Y81:AA81"/>
-    <mergeCell ref="AB10:AD10"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AJ80:AL80"/>
+    <mergeCell ref="AM80:AO80"/>
+    <mergeCell ref="AP75:AR75"/>
+    <mergeCell ref="AJ74:AL74"/>
+    <mergeCell ref="AM74:AO74"/>
+    <mergeCell ref="AP74:AR74"/>
+    <mergeCell ref="AP77:AR77"/>
+    <mergeCell ref="AJ76:AL76"/>
+    <mergeCell ref="AM76:AO76"/>
+    <mergeCell ref="AP76:AR76"/>
+    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AJ78:AL78"/>
+    <mergeCell ref="AM78:AO78"/>
+    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="AM10:AO10"/>
     <mergeCell ref="AP10:AR10"/>
     <mergeCell ref="E10:G10"/>
@@ -22177,7 +22195,6 @@
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AG9:AI9"/>
     <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AM9:AO9"/>
@@ -22198,10 +22215,6 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AB80:AD80"/>
-    <mergeCell ref="AG80:AI80"/>
-    <mergeCell ref="AJ80:AL80"/>
-    <mergeCell ref="AM80:AO80"/>
     <mergeCell ref="AP80:AR80"/>
     <mergeCell ref="E80:G80"/>
     <mergeCell ref="H80:J80"/>
@@ -22222,6 +22235,10 @@
     <mergeCell ref="S72:U72"/>
     <mergeCell ref="V72:X72"/>
     <mergeCell ref="Y72:AA72"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="K73:M73"/>
     <mergeCell ref="AB71:AD71"/>
     <mergeCell ref="AG71:AI71"/>
     <mergeCell ref="AJ71:AL71"/>

--- a/To-Do/MainALR.xlsx
+++ b/To-Do/MainALR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmcdonnell1\Downloads\Cost-of-Betrayal\To-Do\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266356D0-C831-4220-B21A-167CD99E0F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46177AEA-2911-4581-8E72-5D74F8705D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42696" yWindow="144" windowWidth="17880" windowHeight="15348" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="154">
   <si>
     <t>MainALR</t>
   </si>
@@ -203,9 +203,6 @@
   </si>
   <si>
     <t>Basic Movement Section</t>
-  </si>
-  <si>
-    <t>Node Name: Start Movement Section</t>
   </si>
   <si>
     <t>A node that'll take an existing object in the game, and then utilize the fade ui to seemlessly switch from a scene in which you're only watching, to a playable section with limited movement for the player to do certain actions</t>
@@ -482,6 +479,27 @@
   </si>
   <si>
     <t>BPI_MusicHandler</t>
+  </si>
+  <si>
+    <t>Node Name: Swap Scene Type</t>
+  </si>
+  <si>
+    <t>Freeroam Movement</t>
+  </si>
+  <si>
+    <t>Node Name: Begin Freeroam</t>
+  </si>
+  <si>
+    <t>Screen Shakeing</t>
+  </si>
+  <si>
+    <t>Node Name: Shake Event</t>
+  </si>
+  <si>
+    <t>A node that'll allow developers to switch from a regular scene to one in witch the player has complete control of the movement of the character and can interact with the background and area around them</t>
+  </si>
+  <si>
+    <t>A node that'll allow developers to call of a shake effect to simulate something slamming into something else, an earthquake, or any other similar effect</t>
   </si>
 </sst>
 </file>
@@ -2163,7 +2181,7 @@
     </row>
     <row r="20" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D20" s="7" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>59</v>
@@ -2171,12 +2189,12 @@
       <c r="F20" s="16"/>
       <c r="G20" s="17"/>
       <c r="H20" s="15" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="I20" s="16"/>
       <c r="J20" s="17"/>
       <c r="K20" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="17"/>
@@ -2207,19 +2225,21 @@
       <c r="AM20" s="17"/>
     </row>
     <row r="21" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D21" s="8"/>
+      <c r="D21" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="E21" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="17"/>
       <c r="H21" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I21" s="16"/>
       <c r="J21" s="17"/>
       <c r="K21" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="17"/>
@@ -2254,17 +2274,17 @@
         <v>12</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="17"/>
       <c r="H22" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I22" s="16"/>
       <c r="J22" s="17"/>
       <c r="K22" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="17"/>
@@ -2299,17 +2319,17 @@
         <v>12</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="17"/>
       <c r="H23" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="17"/>
       <c r="K23" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="17"/>
@@ -2341,13 +2361,19 @@
     </row>
     <row r="24" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="7"/>
-      <c r="E24" s="15"/>
+      <c r="E24" s="15" t="s">
+        <v>148</v>
+      </c>
       <c r="F24" s="16"/>
       <c r="G24" s="17"/>
-      <c r="H24" s="24"/>
+      <c r="H24" s="24" t="s">
+        <v>149</v>
+      </c>
       <c r="I24" s="16"/>
       <c r="J24" s="17"/>
-      <c r="K24" s="24"/>
+      <c r="K24" s="24" t="s">
+        <v>152</v>
+      </c>
       <c r="L24" s="16"/>
       <c r="M24" s="17"/>
       <c r="N24" s="2"/>
@@ -2378,13 +2404,19 @@
     </row>
     <row r="25" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="8"/>
-      <c r="E25" s="18"/>
+      <c r="E25" s="18" t="s">
+        <v>150</v>
+      </c>
       <c r="F25" s="16"/>
       <c r="G25" s="17"/>
-      <c r="H25" s="19"/>
+      <c r="H25" s="19" t="s">
+        <v>151</v>
+      </c>
       <c r="I25" s="16"/>
       <c r="J25" s="17"/>
-      <c r="K25" s="19"/>
+      <c r="K25" s="19" t="s">
+        <v>153</v>
+      </c>
       <c r="L25" s="16"/>
       <c r="M25" s="17"/>
       <c r="N25" s="2"/>
@@ -6769,10 +6801,10 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -6780,7 +6812,7 @@
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -6810,7 +6842,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="17"/>
@@ -6825,7 +6857,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
       <c r="N5" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="17"/>
@@ -6834,7 +6866,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="T5" s="16"/>
       <c r="U5" s="17"/>
@@ -6849,7 +6881,7 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="17"/>
       <c r="AB5" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="17"/>
@@ -6857,7 +6889,7 @@
         <v>7</v>
       </c>
       <c r="AG5" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AH5" s="21"/>
       <c r="AI5" s="22"/>
@@ -6872,7 +6904,7 @@
       <c r="AN5" s="16"/>
       <c r="AO5" s="17"/>
       <c r="AP5" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ5" s="16"/>
       <c r="AR5" s="17"/>
@@ -6886,17 +6918,17 @@
         <v>12</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="17"/>
       <c r="K6" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
@@ -6940,17 +6972,17 @@
         <v>12</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="17"/>
       <c r="K7" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
@@ -6992,17 +7024,17 @@
       <c r="B8" s="17"/>
       <c r="D8" s="7"/>
       <c r="E8" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="17"/>
       <c r="H8" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="17"/>
       <c r="K8" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="17"/>
@@ -7040,17 +7072,17 @@
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="7"/>
       <c r="E9" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
       <c r="H9" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="17"/>
       <c r="K9" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="17"/>
@@ -7088,17 +7120,17 @@
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="7"/>
       <c r="E10" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="17"/>
       <c r="K10" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
@@ -7135,22 +7167,22 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="7"/>
       <c r="E11" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
       <c r="H11" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="17"/>
       <c r="K11" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="17"/>
@@ -7188,17 +7220,17 @@
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="7"/>
       <c r="E12" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
       <c r="H12" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="17"/>
       <c r="K12" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
@@ -7238,17 +7270,17 @@
         <v>12</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="17"/>
       <c r="H13" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="17"/>
       <c r="K13" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="17"/>
@@ -7286,17 +7318,17 @@
     <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="7"/>
       <c r="E14" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
       <c r="H14" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I14" s="16"/>
       <c r="J14" s="17"/>
       <c r="K14" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="17"/>
@@ -7333,24 +7365,24 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" s="3"/>
       <c r="D15" s="7" t="s">
         <v>58</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
       <c r="H15" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I15" s="16"/>
       <c r="J15" s="17"/>
       <c r="K15" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="17"/>
@@ -11554,7 +11586,6 @@
     <mergeCell ref="S16:U16"/>
     <mergeCell ref="V16:X16"/>
     <mergeCell ref="Y16:AA16"/>
-    <mergeCell ref="AB15:AD15"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="AM15:AO15"/>
@@ -11566,6 +11597,14 @@
     <mergeCell ref="S15:U15"/>
     <mergeCell ref="V15:X15"/>
     <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="S13:U13"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="AB14:AD14"/>
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="AJ14:AL14"/>
@@ -11578,18 +11617,14 @@
     <mergeCell ref="S14:U14"/>
     <mergeCell ref="V14:X14"/>
     <mergeCell ref="Y14:AA14"/>
-    <mergeCell ref="AB13:AD13"/>
-    <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="AM13:AO13"/>
-    <mergeCell ref="AP13:AR13"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="S13:U13"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="AB12:AD12"/>
     <mergeCell ref="AG12:AI12"/>
     <mergeCell ref="AJ12:AL12"/>
@@ -11602,17 +11637,6 @@
     <mergeCell ref="S12:U12"/>
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="AM11:AO11"/>
-    <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="S11:U11"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="E6:G6"/>
@@ -11735,6 +11759,13 @@
     <mergeCell ref="Y81:AA81"/>
     <mergeCell ref="AB80:AD80"/>
     <mergeCell ref="AG80:AI80"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="K80:M80"/>
+    <mergeCell ref="N80:P80"/>
+    <mergeCell ref="S80:U80"/>
+    <mergeCell ref="V80:X80"/>
+    <mergeCell ref="Y80:AA80"/>
     <mergeCell ref="N73:P73"/>
     <mergeCell ref="S73:U73"/>
     <mergeCell ref="V73:X73"/>
@@ -11758,6 +11789,15 @@
     <mergeCell ref="AJ78:AL78"/>
     <mergeCell ref="AM78:AO78"/>
     <mergeCell ref="AP78:AR78"/>
+    <mergeCell ref="AP80:AR80"/>
+    <mergeCell ref="AP9:AR9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AM10:AO10"/>
     <mergeCell ref="AP10:AR10"/>
     <mergeCell ref="E10:G10"/>
@@ -11767,17 +11807,10 @@
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AG9:AI9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="AM9:AO9"/>
-    <mergeCell ref="AP9:AR9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="S72:U72"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Y72:AA72"/>
     <mergeCell ref="AJ8:AL8"/>
     <mergeCell ref="AM8:AO8"/>
     <mergeCell ref="K8:M8"/>
@@ -11787,26 +11820,17 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AP80:AR80"/>
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="K80:M80"/>
-    <mergeCell ref="N80:P80"/>
-    <mergeCell ref="S80:U80"/>
-    <mergeCell ref="V80:X80"/>
-    <mergeCell ref="Y80:AA80"/>
-    <mergeCell ref="AB72:AD72"/>
-    <mergeCell ref="AG72:AI72"/>
-    <mergeCell ref="AJ72:AL72"/>
-    <mergeCell ref="AM72:AO72"/>
-    <mergeCell ref="AP72:AR72"/>
-    <mergeCell ref="E72:G72"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="S72:U72"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Y72:AA72"/>
+    <mergeCell ref="AG9:AI9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AM9:AO9"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="AM11:AO11"/>
+    <mergeCell ref="AB13:AD13"/>
+    <mergeCell ref="AG13:AI13"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="AB15:AD15"/>
     <mergeCell ref="AP73:AR73"/>
     <mergeCell ref="E73:G73"/>
     <mergeCell ref="H73:J73"/>
@@ -11823,6 +11847,14 @@
     <mergeCell ref="S71:U71"/>
     <mergeCell ref="V71:X71"/>
     <mergeCell ref="Y71:AA71"/>
+    <mergeCell ref="AB72:AD72"/>
+    <mergeCell ref="AG72:AI72"/>
+    <mergeCell ref="AJ72:AL72"/>
+    <mergeCell ref="AM72:AO72"/>
+    <mergeCell ref="AP72:AR72"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="K72:M72"/>
     <mergeCell ref="AB70:AD70"/>
     <mergeCell ref="AG70:AI70"/>
     <mergeCell ref="AJ70:AL70"/>
@@ -12000,10 +12032,10 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -12011,7 +12043,7 @@
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -12041,7 +12073,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="17"/>
@@ -12056,7 +12088,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
       <c r="N5" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="17"/>
@@ -12065,7 +12097,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T5" s="16"/>
       <c r="U5" s="17"/>
@@ -12080,7 +12112,7 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="17"/>
       <c r="AB5" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="17"/>
@@ -12088,7 +12120,7 @@
         <v>7</v>
       </c>
       <c r="AG5" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AH5" s="21"/>
       <c r="AI5" s="22"/>
@@ -12103,36 +12135,36 @@
       <c r="AN5" s="16"/>
       <c r="AO5" s="17"/>
       <c r="AP5" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ5" s="16"/>
       <c r="AR5" s="17"/>
     </row>
     <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" s="17"/>
       <c r="D6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="17"/>
       <c r="K6" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
       <c r="N6" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O6" s="16"/>
       <c r="P6" s="17"/>
@@ -12166,27 +12198,27 @@
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B7" s="17"/>
       <c r="D7" s="7"/>
       <c r="E7" s="40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="17"/>
       <c r="K7" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
       <c r="N7" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O7" s="16"/>
       <c r="P7" s="17"/>
@@ -12220,14 +12252,14 @@
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B8" s="17"/>
       <c r="D8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="17"/>
@@ -12237,12 +12269,12 @@
       <c r="I8" s="16"/>
       <c r="J8" s="17"/>
       <c r="K8" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="17"/>
       <c r="N8" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O8" s="16"/>
       <c r="P8" s="17"/>
@@ -12277,22 +12309,22 @@
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="7"/>
       <c r="E9" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
       <c r="H9" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="17"/>
       <c r="K9" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="17"/>
       <c r="N9" s="38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O9" s="16"/>
       <c r="P9" s="17"/>
@@ -12327,22 +12359,22 @@
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="7"/>
       <c r="E10" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="17"/>
       <c r="K10" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
       <c r="N10" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O10" s="16"/>
       <c r="P10" s="17"/>
@@ -12376,22 +12408,22 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="7"/>
       <c r="E11" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
       <c r="H11" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="17"/>
       <c r="K11" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="17"/>
@@ -12429,22 +12461,22 @@
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="7"/>
       <c r="E12" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
       <c r="H12" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="17"/>
       <c r="K12" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
       <c r="N12" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O12" s="16"/>
       <c r="P12" s="17"/>
@@ -12479,22 +12511,22 @@
     <row r="13" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D13" s="7"/>
       <c r="E13" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="17"/>
       <c r="H13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="17"/>
       <c r="K13" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="17"/>
       <c r="N13" s="38" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O13" s="16"/>
       <c r="P13" s="17"/>
@@ -12529,22 +12561,22 @@
     <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="7"/>
       <c r="E14" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
       <c r="H14" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I14" s="16"/>
       <c r="J14" s="17"/>
       <c r="K14" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="17"/>
       <c r="N14" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O14" s="16"/>
       <c r="P14" s="17"/>
@@ -12578,14 +12610,14 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" s="3"/>
       <c r="D15" s="7" t="s">
         <v>58</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
@@ -12595,7 +12627,7 @@
       <c r="I15" s="16"/>
       <c r="J15" s="17"/>
       <c r="K15" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="17"/>
@@ -16799,7 +16831,6 @@
     <mergeCell ref="S16:U16"/>
     <mergeCell ref="V16:X16"/>
     <mergeCell ref="Y16:AA16"/>
-    <mergeCell ref="AB15:AD15"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="AM15:AO15"/>
@@ -16811,6 +16842,14 @@
     <mergeCell ref="S15:U15"/>
     <mergeCell ref="V15:X15"/>
     <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="S13:U13"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="AB14:AD14"/>
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="AJ14:AL14"/>
@@ -16823,18 +16862,14 @@
     <mergeCell ref="S14:U14"/>
     <mergeCell ref="V14:X14"/>
     <mergeCell ref="Y14:AA14"/>
-    <mergeCell ref="AB13:AD13"/>
-    <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="AM13:AO13"/>
-    <mergeCell ref="AP13:AR13"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="S13:U13"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="AB12:AD12"/>
     <mergeCell ref="AG12:AI12"/>
     <mergeCell ref="AJ12:AL12"/>
@@ -16847,17 +16882,6 @@
     <mergeCell ref="S12:U12"/>
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="AM11:AO11"/>
-    <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="S11:U11"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="E6:G6"/>
@@ -16980,6 +17004,13 @@
     <mergeCell ref="Y81:AA81"/>
     <mergeCell ref="AB80:AD80"/>
     <mergeCell ref="AG80:AI80"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="K80:M80"/>
+    <mergeCell ref="N80:P80"/>
+    <mergeCell ref="S80:U80"/>
+    <mergeCell ref="V80:X80"/>
+    <mergeCell ref="Y80:AA80"/>
     <mergeCell ref="N73:P73"/>
     <mergeCell ref="S73:U73"/>
     <mergeCell ref="V73:X73"/>
@@ -17003,6 +17034,15 @@
     <mergeCell ref="AJ78:AL78"/>
     <mergeCell ref="AM78:AO78"/>
     <mergeCell ref="AP78:AR78"/>
+    <mergeCell ref="AP80:AR80"/>
+    <mergeCell ref="AP9:AR9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AM10:AO10"/>
     <mergeCell ref="AP10:AR10"/>
     <mergeCell ref="E10:G10"/>
@@ -17012,17 +17052,10 @@
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AG9:AI9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="AM9:AO9"/>
-    <mergeCell ref="AP9:AR9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="S72:U72"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Y72:AA72"/>
     <mergeCell ref="AJ8:AL8"/>
     <mergeCell ref="AM8:AO8"/>
     <mergeCell ref="K8:M8"/>
@@ -17032,26 +17065,17 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AP80:AR80"/>
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="K80:M80"/>
-    <mergeCell ref="N80:P80"/>
-    <mergeCell ref="S80:U80"/>
-    <mergeCell ref="V80:X80"/>
-    <mergeCell ref="Y80:AA80"/>
-    <mergeCell ref="AB72:AD72"/>
-    <mergeCell ref="AG72:AI72"/>
-    <mergeCell ref="AJ72:AL72"/>
-    <mergeCell ref="AM72:AO72"/>
-    <mergeCell ref="AP72:AR72"/>
-    <mergeCell ref="E72:G72"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="S72:U72"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Y72:AA72"/>
+    <mergeCell ref="AG9:AI9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AM9:AO9"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="AM11:AO11"/>
+    <mergeCell ref="AB13:AD13"/>
+    <mergeCell ref="AG13:AI13"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="AB15:AD15"/>
     <mergeCell ref="AP73:AR73"/>
     <mergeCell ref="E73:G73"/>
     <mergeCell ref="H73:J73"/>
@@ -17068,6 +17092,14 @@
     <mergeCell ref="S71:U71"/>
     <mergeCell ref="V71:X71"/>
     <mergeCell ref="Y71:AA71"/>
+    <mergeCell ref="AB72:AD72"/>
+    <mergeCell ref="AG72:AI72"/>
+    <mergeCell ref="AJ72:AL72"/>
+    <mergeCell ref="AM72:AO72"/>
+    <mergeCell ref="AP72:AR72"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="K72:M72"/>
     <mergeCell ref="AB70:AD70"/>
     <mergeCell ref="AG70:AI70"/>
     <mergeCell ref="AJ70:AL70"/>
@@ -17251,10 +17283,10 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -17262,7 +17294,7 @@
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -17292,7 +17324,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="17"/>
@@ -17307,7 +17339,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
       <c r="N5" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="17"/>
@@ -17316,7 +17348,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T5" s="16"/>
       <c r="U5" s="17"/>
@@ -17331,7 +17363,7 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="17"/>
       <c r="AB5" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="17"/>
@@ -17339,7 +17371,7 @@
         <v>7</v>
       </c>
       <c r="AG5" s="37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AH5" s="21"/>
       <c r="AI5" s="22"/>
@@ -17354,7 +17386,7 @@
       <c r="AN5" s="16"/>
       <c r="AO5" s="17"/>
       <c r="AP5" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ5" s="16"/>
       <c r="AR5" s="17"/>
@@ -17368,17 +17400,17 @@
         <v>12</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="17"/>
       <c r="K6" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
@@ -17420,17 +17452,17 @@
       <c r="B7" s="17"/>
       <c r="D7" s="7"/>
       <c r="E7" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="17"/>
       <c r="K7" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
@@ -17597,7 +17629,7 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="7"/>
@@ -17769,7 +17801,7 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" s="3"/>
       <c r="D15" s="7"/>
@@ -21982,7 +22014,6 @@
     <mergeCell ref="S16:U16"/>
     <mergeCell ref="V16:X16"/>
     <mergeCell ref="Y16:AA16"/>
-    <mergeCell ref="AB15:AD15"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="AM15:AO15"/>
@@ -21994,6 +22025,14 @@
     <mergeCell ref="S15:U15"/>
     <mergeCell ref="V15:X15"/>
     <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="S13:U13"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="AB14:AD14"/>
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="AJ14:AL14"/>
@@ -22006,18 +22045,14 @@
     <mergeCell ref="S14:U14"/>
     <mergeCell ref="V14:X14"/>
     <mergeCell ref="Y14:AA14"/>
-    <mergeCell ref="AB13:AD13"/>
-    <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="AM13:AO13"/>
-    <mergeCell ref="AP13:AR13"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="S13:U13"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="AB12:AD12"/>
     <mergeCell ref="AG12:AI12"/>
     <mergeCell ref="AJ12:AL12"/>
@@ -22030,17 +22065,6 @@
     <mergeCell ref="S12:U12"/>
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="AM11:AO11"/>
-    <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="S11:U11"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="E6:G6"/>
@@ -22163,6 +22187,13 @@
     <mergeCell ref="Y81:AA81"/>
     <mergeCell ref="AB80:AD80"/>
     <mergeCell ref="AG80:AI80"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="K80:M80"/>
+    <mergeCell ref="N80:P80"/>
+    <mergeCell ref="S80:U80"/>
+    <mergeCell ref="V80:X80"/>
+    <mergeCell ref="Y80:AA80"/>
     <mergeCell ref="N73:P73"/>
     <mergeCell ref="S73:U73"/>
     <mergeCell ref="V73:X73"/>
@@ -22186,6 +22217,15 @@
     <mergeCell ref="AJ78:AL78"/>
     <mergeCell ref="AM78:AO78"/>
     <mergeCell ref="AP78:AR78"/>
+    <mergeCell ref="AP80:AR80"/>
+    <mergeCell ref="AP9:AR9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="Y9:AA9"/>
     <mergeCell ref="AM10:AO10"/>
     <mergeCell ref="AP10:AR10"/>
     <mergeCell ref="E10:G10"/>
@@ -22195,17 +22235,10 @@
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AG9:AI9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="AM9:AO9"/>
-    <mergeCell ref="AP9:AR9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="S72:U72"/>
+    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="Y72:AA72"/>
     <mergeCell ref="AJ8:AL8"/>
     <mergeCell ref="AM8:AO8"/>
     <mergeCell ref="K8:M8"/>
@@ -22215,26 +22248,17 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AP80:AR80"/>
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="K80:M80"/>
-    <mergeCell ref="N80:P80"/>
-    <mergeCell ref="S80:U80"/>
-    <mergeCell ref="V80:X80"/>
-    <mergeCell ref="Y80:AA80"/>
-    <mergeCell ref="AB72:AD72"/>
-    <mergeCell ref="AG72:AI72"/>
-    <mergeCell ref="AJ72:AL72"/>
-    <mergeCell ref="AM72:AO72"/>
-    <mergeCell ref="AP72:AR72"/>
-    <mergeCell ref="E72:G72"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="N72:P72"/>
-    <mergeCell ref="S72:U72"/>
-    <mergeCell ref="V72:X72"/>
-    <mergeCell ref="Y72:AA72"/>
+    <mergeCell ref="AG9:AI9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="AM9:AO9"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="AM11:AO11"/>
+    <mergeCell ref="AB13:AD13"/>
+    <mergeCell ref="AG13:AI13"/>
+    <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="AB15:AD15"/>
     <mergeCell ref="AP73:AR73"/>
     <mergeCell ref="E73:G73"/>
     <mergeCell ref="H73:J73"/>
@@ -22251,6 +22275,14 @@
     <mergeCell ref="S71:U71"/>
     <mergeCell ref="V71:X71"/>
     <mergeCell ref="Y71:AA71"/>
+    <mergeCell ref="AB72:AD72"/>
+    <mergeCell ref="AG72:AI72"/>
+    <mergeCell ref="AJ72:AL72"/>
+    <mergeCell ref="AM72:AO72"/>
+    <mergeCell ref="AP72:AR72"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="K72:M72"/>
     <mergeCell ref="AB70:AD70"/>
     <mergeCell ref="AG70:AI70"/>
     <mergeCell ref="AJ70:AL70"/>

--- a/To-Do/MainALR.xlsx
+++ b/To-Do/MainALR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmcdonnell1\Downloads\Cost-of-Betrayal\To-Do\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46177AEA-2911-4581-8E72-5D74F8705D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3BD27D-9F06-43A0-8FD9-DCE196FEC1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42696" yWindow="144" windowWidth="17880" windowHeight="15348" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="154">
   <si>
     <t>MainALR</t>
   </si>
@@ -2403,7 +2403,9 @@
       <c r="AM24" s="17"/>
     </row>
     <row r="25" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D25" s="8"/>
+      <c r="D25" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="E25" s="18" t="s">
         <v>150</v>
       </c>

--- a/To-Do/MainALR.xlsx
+++ b/To-Do/MainALR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmcdonnell1\Downloads\Cost-of-Betrayal\To-Do\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DED424-23DD-451A-9DC4-552FE162F222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97789D77-844A-474A-B3D3-9D4B2488FB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42696" yWindow="144" windowWidth="17880" windowHeight="15348" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="172">
   <si>
     <t>MainALR</t>
   </si>
@@ -104,18 +104,6 @@
   </si>
   <si>
     <t>To use the sweep scene node to sweep the camera between two locations, put in the first, and current location, in the Scene #1 Slot. It is very important that the camera is already at the first location you input. Next you input the desired location to interpolate to in the Scene #2 Slot, you'll have to tinker a little bit with the speed and rotate value, the rotate value should probably be VERY low though, the default values are about what is good for most cases.</t>
-  </si>
-  <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>Title Card Popup</t>
-  </si>
-  <si>
-    <t>UI_Popup</t>
-  </si>
-  <si>
-    <t>( TITLE NEEDS TO BE DONE FIRST )  Going to have a popup during in the intro section with a panning camera, this might require some outside UI Design, but honestly it should be something that I can mostly just do inside of Unreal</t>
   </si>
   <si>
     <t>Saving Player Data</t>
@@ -545,6 +533,27 @@
   </si>
   <si>
     <t>A quick time event that'll require the player to spam a button a set amount of times, and if the player doesn't manage to spam it enough, it can lead to an end state, this'll have a customizable amount / resistance based on an integer and/or float value that can be controlled when the node is called</t>
+  </si>
+  <si>
+    <t>Moverment Animation Code</t>
+  </si>
+  <si>
+    <t>BPA_Movement</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>The animation blueprints responsible for handling animations of the player both in and out of playable sections</t>
+  </si>
+  <si>
+    <t>Intro Credits</t>
+  </si>
+  <si>
+    <t>UI_Credits</t>
+  </si>
+  <si>
+    <t>(FIRST SCENE MUST BE DONE) Introduction credits to pop up during the introduction scenes as we get different views of Carl walking through the desert to El Puente, those scenes must be finished so I can get all the timing right</t>
   </si>
 </sst>
 </file>
@@ -1776,20 +1785,20 @@
     </row>
     <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="7" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>28</v>
+        <v>169</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="15" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="17"/>
       <c r="K10" s="15" t="s">
-        <v>30</v>
+        <v>171</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
@@ -1824,17 +1833,17 @@
         <v>12</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
       <c r="H11" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="17"/>
       <c r="K11" s="18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="17"/>
@@ -1869,17 +1878,17 @@
         <v>12</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
       <c r="H12" s="15" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="17"/>
       <c r="K12" s="15" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
@@ -1914,17 +1923,17 @@
         <v>12</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="17"/>
       <c r="H13" s="18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="17"/>
       <c r="K13" s="15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="17"/>
@@ -1959,17 +1968,17 @@
         <v>12</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
       <c r="H14" s="15" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I14" s="16"/>
       <c r="J14" s="17"/>
       <c r="K14" s="15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="17"/>
@@ -2004,17 +2013,17 @@
         <v>12</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
       <c r="H15" s="19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I15" s="16"/>
       <c r="J15" s="17"/>
       <c r="K15" s="19" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="17"/>
@@ -2049,17 +2058,17 @@
         <v>12</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F16" s="21"/>
       <c r="G16" s="22"/>
       <c r="H16" s="23" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I16" s="21"/>
       <c r="J16" s="22"/>
       <c r="K16" s="23" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L16" s="21"/>
       <c r="M16" s="22"/>
@@ -2094,17 +2103,17 @@
         <v>12</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="17"/>
       <c r="H17" s="18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I17" s="16"/>
       <c r="J17" s="17"/>
       <c r="K17" s="18" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L17" s="16"/>
       <c r="M17" s="17"/>
@@ -2139,17 +2148,17 @@
         <v>12</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F18" s="16"/>
       <c r="G18" s="17"/>
       <c r="H18" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="17"/>
       <c r="K18" s="15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="17"/>
@@ -2184,17 +2193,17 @@
         <v>12</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="17"/>
       <c r="H19" s="18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I19" s="16"/>
       <c r="J19" s="17"/>
       <c r="K19" s="18" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L19" s="16"/>
       <c r="M19" s="17"/>
@@ -2229,17 +2238,17 @@
         <v>12</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="17"/>
       <c r="H20" s="15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I20" s="16"/>
       <c r="J20" s="17"/>
       <c r="K20" s="15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="17"/>
@@ -2271,20 +2280,20 @@
     </row>
     <row r="21" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D21" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="17"/>
       <c r="H21" s="18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I21" s="16"/>
       <c r="J21" s="17"/>
       <c r="K21" s="18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="17"/>
@@ -2319,17 +2328,17 @@
         <v>12</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="17"/>
       <c r="H22" s="15" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I22" s="16"/>
       <c r="J22" s="17"/>
       <c r="K22" s="15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="17"/>
@@ -2364,17 +2373,17 @@
         <v>12</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="17"/>
       <c r="H23" s="18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="17"/>
       <c r="K23" s="18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="17"/>
@@ -2406,20 +2415,20 @@
     </row>
     <row r="24" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="7" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="17"/>
       <c r="H24" s="24" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I24" s="16"/>
       <c r="J24" s="17"/>
       <c r="K24" s="24" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L24" s="16"/>
       <c r="M24" s="17"/>
@@ -2454,17 +2463,17 @@
         <v>12</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F25" s="16"/>
       <c r="G25" s="17"/>
       <c r="H25" s="19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I25" s="16"/>
       <c r="J25" s="17"/>
       <c r="K25" s="19" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="17"/>
@@ -2499,17 +2508,17 @@
         <v>12</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="17"/>
       <c r="H26" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I26" s="16"/>
       <c r="J26" s="17"/>
       <c r="K26" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L26" s="16"/>
       <c r="M26" s="17"/>
@@ -2544,17 +2553,17 @@
         <v>12</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F27" s="16"/>
       <c r="G27" s="17"/>
       <c r="H27" s="18" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I27" s="16"/>
       <c r="J27" s="17"/>
       <c r="K27" s="18" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="L27" s="16"/>
       <c r="M27" s="17"/>
@@ -2585,14 +2594,22 @@
       <c r="AM27" s="17"/>
     </row>
     <row r="28" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D28" s="7"/>
-      <c r="E28" s="15"/>
+      <c r="D28" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>165</v>
+      </c>
       <c r="F28" s="16"/>
       <c r="G28" s="17"/>
-      <c r="H28" s="15"/>
+      <c r="H28" s="15" t="s">
+        <v>166</v>
+      </c>
       <c r="I28" s="16"/>
       <c r="J28" s="17"/>
-      <c r="K28" s="15"/>
+      <c r="K28" s="15" t="s">
+        <v>168</v>
+      </c>
       <c r="L28" s="16"/>
       <c r="M28" s="17"/>
       <c r="N28" s="2"/>
@@ -6866,10 +6883,10 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -6877,7 +6894,7 @@
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -6907,7 +6924,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="17"/>
@@ -6922,7 +6939,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
       <c r="N5" s="32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="17"/>
@@ -6931,7 +6948,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="32" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="T5" s="16"/>
       <c r="U5" s="17"/>
@@ -6946,7 +6963,7 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="17"/>
       <c r="AB5" s="32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="17"/>
@@ -6954,7 +6971,7 @@
         <v>7</v>
       </c>
       <c r="AG5" s="37" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AH5" s="21"/>
       <c r="AI5" s="22"/>
@@ -6969,7 +6986,7 @@
       <c r="AN5" s="16"/>
       <c r="AO5" s="17"/>
       <c r="AP5" s="32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AQ5" s="16"/>
       <c r="AR5" s="17"/>
@@ -6983,17 +7000,17 @@
         <v>12</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="17"/>
       <c r="K6" s="15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
@@ -7037,17 +7054,17 @@
         <v>12</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="17"/>
       <c r="K7" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
@@ -7089,17 +7106,17 @@
       <c r="B8" s="17"/>
       <c r="D8" s="7"/>
       <c r="E8" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="17"/>
       <c r="H8" s="18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="17"/>
       <c r="K8" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="17"/>
@@ -7137,17 +7154,17 @@
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="7"/>
       <c r="E9" s="18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
       <c r="H9" s="18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="17"/>
       <c r="K9" s="18" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="17"/>
@@ -7185,17 +7202,17 @@
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="7"/>
       <c r="E10" s="15" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="17"/>
       <c r="K10" s="15" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
@@ -7232,22 +7249,22 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="7"/>
       <c r="E11" s="18" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
       <c r="H11" s="18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="17"/>
       <c r="K11" s="18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="17"/>
@@ -7285,17 +7302,17 @@
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="7"/>
       <c r="E12" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
       <c r="H12" s="18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="17"/>
       <c r="K12" s="15" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
@@ -7335,17 +7352,17 @@
         <v>12</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="17"/>
       <c r="H13" s="18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="17"/>
       <c r="K13" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="17"/>
@@ -7383,17 +7400,17 @@
     <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="7"/>
       <c r="E14" s="15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
       <c r="H14" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I14" s="16"/>
       <c r="J14" s="17"/>
       <c r="K14" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="17"/>
@@ -7430,24 +7447,24 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3"/>
       <c r="D15" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
       <c r="H15" s="18" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I15" s="16"/>
       <c r="J15" s="17"/>
       <c r="K15" s="18" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="17"/>
@@ -12097,10 +12114,10 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -12108,7 +12125,7 @@
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -12138,7 +12155,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="17"/>
@@ -12153,7 +12170,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
       <c r="N5" s="32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="17"/>
@@ -12162,7 +12179,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="32" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T5" s="16"/>
       <c r="U5" s="17"/>
@@ -12177,7 +12194,7 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="17"/>
       <c r="AB5" s="32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="17"/>
@@ -12185,7 +12202,7 @@
         <v>7</v>
       </c>
       <c r="AG5" s="37" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AH5" s="21"/>
       <c r="AI5" s="22"/>
@@ -12200,36 +12217,36 @@
       <c r="AN5" s="16"/>
       <c r="AO5" s="17"/>
       <c r="AP5" s="32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AQ5" s="16"/>
       <c r="AR5" s="17"/>
     </row>
     <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="35" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B6" s="17"/>
       <c r="D6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="15" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="17"/>
       <c r="K6" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
       <c r="N6" s="15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O6" s="16"/>
       <c r="P6" s="17"/>
@@ -12263,27 +12280,27 @@
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="35" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B7" s="17"/>
       <c r="D7" s="7"/>
       <c r="E7" s="40" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="17"/>
       <c r="K7" s="18" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
       <c r="N7" s="18" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="O7" s="16"/>
       <c r="P7" s="17"/>
@@ -12317,29 +12334,29 @@
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="35" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B8" s="17"/>
       <c r="D8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="17"/>
       <c r="H8" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="17"/>
       <c r="K8" s="15" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="17"/>
       <c r="N8" s="15" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O8" s="16"/>
       <c r="P8" s="17"/>
@@ -12374,22 +12391,22 @@
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="7"/>
       <c r="E9" s="18" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
       <c r="H9" s="18" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="17"/>
       <c r="K9" s="18" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="17"/>
       <c r="N9" s="38" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="O9" s="16"/>
       <c r="P9" s="17"/>
@@ -12424,22 +12441,22 @@
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="7"/>
       <c r="E10" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="17"/>
       <c r="K10" s="15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
       <c r="N10" s="15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="O10" s="16"/>
       <c r="P10" s="17"/>
@@ -12473,24 +12490,24 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
       <c r="H11" s="18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="17"/>
       <c r="K11" s="18" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="17"/>
@@ -12528,22 +12545,22 @@
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="7"/>
       <c r="E12" s="15" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
       <c r="H12" s="15" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="17"/>
       <c r="K12" s="15" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
       <c r="N12" s="41" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O12" s="16"/>
       <c r="P12" s="17"/>
@@ -12578,22 +12595,22 @@
     <row r="13" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D13" s="7"/>
       <c r="E13" s="18" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="17"/>
       <c r="H13" s="18" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="17"/>
       <c r="K13" s="18" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="17"/>
       <c r="N13" s="38" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O13" s="16"/>
       <c r="P13" s="17"/>
@@ -12630,22 +12647,22 @@
         <v>12</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
       <c r="H14" s="15" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I14" s="16"/>
       <c r="J14" s="17"/>
       <c r="K14" s="15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="17"/>
       <c r="N14" s="42" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="O14" s="16"/>
       <c r="P14" s="17"/>
@@ -12679,24 +12696,24 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3"/>
       <c r="D15" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
       <c r="H15" s="18" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I15" s="16"/>
       <c r="J15" s="17"/>
       <c r="K15" s="18" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="17"/>
@@ -17352,10 +17369,10 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -17363,7 +17380,7 @@
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -17393,7 +17410,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="17"/>
@@ -17408,7 +17425,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
       <c r="N5" s="32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="17"/>
@@ -17417,7 +17434,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="32" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="T5" s="16"/>
       <c r="U5" s="17"/>
@@ -17432,7 +17449,7 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="17"/>
       <c r="AB5" s="32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="17"/>
@@ -17440,7 +17457,7 @@
         <v>7</v>
       </c>
       <c r="AG5" s="37" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AH5" s="21"/>
       <c r="AI5" s="22"/>
@@ -17455,7 +17472,7 @@
       <c r="AN5" s="16"/>
       <c r="AO5" s="17"/>
       <c r="AP5" s="32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AQ5" s="16"/>
       <c r="AR5" s="17"/>
@@ -17469,17 +17486,17 @@
         <v>12</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="17"/>
       <c r="K6" s="15" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
@@ -17521,17 +17538,17 @@
       <c r="B7" s="17"/>
       <c r="D7" s="7"/>
       <c r="E7" s="18" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="17"/>
       <c r="K7" s="18" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
@@ -17573,17 +17590,17 @@
       <c r="B8" s="17"/>
       <c r="D8" s="7"/>
       <c r="E8" s="15" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="17"/>
       <c r="H8" s="15" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="17"/>
       <c r="K8" s="15" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="17"/>
@@ -17621,17 +17638,17 @@
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="7"/>
       <c r="E9" s="18" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
       <c r="H9" s="18" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="17"/>
       <c r="K9" s="18" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="17"/>
@@ -17669,17 +17686,17 @@
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="7"/>
       <c r="E10" s="15" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="15" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="17"/>
       <c r="K10" s="15" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
@@ -17716,7 +17733,7 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="7"/>
@@ -17888,7 +17905,7 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3"/>
       <c r="D15" s="7"/>

--- a/To-Do/MainALR.xlsx
+++ b/To-Do/MainALR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmcdonnell1\Downloads\Cost-of-Betrayal\To-Do\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A08460-A7E1-49A6-9150-5F4AF7E156AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDA60FC-1116-4045-963C-156A1A8E862C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42696" yWindow="144" windowWidth="17880" windowHeight="15348" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42696" yWindow="144" windowWidth="17880" windowHeight="15348" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coding" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="183">
   <si>
     <t>MainALR</t>
   </si>
@@ -229,9 +229,6 @@
     <t>Node Name: Begin Freeroam</t>
   </si>
   <si>
-    <t>A node that'll allow developers to switch from a regular scene to one in witch the player has complete control of the movement of the character and can interact with the background and area around them</t>
-  </si>
-  <si>
     <t>Screen Shakeing</t>
   </si>
   <si>
@@ -302,12 +299,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>El Puente  Rocky Terrain</t>
-  </si>
-  <si>
-    <t>terrain bro, mostly flat for the town</t>
   </si>
   <si>
     <t>Tumbleweed Model</t>
@@ -587,6 +578,15 @@
   </si>
   <si>
     <t>A blueprint that can allow multiple meshes to be combined into a single model for use in the game up to 6 meshes at once.</t>
+  </si>
+  <si>
+    <t>A node that allows developers to switch from a regular scene to one in which the player has complete control of the movement of the character and can interact with the background and area around them</t>
+  </si>
+  <si>
+    <t>El Puente Props</t>
+  </si>
+  <si>
+    <t>props such as fences, chairs, benches, crates, barrels, a centerpiece for the town, hitching posts, and lanturns. (feel free to add any other shit u come up with too)</t>
   </si>
 </sst>
 </file>
@@ -1830,20 +1830,20 @@
     </row>
     <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="15" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="17"/>
       <c r="K10" s="15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
@@ -2473,7 +2473,7 @@
       <c r="I24" s="16"/>
       <c r="J24" s="17"/>
       <c r="K24" s="18" t="s">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="L24" s="16"/>
       <c r="M24" s="17"/>
@@ -2508,17 +2508,17 @@
         <v>12</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F25" s="16"/>
       <c r="G25" s="17"/>
       <c r="H25" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I25" s="16"/>
       <c r="J25" s="17"/>
       <c r="K25" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="17"/>
@@ -2553,17 +2553,17 @@
         <v>12</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="17"/>
       <c r="H26" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I26" s="16"/>
       <c r="J26" s="17"/>
       <c r="K26" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L26" s="16"/>
       <c r="M26" s="17"/>
@@ -2598,17 +2598,17 @@
         <v>12</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F27" s="16"/>
       <c r="G27" s="17"/>
       <c r="H27" s="25" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I27" s="16"/>
       <c r="J27" s="17"/>
       <c r="K27" s="25" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="L27" s="16"/>
       <c r="M27" s="17"/>
@@ -2640,20 +2640,20 @@
     </row>
     <row r="28" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D28" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="17"/>
       <c r="H28" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I28" s="16"/>
       <c r="J28" s="17"/>
       <c r="K28" s="15" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L28" s="16"/>
       <c r="M28" s="17"/>
@@ -2688,17 +2688,17 @@
         <v>12</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="17"/>
       <c r="H29" s="25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I29" s="16"/>
       <c r="J29" s="17"/>
       <c r="K29" s="25" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L29" s="16"/>
       <c r="M29" s="17"/>
@@ -2731,17 +2731,17 @@
     <row r="30" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D30" s="7"/>
       <c r="E30" s="15" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="17"/>
       <c r="H30" s="15" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I30" s="16"/>
       <c r="J30" s="17"/>
       <c r="K30" s="15" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L30" s="16"/>
       <c r="M30" s="17"/>
@@ -2776,17 +2776,17 @@
         <v>12</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F31" s="16"/>
       <c r="G31" s="17"/>
       <c r="H31" s="25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I31" s="16"/>
       <c r="J31" s="17"/>
       <c r="K31" s="25" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L31" s="16"/>
       <c r="M31" s="17"/>
@@ -2821,17 +2821,17 @@
         <v>12</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="17"/>
       <c r="H32" s="15" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I32" s="16"/>
       <c r="J32" s="17"/>
       <c r="K32" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L32" s="16"/>
       <c r="M32" s="17"/>
@@ -6958,10 +6958,10 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -6969,7 +6969,7 @@
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -6999,7 +6999,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="17"/>
@@ -7014,7 +7014,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
       <c r="N5" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="17"/>
@@ -7023,7 +7023,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T5" s="16"/>
       <c r="U5" s="17"/>
@@ -7038,7 +7038,7 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="17"/>
       <c r="AB5" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="17"/>
@@ -7046,7 +7046,7 @@
         <v>7</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH5" s="20"/>
       <c r="AI5" s="21"/>
@@ -7061,7 +7061,7 @@
       <c r="AN5" s="16"/>
       <c r="AO5" s="17"/>
       <c r="AP5" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AQ5" s="16"/>
       <c r="AR5" s="17"/>
@@ -7075,17 +7075,17 @@
         <v>12</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="17"/>
       <c r="K6" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
@@ -7129,17 +7129,17 @@
         <v>12</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="17"/>
       <c r="K7" s="25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
@@ -7181,17 +7181,17 @@
       <c r="B8" s="17"/>
       <c r="D8" s="7"/>
       <c r="E8" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="17"/>
       <c r="H8" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="17"/>
       <c r="K8" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="17"/>
@@ -7229,17 +7229,17 @@
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="7"/>
       <c r="E9" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
       <c r="H9" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="17"/>
       <c r="K9" s="25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="17"/>
@@ -7277,17 +7277,17 @@
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="7"/>
       <c r="E10" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="17"/>
       <c r="K10" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
@@ -7324,22 +7324,22 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="7"/>
       <c r="E11" s="25" t="s">
-        <v>93</v>
+        <v>181</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
       <c r="H11" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="17"/>
       <c r="K11" s="25" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="17"/>
@@ -7377,17 +7377,17 @@
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="7"/>
       <c r="E12" s="15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
       <c r="H12" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="17"/>
       <c r="K12" s="15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
@@ -7427,17 +7427,17 @@
         <v>12</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="17"/>
       <c r="H13" s="25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="17"/>
       <c r="K13" s="25" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="17"/>
@@ -7473,19 +7473,21 @@
       <c r="AR13" s="17"/>
     </row>
     <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="E14" s="15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
       <c r="H14" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I14" s="16"/>
       <c r="J14" s="17"/>
       <c r="K14" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="17"/>
@@ -7522,24 +7524,24 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15" s="3"/>
       <c r="D15" s="7" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
       <c r="H15" s="25" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I15" s="16"/>
       <c r="J15" s="17"/>
       <c r="K15" s="25" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="17"/>
@@ -12189,10 +12191,10 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -12200,7 +12202,7 @@
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -12230,7 +12232,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="17"/>
@@ -12245,7 +12247,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
       <c r="N5" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="17"/>
@@ -12254,7 +12256,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="31" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T5" s="16"/>
       <c r="U5" s="17"/>
@@ -12269,7 +12271,7 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="17"/>
       <c r="AB5" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="17"/>
@@ -12277,7 +12279,7 @@
         <v>7</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="AH5" s="20"/>
       <c r="AI5" s="21"/>
@@ -12292,36 +12294,36 @@
       <c r="AN5" s="16"/>
       <c r="AO5" s="17"/>
       <c r="AP5" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AQ5" s="16"/>
       <c r="AR5" s="17"/>
     </row>
     <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="29" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B6" s="17"/>
       <c r="D6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="17"/>
       <c r="K6" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
       <c r="N6" s="15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O6" s="16"/>
       <c r="P6" s="17"/>
@@ -12355,29 +12357,29 @@
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="29" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B7" s="17"/>
       <c r="D7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="17"/>
       <c r="K7" s="25" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
       <c r="N7" s="25" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O7" s="16"/>
       <c r="P7" s="17"/>
@@ -12411,14 +12413,14 @@
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B8" s="17"/>
       <c r="D8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="43" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="17"/>
@@ -12428,12 +12430,12 @@
       <c r="I8" s="16"/>
       <c r="J8" s="17"/>
       <c r="K8" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="17"/>
       <c r="N8" s="15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O8" s="16"/>
       <c r="P8" s="17"/>
@@ -12468,22 +12470,22 @@
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="7"/>
       <c r="E9" s="25" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
       <c r="H9" s="25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="17"/>
       <c r="K9" s="25" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="17"/>
       <c r="N9" s="38" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="O9" s="16"/>
       <c r="P9" s="17"/>
@@ -12517,25 +12519,25 @@
     </row>
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="15" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="17"/>
       <c r="K10" s="15" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
       <c r="N10" s="45" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="O10" s="16"/>
       <c r="P10" s="17"/>
@@ -12569,24 +12571,24 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="17"/>
       <c r="H11" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="17"/>
       <c r="K11" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="17"/>
@@ -12626,22 +12628,22 @@
         <v>12</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="17"/>
       <c r="H12" s="15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I12" s="16"/>
       <c r="J12" s="17"/>
       <c r="K12" s="15" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
       <c r="N12" s="42" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O12" s="16"/>
       <c r="P12" s="17"/>
@@ -12678,22 +12680,22 @@
         <v>12</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="17"/>
       <c r="H13" s="25" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="17"/>
       <c r="K13" s="25" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="17"/>
       <c r="N13" s="38" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O13" s="16"/>
       <c r="P13" s="17"/>
@@ -12730,22 +12732,22 @@
         <v>12</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="17"/>
       <c r="H14" s="15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I14" s="16"/>
       <c r="J14" s="17"/>
       <c r="K14" s="15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="17"/>
       <c r="N14" s="39" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O14" s="16"/>
       <c r="P14" s="17"/>
@@ -12779,14 +12781,14 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15" s="3"/>
       <c r="D15" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="17"/>
@@ -12796,7 +12798,7 @@
       <c r="I15" s="16"/>
       <c r="J15" s="17"/>
       <c r="K15" s="25" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="17"/>
@@ -17453,10 +17455,10 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -17464,7 +17466,7 @@
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -17494,7 +17496,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="17"/>
@@ -17509,7 +17511,7 @@
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
       <c r="N5" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="17"/>
@@ -17518,7 +17520,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="31" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="T5" s="16"/>
       <c r="U5" s="17"/>
@@ -17533,7 +17535,7 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="17"/>
       <c r="AB5" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="17"/>
@@ -17541,7 +17543,7 @@
         <v>7</v>
       </c>
       <c r="AG5" s="36" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="AH5" s="20"/>
       <c r="AI5" s="21"/>
@@ -17556,7 +17558,7 @@
       <c r="AN5" s="16"/>
       <c r="AO5" s="17"/>
       <c r="AP5" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AQ5" s="16"/>
       <c r="AR5" s="17"/>
@@ -17570,17 +17572,17 @@
         <v>12</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="15" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I6" s="16"/>
       <c r="J6" s="17"/>
       <c r="K6" s="15" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
@@ -17622,17 +17624,17 @@
       <c r="B7" s="17"/>
       <c r="D7" s="7"/>
       <c r="E7" s="25" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="25" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="17"/>
       <c r="K7" s="25" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
@@ -17674,17 +17676,17 @@
       <c r="B8" s="17"/>
       <c r="D8" s="7"/>
       <c r="E8" s="15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="17"/>
       <c r="H8" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I8" s="16"/>
       <c r="J8" s="17"/>
       <c r="K8" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="17"/>
@@ -17722,17 +17724,17 @@
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="7"/>
       <c r="E9" s="25" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="17"/>
       <c r="H9" s="25" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="17"/>
       <c r="K9" s="25" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="17"/>
@@ -17770,17 +17772,17 @@
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="7"/>
       <c r="E10" s="15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="17"/>
       <c r="H10" s="15" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="17"/>
       <c r="K10" s="15" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
@@ -17817,7 +17819,7 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="7"/>
@@ -17989,7 +17991,7 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15" s="3"/>
       <c r="D15" s="7"/>

--- a/To-Do/MainALR.xlsx
+++ b/To-Do/MainALR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmcdonnell1\Downloads\Cost-of-Betrayal\To-Do\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9364E705-6E2A-42DA-8EE1-09B80F6F92D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C21C490-E870-4A0F-8A2A-CE9D9CBD446E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="47856" yWindow="2832" windowWidth="17928" windowHeight="12168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/To-Do/MainALR.xlsx
+++ b/To-Do/MainALR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmcdonnell1\Downloads\Cost-of-Betrayal\To-Do\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F12E6EE-D562-457D-B82C-1E0D9E984514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D10663-5649-45A8-8970-846B6FF7A524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44892" yWindow="804" windowWidth="17928" windowHeight="12168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42756" yWindow="888" windowWidth="17928" windowHeight="12168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coding" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="210">
   <si>
     <t>MainALR</t>
   </si>
@@ -660,6 +660,15 @@
   <si>
     <t>2 basic lighter noises that can be alternated between the form the typing noises for basic female characters in the game</t>
   </si>
+  <si>
+    <t>Animated Control-less Movement</t>
+  </si>
+  <si>
+    <t>BP_Movement</t>
+  </si>
+  <si>
+    <t>Blueprint / Node that can be used to give the apperance of the player moving while not actually having the player themselves need to push any inputs at all while also working perfectly with the animation system</t>
+  </si>
 </sst>
 </file>
 
@@ -995,8 +1004,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2790,7 +2799,7 @@
     </row>
     <row r="30" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D30" s="7" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>88</v>
@@ -3058,13 +3067,19 @@
     </row>
     <row r="36" spans="4:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D36" s="7"/>
-      <c r="E36" s="15"/>
+      <c r="E36" s="15" t="s">
+        <v>207</v>
+      </c>
       <c r="F36" s="16"/>
       <c r="G36" s="17"/>
-      <c r="H36" s="15"/>
+      <c r="H36" s="15" t="s">
+        <v>208</v>
+      </c>
       <c r="I36" s="16"/>
       <c r="J36" s="17"/>
-      <c r="K36" s="15"/>
+      <c r="K36" s="15" t="s">
+        <v>209</v>
+      </c>
       <c r="L36" s="16"/>
       <c r="M36" s="17"/>
       <c r="N36" s="2"/>
@@ -6572,6 +6587,11 @@
     <mergeCell ref="R10:T10"/>
     <mergeCell ref="U10:W10"/>
     <mergeCell ref="X10:Z10"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="AB9:AD9"/>
+    <mergeCell ref="AE9:AG9"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="AK9:AM9"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="K5:M5"/>
@@ -6582,6 +6602,8 @@
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
     <mergeCell ref="AK83:AM83"/>
     <mergeCell ref="E83:G83"/>
     <mergeCell ref="H83:J83"/>
@@ -6683,6 +6705,11 @@
     <mergeCell ref="H93:J93"/>
     <mergeCell ref="K93:M93"/>
     <mergeCell ref="E94:G94"/>
+    <mergeCell ref="E91:G91"/>
+    <mergeCell ref="H91:J91"/>
+    <mergeCell ref="K91:M91"/>
+    <mergeCell ref="H90:J90"/>
+    <mergeCell ref="K90:M90"/>
     <mergeCell ref="H109:J109"/>
     <mergeCell ref="K109:M109"/>
     <mergeCell ref="E107:G107"/>
@@ -6710,14 +6737,6 @@
     <mergeCell ref="H102:J102"/>
     <mergeCell ref="K102:M102"/>
     <mergeCell ref="E103:G103"/>
-    <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="AB9:AD9"/>
-    <mergeCell ref="AE9:AG9"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="AK9:AM9"/>
-    <mergeCell ref="E91:G91"/>
-    <mergeCell ref="H91:J91"/>
-    <mergeCell ref="K91:M91"/>
     <mergeCell ref="H100:J100"/>
     <mergeCell ref="K100:M100"/>
     <mergeCell ref="E98:G98"/>
@@ -6727,8 +6746,6 @@
     <mergeCell ref="H99:J99"/>
     <mergeCell ref="K99:M99"/>
     <mergeCell ref="E100:G100"/>
-    <mergeCell ref="H90:J90"/>
-    <mergeCell ref="K90:M90"/>
     <mergeCell ref="E88:G88"/>
     <mergeCell ref="H88:J88"/>
     <mergeCell ref="K88:M88"/>
@@ -6738,6 +6755,21 @@
     <mergeCell ref="AB7:AD7"/>
     <mergeCell ref="AE7:AG7"/>
     <mergeCell ref="AH7:AJ7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="AB78:AD78"/>
+    <mergeCell ref="AE78:AG78"/>
+    <mergeCell ref="AH78:AJ78"/>
+    <mergeCell ref="AB76:AD76"/>
+    <mergeCell ref="AE76:AG76"/>
+    <mergeCell ref="AH76:AJ76"/>
     <mergeCell ref="AK7:AM7"/>
     <mergeCell ref="O8:Q8"/>
     <mergeCell ref="R8:T8"/>
@@ -6747,6 +6779,9 @@
     <mergeCell ref="AE8:AG8"/>
     <mergeCell ref="AH8:AJ8"/>
     <mergeCell ref="AK8:AM8"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="U7:W7"/>
     <mergeCell ref="AE5:AG5"/>
     <mergeCell ref="AH5:AJ5"/>
     <mergeCell ref="AK5:AM5"/>
@@ -6769,23 +6804,6 @@
     <mergeCell ref="X5:Z5"/>
     <mergeCell ref="AB5:AD5"/>
     <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="R7:T7"/>
-    <mergeCell ref="U7:W7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="U9:W9"/>
-    <mergeCell ref="AB78:AD78"/>
-    <mergeCell ref="AE78:AG78"/>
-    <mergeCell ref="AH78:AJ78"/>
     <mergeCell ref="AK78:AM78"/>
     <mergeCell ref="E78:G78"/>
     <mergeCell ref="H78:J78"/>
@@ -6805,9 +6823,6 @@
     <mergeCell ref="R77:T77"/>
     <mergeCell ref="U77:W77"/>
     <mergeCell ref="X77:Z77"/>
-    <mergeCell ref="AB76:AD76"/>
-    <mergeCell ref="AE76:AG76"/>
-    <mergeCell ref="AH76:AJ76"/>
     <mergeCell ref="AK76:AM76"/>
     <mergeCell ref="E76:G76"/>
     <mergeCell ref="H76:J76"/>
@@ -7066,7 +7081,7 @@
       <c r="R4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="S4" s="37"/>
+      <c r="S4" s="36"/>
       <c r="T4" s="30"/>
       <c r="AF4" s="14" t="s">
         <v>5</v>
@@ -7129,7 +7144,7 @@
       <c r="AF5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="AG5" s="36" t="s">
+      <c r="AG5" s="37" t="s">
         <v>109</v>
       </c>
       <c r="AH5" s="21"/>
@@ -11937,6 +11952,12 @@
     <mergeCell ref="AB11:AD11"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AM6:AO6"/>
     <mergeCell ref="AP6:AR6"/>
     <mergeCell ref="AP8:AR8"/>
@@ -11953,11 +11974,6 @@
     <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="AM7:AO7"/>
     <mergeCell ref="AP7:AR7"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
     <mergeCell ref="S7:U7"/>
     <mergeCell ref="V5:X5"/>
     <mergeCell ref="Y5:AA5"/>
@@ -11975,7 +11991,21 @@
     <mergeCell ref="AG79:AI79"/>
     <mergeCell ref="AJ79:AL79"/>
     <mergeCell ref="AM79:AO79"/>
-    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AB77:AD77"/>
+    <mergeCell ref="AG77:AI77"/>
+    <mergeCell ref="AJ77:AL77"/>
+    <mergeCell ref="AM77:AO77"/>
+    <mergeCell ref="AB75:AD75"/>
+    <mergeCell ref="AG75:AI75"/>
+    <mergeCell ref="AJ75:AL75"/>
+    <mergeCell ref="AM75:AO75"/>
+    <mergeCell ref="AB73:AD73"/>
+    <mergeCell ref="AG73:AI73"/>
+    <mergeCell ref="AJ73:AL73"/>
+    <mergeCell ref="AM73:AO73"/>
+    <mergeCell ref="AB10:AD10"/>
+    <mergeCell ref="AG10:AI10"/>
+    <mergeCell ref="AJ10:AL10"/>
     <mergeCell ref="E79:G79"/>
     <mergeCell ref="H79:J79"/>
     <mergeCell ref="K79:M79"/>
@@ -11985,9 +12015,6 @@
     <mergeCell ref="Y79:AA79"/>
     <mergeCell ref="AB78:AD78"/>
     <mergeCell ref="AG78:AI78"/>
-    <mergeCell ref="AJ78:AL78"/>
-    <mergeCell ref="AM78:AO78"/>
-    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="E78:G78"/>
     <mergeCell ref="H78:J78"/>
     <mergeCell ref="K78:M78"/>
@@ -11995,11 +12022,6 @@
     <mergeCell ref="S78:U78"/>
     <mergeCell ref="V78:X78"/>
     <mergeCell ref="Y78:AA78"/>
-    <mergeCell ref="AB77:AD77"/>
-    <mergeCell ref="AG77:AI77"/>
-    <mergeCell ref="AJ77:AL77"/>
-    <mergeCell ref="AM77:AO77"/>
-    <mergeCell ref="AP77:AR77"/>
     <mergeCell ref="E77:G77"/>
     <mergeCell ref="H77:J77"/>
     <mergeCell ref="K77:M77"/>
@@ -12009,9 +12031,6 @@
     <mergeCell ref="Y77:AA77"/>
     <mergeCell ref="AB76:AD76"/>
     <mergeCell ref="AG76:AI76"/>
-    <mergeCell ref="AJ76:AL76"/>
-    <mergeCell ref="AM76:AO76"/>
-    <mergeCell ref="AP76:AR76"/>
     <mergeCell ref="E76:G76"/>
     <mergeCell ref="H76:J76"/>
     <mergeCell ref="K76:M76"/>
@@ -12019,11 +12038,6 @@
     <mergeCell ref="S76:U76"/>
     <mergeCell ref="V76:X76"/>
     <mergeCell ref="Y76:AA76"/>
-    <mergeCell ref="AB75:AD75"/>
-    <mergeCell ref="AG75:AI75"/>
-    <mergeCell ref="AJ75:AL75"/>
-    <mergeCell ref="AM75:AO75"/>
-    <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="E75:G75"/>
     <mergeCell ref="H75:J75"/>
     <mergeCell ref="K75:M75"/>
@@ -12033,9 +12047,6 @@
     <mergeCell ref="Y75:AA75"/>
     <mergeCell ref="AB74:AD74"/>
     <mergeCell ref="AG74:AI74"/>
-    <mergeCell ref="AJ74:AL74"/>
-    <mergeCell ref="AM74:AO74"/>
-    <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="E74:G74"/>
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="K74:M74"/>
@@ -12043,14 +12054,15 @@
     <mergeCell ref="S74:U74"/>
     <mergeCell ref="V74:X74"/>
     <mergeCell ref="Y74:AA74"/>
-    <mergeCell ref="AB73:AD73"/>
-    <mergeCell ref="AG73:AI73"/>
-    <mergeCell ref="AJ73:AL73"/>
-    <mergeCell ref="AM73:AO73"/>
-    <mergeCell ref="AP73:AR73"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="K73:M73"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="S81:U81"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="Y81:AA81"/>
+    <mergeCell ref="AB80:AD80"/>
+    <mergeCell ref="AG80:AI80"/>
     <mergeCell ref="N73:P73"/>
     <mergeCell ref="S73:U73"/>
     <mergeCell ref="V73:X73"/>
@@ -12060,16 +12072,20 @@
     <mergeCell ref="AJ81:AL81"/>
     <mergeCell ref="AM81:AO81"/>
     <mergeCell ref="AP81:AR81"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="H81:J81"/>
-    <mergeCell ref="K81:M81"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="S81:U81"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="Y81:AA81"/>
-    <mergeCell ref="AB10:AD10"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AJ80:AL80"/>
+    <mergeCell ref="AM80:AO80"/>
+    <mergeCell ref="AP75:AR75"/>
+    <mergeCell ref="AJ74:AL74"/>
+    <mergeCell ref="AM74:AO74"/>
+    <mergeCell ref="AP74:AR74"/>
+    <mergeCell ref="AP77:AR77"/>
+    <mergeCell ref="AJ76:AL76"/>
+    <mergeCell ref="AM76:AO76"/>
+    <mergeCell ref="AP76:AR76"/>
+    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AJ78:AL78"/>
+    <mergeCell ref="AM78:AO78"/>
+    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="AM10:AO10"/>
     <mergeCell ref="AP10:AR10"/>
     <mergeCell ref="E10:G10"/>
@@ -12079,7 +12095,6 @@
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AG9:AI9"/>
     <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AM9:AO9"/>
@@ -12100,10 +12115,6 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AB80:AD80"/>
-    <mergeCell ref="AG80:AI80"/>
-    <mergeCell ref="AJ80:AL80"/>
-    <mergeCell ref="AM80:AO80"/>
     <mergeCell ref="AP80:AR80"/>
     <mergeCell ref="E80:G80"/>
     <mergeCell ref="H80:J80"/>
@@ -12124,6 +12135,10 @@
     <mergeCell ref="S72:U72"/>
     <mergeCell ref="V72:X72"/>
     <mergeCell ref="Y72:AA72"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="K73:M73"/>
     <mergeCell ref="AB71:AD71"/>
     <mergeCell ref="AG71:AI71"/>
     <mergeCell ref="AJ71:AL71"/>
@@ -12337,7 +12352,7 @@
       <c r="R4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="S4" s="37"/>
+      <c r="S4" s="36"/>
       <c r="T4" s="30"/>
       <c r="AF4" s="14" t="s">
         <v>5</v>
@@ -12400,7 +12415,7 @@
       <c r="AF5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="AG5" s="36" t="s">
+      <c r="AG5" s="37" t="s">
         <v>149</v>
       </c>
       <c r="AH5" s="21"/>
@@ -17202,6 +17217,12 @@
     <mergeCell ref="AB11:AD11"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AM6:AO6"/>
     <mergeCell ref="AP6:AR6"/>
     <mergeCell ref="AP8:AR8"/>
@@ -17218,11 +17239,6 @@
     <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="AM7:AO7"/>
     <mergeCell ref="AP7:AR7"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
     <mergeCell ref="S7:U7"/>
     <mergeCell ref="V5:X5"/>
     <mergeCell ref="Y5:AA5"/>
@@ -17240,7 +17256,21 @@
     <mergeCell ref="AG79:AI79"/>
     <mergeCell ref="AJ79:AL79"/>
     <mergeCell ref="AM79:AO79"/>
-    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AB77:AD77"/>
+    <mergeCell ref="AG77:AI77"/>
+    <mergeCell ref="AJ77:AL77"/>
+    <mergeCell ref="AM77:AO77"/>
+    <mergeCell ref="AB75:AD75"/>
+    <mergeCell ref="AG75:AI75"/>
+    <mergeCell ref="AJ75:AL75"/>
+    <mergeCell ref="AM75:AO75"/>
+    <mergeCell ref="AB73:AD73"/>
+    <mergeCell ref="AG73:AI73"/>
+    <mergeCell ref="AJ73:AL73"/>
+    <mergeCell ref="AM73:AO73"/>
+    <mergeCell ref="AB10:AD10"/>
+    <mergeCell ref="AG10:AI10"/>
+    <mergeCell ref="AJ10:AL10"/>
     <mergeCell ref="E79:G79"/>
     <mergeCell ref="H79:J79"/>
     <mergeCell ref="K79:M79"/>
@@ -17250,9 +17280,6 @@
     <mergeCell ref="Y79:AA79"/>
     <mergeCell ref="AB78:AD78"/>
     <mergeCell ref="AG78:AI78"/>
-    <mergeCell ref="AJ78:AL78"/>
-    <mergeCell ref="AM78:AO78"/>
-    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="E78:G78"/>
     <mergeCell ref="H78:J78"/>
     <mergeCell ref="K78:M78"/>
@@ -17260,11 +17287,6 @@
     <mergeCell ref="S78:U78"/>
     <mergeCell ref="V78:X78"/>
     <mergeCell ref="Y78:AA78"/>
-    <mergeCell ref="AB77:AD77"/>
-    <mergeCell ref="AG77:AI77"/>
-    <mergeCell ref="AJ77:AL77"/>
-    <mergeCell ref="AM77:AO77"/>
-    <mergeCell ref="AP77:AR77"/>
     <mergeCell ref="E77:G77"/>
     <mergeCell ref="H77:J77"/>
     <mergeCell ref="K77:M77"/>
@@ -17274,9 +17296,6 @@
     <mergeCell ref="Y77:AA77"/>
     <mergeCell ref="AB76:AD76"/>
     <mergeCell ref="AG76:AI76"/>
-    <mergeCell ref="AJ76:AL76"/>
-    <mergeCell ref="AM76:AO76"/>
-    <mergeCell ref="AP76:AR76"/>
     <mergeCell ref="E76:G76"/>
     <mergeCell ref="H76:J76"/>
     <mergeCell ref="K76:M76"/>
@@ -17284,11 +17303,6 @@
     <mergeCell ref="S76:U76"/>
     <mergeCell ref="V76:X76"/>
     <mergeCell ref="Y76:AA76"/>
-    <mergeCell ref="AB75:AD75"/>
-    <mergeCell ref="AG75:AI75"/>
-    <mergeCell ref="AJ75:AL75"/>
-    <mergeCell ref="AM75:AO75"/>
-    <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="E75:G75"/>
     <mergeCell ref="H75:J75"/>
     <mergeCell ref="K75:M75"/>
@@ -17298,9 +17312,6 @@
     <mergeCell ref="Y75:AA75"/>
     <mergeCell ref="AB74:AD74"/>
     <mergeCell ref="AG74:AI74"/>
-    <mergeCell ref="AJ74:AL74"/>
-    <mergeCell ref="AM74:AO74"/>
-    <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="E74:G74"/>
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="K74:M74"/>
@@ -17308,14 +17319,15 @@
     <mergeCell ref="S74:U74"/>
     <mergeCell ref="V74:X74"/>
     <mergeCell ref="Y74:AA74"/>
-    <mergeCell ref="AB73:AD73"/>
-    <mergeCell ref="AG73:AI73"/>
-    <mergeCell ref="AJ73:AL73"/>
-    <mergeCell ref="AM73:AO73"/>
-    <mergeCell ref="AP73:AR73"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="K73:M73"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="S81:U81"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="Y81:AA81"/>
+    <mergeCell ref="AB80:AD80"/>
+    <mergeCell ref="AG80:AI80"/>
     <mergeCell ref="N73:P73"/>
     <mergeCell ref="S73:U73"/>
     <mergeCell ref="V73:X73"/>
@@ -17325,16 +17337,20 @@
     <mergeCell ref="AJ81:AL81"/>
     <mergeCell ref="AM81:AO81"/>
     <mergeCell ref="AP81:AR81"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="H81:J81"/>
-    <mergeCell ref="K81:M81"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="S81:U81"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="Y81:AA81"/>
-    <mergeCell ref="AB10:AD10"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AJ80:AL80"/>
+    <mergeCell ref="AM80:AO80"/>
+    <mergeCell ref="AP75:AR75"/>
+    <mergeCell ref="AJ74:AL74"/>
+    <mergeCell ref="AM74:AO74"/>
+    <mergeCell ref="AP74:AR74"/>
+    <mergeCell ref="AP77:AR77"/>
+    <mergeCell ref="AJ76:AL76"/>
+    <mergeCell ref="AM76:AO76"/>
+    <mergeCell ref="AP76:AR76"/>
+    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AJ78:AL78"/>
+    <mergeCell ref="AM78:AO78"/>
+    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="AM10:AO10"/>
     <mergeCell ref="AP10:AR10"/>
     <mergeCell ref="E10:G10"/>
@@ -17344,7 +17360,6 @@
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AG9:AI9"/>
     <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AM9:AO9"/>
@@ -17365,10 +17380,6 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AB80:AD80"/>
-    <mergeCell ref="AG80:AI80"/>
-    <mergeCell ref="AJ80:AL80"/>
-    <mergeCell ref="AM80:AO80"/>
     <mergeCell ref="AP80:AR80"/>
     <mergeCell ref="E80:G80"/>
     <mergeCell ref="H80:J80"/>
@@ -17389,6 +17400,10 @@
     <mergeCell ref="S72:U72"/>
     <mergeCell ref="V72:X72"/>
     <mergeCell ref="Y72:AA72"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="K73:M73"/>
     <mergeCell ref="AB71:AD71"/>
     <mergeCell ref="AG71:AI71"/>
     <mergeCell ref="AJ71:AL71"/>
@@ -17610,7 +17625,7 @@
       <c r="R4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="S4" s="37"/>
+      <c r="S4" s="36"/>
       <c r="T4" s="30"/>
       <c r="AF4" s="14" t="s">
         <v>5</v>
@@ -17673,7 +17688,7 @@
       <c r="AF5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="AG5" s="36" t="s">
+      <c r="AG5" s="37" t="s">
         <v>191</v>
       </c>
       <c r="AH5" s="21"/>
@@ -22405,6 +22420,12 @@
     <mergeCell ref="AB11:AD11"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AM6:AO6"/>
     <mergeCell ref="AP6:AR6"/>
     <mergeCell ref="AP8:AR8"/>
@@ -22421,11 +22442,6 @@
     <mergeCell ref="AJ7:AL7"/>
     <mergeCell ref="AM7:AO7"/>
     <mergeCell ref="AP7:AR7"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
     <mergeCell ref="S7:U7"/>
     <mergeCell ref="V5:X5"/>
     <mergeCell ref="Y5:AA5"/>
@@ -22443,7 +22459,21 @@
     <mergeCell ref="AG79:AI79"/>
     <mergeCell ref="AJ79:AL79"/>
     <mergeCell ref="AM79:AO79"/>
-    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AB77:AD77"/>
+    <mergeCell ref="AG77:AI77"/>
+    <mergeCell ref="AJ77:AL77"/>
+    <mergeCell ref="AM77:AO77"/>
+    <mergeCell ref="AB75:AD75"/>
+    <mergeCell ref="AG75:AI75"/>
+    <mergeCell ref="AJ75:AL75"/>
+    <mergeCell ref="AM75:AO75"/>
+    <mergeCell ref="AB73:AD73"/>
+    <mergeCell ref="AG73:AI73"/>
+    <mergeCell ref="AJ73:AL73"/>
+    <mergeCell ref="AM73:AO73"/>
+    <mergeCell ref="AB10:AD10"/>
+    <mergeCell ref="AG10:AI10"/>
+    <mergeCell ref="AJ10:AL10"/>
     <mergeCell ref="E79:G79"/>
     <mergeCell ref="H79:J79"/>
     <mergeCell ref="K79:M79"/>
@@ -22453,9 +22483,6 @@
     <mergeCell ref="Y79:AA79"/>
     <mergeCell ref="AB78:AD78"/>
     <mergeCell ref="AG78:AI78"/>
-    <mergeCell ref="AJ78:AL78"/>
-    <mergeCell ref="AM78:AO78"/>
-    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="E78:G78"/>
     <mergeCell ref="H78:J78"/>
     <mergeCell ref="K78:M78"/>
@@ -22463,11 +22490,6 @@
     <mergeCell ref="S78:U78"/>
     <mergeCell ref="V78:X78"/>
     <mergeCell ref="Y78:AA78"/>
-    <mergeCell ref="AB77:AD77"/>
-    <mergeCell ref="AG77:AI77"/>
-    <mergeCell ref="AJ77:AL77"/>
-    <mergeCell ref="AM77:AO77"/>
-    <mergeCell ref="AP77:AR77"/>
     <mergeCell ref="E77:G77"/>
     <mergeCell ref="H77:J77"/>
     <mergeCell ref="K77:M77"/>
@@ -22477,9 +22499,6 @@
     <mergeCell ref="Y77:AA77"/>
     <mergeCell ref="AB76:AD76"/>
     <mergeCell ref="AG76:AI76"/>
-    <mergeCell ref="AJ76:AL76"/>
-    <mergeCell ref="AM76:AO76"/>
-    <mergeCell ref="AP76:AR76"/>
     <mergeCell ref="E76:G76"/>
     <mergeCell ref="H76:J76"/>
     <mergeCell ref="K76:M76"/>
@@ -22487,11 +22506,6 @@
     <mergeCell ref="S76:U76"/>
     <mergeCell ref="V76:X76"/>
     <mergeCell ref="Y76:AA76"/>
-    <mergeCell ref="AB75:AD75"/>
-    <mergeCell ref="AG75:AI75"/>
-    <mergeCell ref="AJ75:AL75"/>
-    <mergeCell ref="AM75:AO75"/>
-    <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="E75:G75"/>
     <mergeCell ref="H75:J75"/>
     <mergeCell ref="K75:M75"/>
@@ -22501,9 +22515,6 @@
     <mergeCell ref="Y75:AA75"/>
     <mergeCell ref="AB74:AD74"/>
     <mergeCell ref="AG74:AI74"/>
-    <mergeCell ref="AJ74:AL74"/>
-    <mergeCell ref="AM74:AO74"/>
-    <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="E74:G74"/>
     <mergeCell ref="H74:J74"/>
     <mergeCell ref="K74:M74"/>
@@ -22511,14 +22522,15 @@
     <mergeCell ref="S74:U74"/>
     <mergeCell ref="V74:X74"/>
     <mergeCell ref="Y74:AA74"/>
-    <mergeCell ref="AB73:AD73"/>
-    <mergeCell ref="AG73:AI73"/>
-    <mergeCell ref="AJ73:AL73"/>
-    <mergeCell ref="AM73:AO73"/>
-    <mergeCell ref="AP73:AR73"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="K73:M73"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="N81:P81"/>
+    <mergeCell ref="S81:U81"/>
+    <mergeCell ref="V81:X81"/>
+    <mergeCell ref="Y81:AA81"/>
+    <mergeCell ref="AB80:AD80"/>
+    <mergeCell ref="AG80:AI80"/>
     <mergeCell ref="N73:P73"/>
     <mergeCell ref="S73:U73"/>
     <mergeCell ref="V73:X73"/>
@@ -22528,16 +22540,20 @@
     <mergeCell ref="AJ81:AL81"/>
     <mergeCell ref="AM81:AO81"/>
     <mergeCell ref="AP81:AR81"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="H81:J81"/>
-    <mergeCell ref="K81:M81"/>
-    <mergeCell ref="N81:P81"/>
-    <mergeCell ref="S81:U81"/>
-    <mergeCell ref="V81:X81"/>
-    <mergeCell ref="Y81:AA81"/>
-    <mergeCell ref="AB10:AD10"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AJ80:AL80"/>
+    <mergeCell ref="AM80:AO80"/>
+    <mergeCell ref="AP75:AR75"/>
+    <mergeCell ref="AJ74:AL74"/>
+    <mergeCell ref="AM74:AO74"/>
+    <mergeCell ref="AP74:AR74"/>
+    <mergeCell ref="AP77:AR77"/>
+    <mergeCell ref="AJ76:AL76"/>
+    <mergeCell ref="AM76:AO76"/>
+    <mergeCell ref="AP76:AR76"/>
+    <mergeCell ref="AP79:AR79"/>
+    <mergeCell ref="AJ78:AL78"/>
+    <mergeCell ref="AM78:AO78"/>
+    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="AM10:AO10"/>
     <mergeCell ref="AP10:AR10"/>
     <mergeCell ref="E10:G10"/>
@@ -22547,7 +22563,6 @@
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V10:X10"/>
     <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AB9:AD9"/>
     <mergeCell ref="AG9:AI9"/>
     <mergeCell ref="AJ9:AL9"/>
     <mergeCell ref="AM9:AO9"/>
@@ -22568,10 +22583,6 @@
     <mergeCell ref="Y8:AA8"/>
     <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AB80:AD80"/>
-    <mergeCell ref="AG80:AI80"/>
-    <mergeCell ref="AJ80:AL80"/>
-    <mergeCell ref="AM80:AO80"/>
     <mergeCell ref="AP80:AR80"/>
     <mergeCell ref="E80:G80"/>
     <mergeCell ref="H80:J80"/>
@@ -22592,6 +22603,10 @@
     <mergeCell ref="S72:U72"/>
     <mergeCell ref="V72:X72"/>
     <mergeCell ref="Y72:AA72"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="K73:M73"/>
     <mergeCell ref="AB71:AD71"/>
     <mergeCell ref="AG71:AI71"/>
     <mergeCell ref="AJ71:AL71"/>
